--- a/OrganizedData/Youngs_Modulus_Results/Youngs_Modulus_All_Specimens.xlsx
+++ b/OrganizedData/Youngs_Modulus_Results/Youngs_Modulus_All_Specimens.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="5240" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="10480" uniqueCount="785">
   <si>
     <t>Year</t>
   </si>
@@ -1335,6 +1335,1041 @@
   </si>
   <si>
     <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10445\tension\TENSION_20260424_180221_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_033016\compression\COMPRESSION_20230417_163903_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040316\compression\COMPRESSION_20230403_163602_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040411\compression\COMPRESSION_20230404_115233_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040416\compression\COMPRESSION_20231114_160620_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\compression\COMPRESSION_20230405_91656_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040608\compression\COMPRESSION_20230406_93115_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040614\compression\COMPRESSION_20230406_142547_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040618\compression\COMPRESSION_20230406_174442_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040414\compression\COMPRESSION_20230419_171957_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040708\compression\COMPRESSION_20230407_90153_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040714\compression\COMPRESSION_20230407_151551_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042111\compression\COMPRESSION_20230407_121438_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042115\compression\COMPRESSION_20230421_150517_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040411\tension\TENSION_20230404_111738_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040416\tension\TENSION_20231114_155317_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040614\tension\TENSION_20230406_141717_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040618\tension\TENSION_20230406_180231_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040414\tension\TENSION_20230419_173120_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040708\tension\TENSION_20230407_84343_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040714\tension\TENSION_20230407_145506_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042109\tension\TENSION_20230421_92743_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042111\tension\TENSION_20230407_123028_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042115\tension\TENSION_20230421_144807_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\monday\monday_040316\compression\COMPRESSION_20230403_163602_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040411\compression\COMPRESSION_20230404_114857_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040416\compression\COMPRESSION_20231114_160620_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\compression\COMPRESSION_20230405_91423_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040608\compression\COMPRESSION_20230406_93115_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040614\compression\COMPRESSION_20230406_142547_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040414\compression\COMPRESSION_20230419_171957_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040708\compression\COMPRESSION_20230407_90153_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040714\compression\COMPRESSION_20230407_151551_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042111\compression\COMPRESSION_20230407_121438_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042115\compression\COMPRESSION_20230421_150517_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040411\tension\TENSION_20230404_113913_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\tuesday\tuesday_040416\tension\TENSION_20231114_155317_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040614\tension\TENSION_20230406_141717_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\thursday\thursday_040618\tension\TENSION_20230406_180231_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040414\tension\TENSION_20230419_173120_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040708\tension\TENSION_20230407_84343_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_040714\tension\TENSION_20230407_145506_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042109\tension\TENSION_20230421_92743_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042111\tension\TENSION_20230407_123028_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\friday\friday_042115\tension\TENSION_20230421_144807_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10418\compression\COMPRESSION_20240401_160942_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10428\compression\COMPRESSION_20240401_185443_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10432\compression\COMPRESSION_20240401_82330_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10415\compression\COMPRESSION_20240402_91710_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10417\compression\COMPRESSION_20240402_111706_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10422\compression\COMPRESSION_20240402_180620_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10431\compression\COMPRESSION_20240402_143204_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10416\compression\COMPRESSION_20240403_84523_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10424\compression\COMPRESSION_20240403_164647_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10425\compression\COMPRESSION_20240403_135735_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10421\compression\COMPRESSION_20240404_112804_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\COMPRESSION_20240404_175301.is_comp_Exports\COMPRESSION_20240404_175301_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10420\COMPRESSION_20240405_121754.is_comp_Exports\COMPRESSION_20240405_121754_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\COMPRESSION_20240405_152822.is_comp_Exports\COMPRESSION_20240405_152822_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10418\compression\COMPRESSION_20240415_164723_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10428\compression\COMPRESSION_20240415_185638_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10432\compression\COMPRESSION_20240415_83136_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10415\compression\COMPRESSION_20240416_84813_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10417\compression\COMPRESSION_20240416_120439_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10422\compression\COMPRESSION_20240416_172030_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10431\compression\COMPRESSION_20240416_145110_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10416\compression\COMPRESSION_20240417_84148_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10424\compression\COMPRESSION_20240417_171125_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10425\compression\COMPRESSION_20240417_140453_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10419\compression\COMPRESSION_20240418_82512_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10421\compression\COMPRESSION_20240418_120928_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10423\compression\COMPRESSION_20240418_182603_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10430\compression\COMPRESSION_20240418_142637_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10420\compression\COMPRESSION_20240419_123337_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10434\compression\COMPRESSION_20240419_155330_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10418\tension\TENSION_20240401_163910_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10428\tension\TENSION_20240401_191732_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10415\tension\TENSION_20240402_82137_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10417\tension\TENSION_20240404_121403_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10422\tension\TENSION_20240402_181443_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10431\tension\TENSION_20240402_144717_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10416\tension\TENSION_20240403_81840_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10424\tension\TENSION_20240403_172802_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10421\tension\TENSION_20240404_121403_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\TENSION_20240404_174421.is_tens_Exports\TENSION_20240404_174421_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\TENSION_20240405_150639.is_tens_Exports\TENSION_20240405_150639_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10418\tension\TENSION_20240415_163324_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10428\tension\TENSION_20240415_195322_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10432\tension\TENSION_20240415_90842_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10415\tension\TENSION_20240416_81513_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10417\tension\TENSION_20240416_121310_3.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10422\tension\TENSION_20240416_174844_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10431\tension\TENSION_20240416_144009_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10424\tension\TENSION_20240417_173337_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10425\tension\TENSION_20240417_135228_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10419\tension\TENSION_20240418_91816_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10421\tension\TENSION_20240418_115359_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10423\tension\TENSION_20240418_175708_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10430\tension\TENSION_20240418_150031_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10434\tension\TENSION_20240419_153237_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10428\compression\COMPRESSION_20240401_185443_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10432\compression\COMPRESSION_20240401_82330_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10417\compression\COMPRESSION_20240402_111706_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10422\compression\COMPRESSION_20240402_180620_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10431\compression\COMPRESSION_20240402_143204_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10416\compression\COMPRESSION_20240403_84523_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10424\compression\COMPRESSION_20240403_164647_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10425\compression\COMPRESSION_20240403_135735_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10421\compression\COMPRESSION_20240404_112804_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\COMPRESSION_20240404_175301.is_comp_Exports\COMPRESSION_20240404_175301_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\friday\friday_10434\COMPRESSION_20240405_152822.is_comp_Exports\COMPRESSION_20240405_152822_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10418\compression\COMPRESSION_20240415_164723_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10428\compression\COMPRESSION_20240415_185638_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10432\compression\COMPRESSION_20240415_83136_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10415\compression\COMPRESSION_20240416_84813_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10417\compression\COMPRESSION_20240416_120439_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10422\compression\COMPRESSION_20240416_172030_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10431\compression\COMPRESSION_20240416_145110_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10416\compression\COMPRESSION_20240417_84148_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10424\compression\COMPRESSION_20240417_171125_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10425\compression\COMPRESSION_20240417_140453_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10419\compression\COMPRESSION_20240418_82512_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10421\compression\COMPRESSION_20240418_120928_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10423\compression\COMPRESSION_20240418_182603_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10430\compression\COMPRESSION_20240418_142637_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10420\compression\COMPRESSION_20240419_113912_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\friday\friday_10434\compression\COMPRESSION_20240419_155330_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10418\tension\TENSION_20240401_163910_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\monday\monday_10428\tension\TENSION_20240401_191732_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10415\tension\TENSION_20240402_84137_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10417\tension\TENSION_20240404_121403_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10422\tension\TENSION_20240402_181443_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\tuesday\tuesday_10431\tension\TENSION_20240402_144717_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10416\tension\TENSION_20240403_81840_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\wednesday\wednesday_10424\tension\TENSION_20240403_172802_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10421\tension\TENSION_20240404_121403_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch1\thursday\thursday_10423\TENSION_20240404_174421.is_tens_Exports\TENSION_20240404_174421_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10418\tension\TENSION_20240415_163324_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\monday\monday_10428\tension\TENSION_20240415_195322_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10415\tension\TENSION_20240416_81513_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10417\tension\TENSION_20240416_121310_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10422\tension\TENSION_20240416_174844_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\tuesday\tuesday_10431\tension\TENSION_20240416_144009_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10424\tension\TENSION_20240417_173337_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\wednesday\wednesday_10425\tension\TENSION_20240417_135228_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10419\tension\TENSION_20240418_85826_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10421\tension\TENSION_20240418_115359_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10423\tension\TENSION_20240418_175708_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2024_organized\batch2\thursday\thursday_10430\tension\TENSION_20240418_150031_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10444\compression\COMPRESSION_20250407_192028_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10448\compression\COMPRESSION_20250410_122710_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10451\compression\COMPRESSION_20250407_155960_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10438\compression\CNT Compression_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10447\compression\COMPRESSION_20250408_144234_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10452\compression\COMPRESSION_20250408_83342_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10454\compression\compression_epoxy_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\compression\COMPRESSION_20250409_172535_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\compression\COMPRESSION_20250409_141814_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10446\compression\COMPRESSION_20250410_143927_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\compression\COMPRESSION_20250409_83645_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10435\compression\COMPRESSION_20250410_90238_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10437\compression\COMPRESSION_20250410_122710_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10436\compression\COMPRESSION_20250411_120041_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10450\compression\COMPRESSION_20250411_150039_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10444\compression\COMPRESSION_20250407_192028_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10448\compression\COMPRESSION_20250421_90459_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10438\compression\CNT Compression_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10447\compression\COMPRESSION_20250408_144234_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10452\compression\COMPRESSION_20250408_83342_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10454\compression\compression_epoxy_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\compression\COMPRESSION_20250409_172535_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\compression\COMPRESSION_20250409_141814_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10446\compression\COMPRESSION_20250410_143927_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\compression\COMPRESSION_20250409_83645_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10435\compression\COMPRESSION_20250410_90238_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10437\compression\COMPRESSION_20250410_122710_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10436\compression\COMPRESSION_20250411_120041_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10450\compression\COMPRESSION_20250411_150039_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10444\tension\TENSION_20250407_190145_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10448\tension\TENSION_20250410_121606_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10451\tension\TENSION_20250407_164257_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10438\tension\CNT Tension_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10447\tension\TENSION_20250408_142244_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10452\tension\TENSION_20250408_85829_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10454\fracture\compactTension_cnt_4_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\tension\TENSION_20250409_171048_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10446\tension\TENSION_20250410_151057_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10437\tension\TENSION_20250410_121606_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10436\tension\TENSION_20250411_113816_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10450\tension\TENSION_20250411_145017_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10444\tension\TENSION_20250407_190145_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10448\tension\TENSION_20250421_84334_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10451\tension\TENSION_20250407_164257_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10438\tension\CNT Tension_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10452\tension\TENSION_20250408_85829_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10454\fracture\compactTension_cnt_4_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\tension\TENSION_20250409_171048_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10446\tension\TENSION_20250410_151057_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10435\tension\TENSION_20250410_95607_4.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10437\tension\TENSION_20250410_121606_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10436\tension\TENSION_20250411_113816_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10450\tension\TENSION_20250411_145017_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10444\compression\COMPRESSION_20250407_192028_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10448\compression\COMPRESSION_20250410_122710_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10438\compression\CNT Compression_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10447\compression\COMPRESSION_20250408_144234_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10452\compression\COMPRESSION_20250408_83342_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10454\compression\compression_cnt_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\compression\COMPRESSION_20250409_172535_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\compression\COMPRESSION_20250409_141814_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10446\compression\COMPRESSION_20250410_143927_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\compression\COMPRESSION_20250409_83645_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10435\compression\COMPRESSION_20250410_90238_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10437\compression\COMPRESSION_20250410_122710_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10436\compression\COMPRESSION_20250411_120041_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10450\compression\COMPRESSION_20250411_150039_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10448\compression\COMPRESSION_20250421_90459_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10438\compression\CNT Compression_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10447\compression\COMPRESSION_20250408_144234_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10452\compression\COMPRESSION_20250408_83342_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10454\compression\compression_cnt_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\compression\COMPRESSION_20250409_172535_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\compression\COMPRESSION_20250409_141814_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10446\compression\COMPRESSION_20250410_143927_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\compression\COMPRESSION_20250409_83645_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10435\compression\COMPRESSION_20250410_90238_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10437\compression\COMPRESSION_20250410_122710_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10436\compression\COMPRESSION_20250411_120041_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10450\compression\COMPRESSION_20250411_150039_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10444\tension\TENSION_20250407_190145_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10448\tension\TENSION_20250408_85829_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10451\tension\TENSION_20250407_164257_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10438\tension\CNT Tension_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10452\tension\TENSION_20250408_85829_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10454\fracture\compactTension_cnt_4_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\tension\TENSION_20250409_171048_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10446\tension\TENSION_20250410_151057_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10437\tension\TENSION_20250408_85829_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10436\tension\TENSION_20250411_113816_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10444\tension\TENSION_20250407_190145_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10448\tension\TENSION_20250421_84334_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10451\tension\TENSION_20250407_164257_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10438\tension\CNT Tension_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10452\tension\TENSION_20250408_85829_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10454\fracture\compactTension_cnt_4_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\tension\TENSION_20250409_171048_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10446\tension\TENSION_20250410_151057_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10437\tension\TENSION_20250421_84334_3.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10453\compression\COMPRESSION_20260406_90517_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10457\compression\COMPRESSION_20260406_170533_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10440\compression\COMPRESSION_20260407_174032_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10449\compression\COMPRESSION_20260407_144614_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10442\compression\COMPRESSION_20260408_164418_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10443\compression\COMPRESSION_20260408_134837_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10447\compression\COMPRESSION_20260408_195727_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10441\compression\COMPRESSION_20260409_172654_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10448\compression\COMPRESSION_20260409_142206_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10450\compression\COMPRESSION_20260409_110850_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10444\compression\COMPRESSION_20260410_82205_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10445\compression\COMPRESSION_20260410_174614_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10451\compression\COMPRESSION_20260410_115513_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10458\compression\COMPRESSION_20260410_161007_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10446\compression\COMPRESSION_20260420_183618_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10453\compression\COMPRESSION_20260420_81741_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10457\compression\COMPRESSION_20260420_165050_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10440\compression\COMPRESSION_20260421_171521_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10449\compression\COMPRESSION_20260421_141116_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10454\compression\COMPRESSION_20260421_111311_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10456\compression\COMPRESSION_20260421_90601_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\compression\COMPRESSION_20260422_163210_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\compression\COMPRESSION_20260422_133560_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\compression\COMPRESSION_20260422_193341_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10441\compression\COMPRESSION_20260423_175437_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10448\compression\COMPRESSION_20260409_142206_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10450\compression\COMPRESSION_20260423_110609_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10452\compression\COMPRESSION_20260423_81011_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10444\compression\COMPRESSION_20260424_80730_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10445\compression\COMPRESSION_20260424_174058_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10451\compression\COMPRESSION_20260424_112945_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10458\compression\COMPRESSION_20260424_145207_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10440\tension\TENSION_20260407_181007_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10449\tension\TENSION_20260407_150234_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10443\tension\TENSION_20260408_142846_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10447\tension\TENSION_20260424_180221_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10441\tension\TENSION_20260409_174654_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10450\tension\TENSION_20260409_113006_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10445\tension\TENSION_20260410_182528_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10451\tension\TENSION_20260410_113512_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10458\tension\TENSION_20260410_165112_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10446\tension\TENSION_20260420_185903_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10453\tension\TENSION_20260420_83635_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10440\tension\TENSION_20260421_142756_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10449\tension\TENSION_20260421_142756_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10456\tension\TENSION_20260421_101138_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\tension\TENSION_20260422_164517_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\tension\TENSION_20260422_135940_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\tension\TENSION_20260422_195602_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10441\tension\TENSION_20260423_182424_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10450\tension\TENSION_20260423_111551_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10452\tension\TENSION_20260423_82926_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10445\tension\TENSION_20260424_180221_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10458\tension\TENSION_20260424_154825_3.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10453\compression\COMPRESSION_20260406_90517_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\monday\monday_10457\compression\COMPRESSION_20260406_153036_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10440\compression\COMPRESSION_20260407_173344_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10442\compression\COMPRESSION_20260408_164418_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10443\compression\COMPRESSION_20260408_134837_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10447\compression\COMPRESSION_20260408_193748_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10441\compression\COMPRESSION_20260409_172037_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10448\compression\COMPRESSION_20260409_140753_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10444\compression\COMPRESSION_20260410_82205_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10451\compression\COMPRESSION_20260410_115513_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10458\compression\COMPRESSION_20260410_161410_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10453\compression\COMPRESSION_20260420_81741_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10440\compression\COMPRESSION_20260421_170933_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10449\compression\COMPRESSION_20260421_141116_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10454\compression\COMPRESSION_20260421_111311_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10456\compression\COMPRESSION_20260421_90601_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\compression\COMPRESSION_20260422_163210_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\compression\COMPRESSION_20260422_133560_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\compression\COMPRESSION_20260422_194554_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10441\compression\COMPRESSION_20260423_175134_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10448\compression\COMPRESSION_20260409_140753_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10450\compression\COMPRESSION_20260423_110609_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10452\compression\COMPRESSION_20260423_81011_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10444\compression\COMPRESSION_20260424_80730_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10445\compression\COMPRESSION_20260424_174058_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10451\compression\COMPRESSION_20260424_112945_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10458\compression\COMPRESSION_20260424_145207_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\tuesday\tuesday_10440\tension\TENSION_20260407_175922_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10443\tension\TENSION_20260408_142846_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\wednesday\wednesday_10447\tension\TENSION_20260424_180221_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10441\tension\TENSION_20260409_175433_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\thursday\thursday_10450\tension\TENSION_20260409_113006_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10445\tension\TENSION_20260410_182528_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch1\friday\friday_10458\tension\TENSION_20260410_165112_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10446\tension\TENSION_20260420_185903_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\monday\monday_10453\tension\TENSION_20260420_83635_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\tuesday\tuesday_10440\tension\TENSION_20260421_142756_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\tension\TENSION_20260422_164517_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\tension\TENSION_20260422_135940_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\tension\TENSION_20260422_200525_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10441\tension\TENSION_20260423_181633_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10450\tension\TENSION_20260423_111551_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\thursday\thursday_10452\tension\TENSION_20260423_82926_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\friday\friday_10445\tension\TENSION_20260424_180221_1.csv</t>
   </si>
 </sst>
 </file>
@@ -1383,22 +2418,22 @@
   <dimension ref="A1:P346"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.90625" customWidth="true"/>
-    <col min="2" max="2" width="7.90625" customWidth="true"/>
-    <col min="3" max="3" width="11.81640625" customWidth="true"/>
-    <col min="4" max="4" width="6.54296875" customWidth="true"/>
-    <col min="5" max="5" width="10.36328125" customWidth="true"/>
-    <col min="6" max="6" width="17.36328125" customWidth="true"/>
-    <col min="7" max="7" width="7.36328125" customWidth="true"/>
-    <col min="8" max="8" width="13.7265625" customWidth="true"/>
-    <col min="9" max="9" width="13.81640625" customWidth="true"/>
-    <col min="10" max="10" width="19" customWidth="true"/>
-    <col min="11" max="11" width="13.453125" customWidth="true"/>
-    <col min="12" max="12" width="14.81640625" customWidth="true"/>
-    <col min="13" max="13" width="11.6328125" customWidth="true"/>
-    <col min="14" max="14" width="10.90625" customWidth="true"/>
-    <col min="15" max="15" width="10.54296875" customWidth="true"/>
-    <col min="16" max="16" width="195.7265625" customWidth="true"/>
+    <col min="1" max="1" width="5.140625" customWidth="true"/>
+    <col min="2" max="2" width="8.5703125" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
+    <col min="4" max="4" width="7" customWidth="true"/>
+    <col min="5" max="5" width="11.28515625" customWidth="true"/>
+    <col min="6" max="6" width="18.28515625" customWidth="true"/>
+    <col min="7" max="7" width="7.85546875" customWidth="true"/>
+    <col min="8" max="8" width="15" customWidth="true"/>
+    <col min="9" max="9" width="15" customWidth="true"/>
+    <col min="10" max="10" width="20" customWidth="true"/>
+    <col min="11" max="11" width="13.7109375" customWidth="true"/>
+    <col min="12" max="12" width="16.28515625" customWidth="true"/>
+    <col min="13" max="13" width="12.7109375" customWidth="true"/>
+    <col min="14" max="14" width="11.85546875" customWidth="true"/>
+    <col min="15" max="15" width="11.7109375" customWidth="true"/>
+    <col min="16" max="16" width="175.28515625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1480,10 +2515,10 @@
         <v>1</v>
       </c>
       <c r="J2" s="0">
-        <v>1577.5282337380456</v>
+        <v>1577.5282337380461</v>
       </c>
       <c r="K2" s="0">
-        <v>0.99053861886916805</v>
+        <v>0.99053861886916794</v>
       </c>
       <c r="L2" s="0">
         <v>10</v>
@@ -1498,7 +2533,7 @@
         <v>1</v>
       </c>
       <c r="P2" s="0" t="s">
-        <v>95</v>
+        <v>440</v>
       </c>
     </row>
     <row r="3">
@@ -1544,7 +2579,7 @@
         <v>0</v>
       </c>
       <c r="P3" s="0" t="s">
-        <v>96</v>
+        <v>441</v>
       </c>
     </row>
     <row r="4">
@@ -1576,7 +2611,7 @@
         <v>1</v>
       </c>
       <c r="J4" s="0">
-        <v>812.17656145159049</v>
+        <v>812.17656145159026</v>
       </c>
       <c r="K4" s="0">
         <v>0.9999145356608955</v>
@@ -1594,7 +2629,7 @@
         <v>1</v>
       </c>
       <c r="P4" s="0" t="s">
-        <v>97</v>
+        <v>442</v>
       </c>
     </row>
     <row r="5">
@@ -1629,7 +2664,7 @@
         <v>1263.4461565876516</v>
       </c>
       <c r="K5" s="0">
-        <v>0.98756011177686887</v>
+        <v>0.98756011177686875</v>
       </c>
       <c r="L5" s="0">
         <v>10</v>
@@ -1644,7 +2679,7 @@
         <v>1</v>
       </c>
       <c r="P5" s="0" t="s">
-        <v>98</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6">
@@ -1676,7 +2711,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="0">
-        <v>36.968752859095488</v>
+        <v>36.968752859095495</v>
       </c>
       <c r="K6" s="0">
         <v>0.98178320762864302</v>
@@ -1694,7 +2729,7 @@
         <v>1</v>
       </c>
       <c r="P6" s="0" t="s">
-        <v>99</v>
+        <v>444</v>
       </c>
     </row>
     <row r="7">
@@ -1744,7 +2779,7 @@
         <v>1</v>
       </c>
       <c r="P7" s="0" t="s">
-        <v>100</v>
+        <v>445</v>
       </c>
     </row>
     <row r="8">
@@ -1779,7 +2814,7 @@
         <v>188.66620995067865</v>
       </c>
       <c r="K8" s="0">
-        <v>0.83977034555327845</v>
+        <v>0.83977034555327856</v>
       </c>
       <c r="L8" s="0">
         <v>10</v>
@@ -1794,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="0" t="s">
-        <v>101</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -1844,7 +2879,7 @@
         <v>1</v>
       </c>
       <c r="P9" s="0" t="s">
-        <v>102</v>
+        <v>447</v>
       </c>
     </row>
     <row r="10">
@@ -1894,7 +2929,7 @@
         <v>1</v>
       </c>
       <c r="P10" s="0" t="s">
-        <v>103</v>
+        <v>448</v>
       </c>
     </row>
     <row r="11">
@@ -1944,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="0" t="s">
-        <v>104</v>
+        <v>449</v>
       </c>
     </row>
     <row r="12">
@@ -1994,7 +3029,7 @@
         <v>1</v>
       </c>
       <c r="P12" s="0" t="s">
-        <v>105</v>
+        <v>450</v>
       </c>
     </row>
     <row r="13">
@@ -2026,7 +3061,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="0">
-        <v>1152.9138297782222</v>
+        <v>1152.9138297782224</v>
       </c>
       <c r="K13" s="0">
         <v>0.96947372692026201</v>
@@ -2044,7 +3079,7 @@
         <v>1</v>
       </c>
       <c r="P13" s="0" t="s">
-        <v>106</v>
+        <v>451</v>
       </c>
     </row>
     <row r="14">
@@ -2076,7 +3111,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="0">
-        <v>217.11967189177653</v>
+        <v>217.11967189177659</v>
       </c>
       <c r="K14" s="0">
         <v>0.96712552976165778</v>
@@ -2094,7 +3129,7 @@
         <v>1</v>
       </c>
       <c r="P14" s="0" t="s">
-        <v>107</v>
+        <v>452</v>
       </c>
     </row>
     <row r="15">
@@ -2126,7 +3161,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="0">
-        <v>2524.0614300894131</v>
+        <v>2524.0614300894135</v>
       </c>
       <c r="K15" s="0">
         <v>0.99863134409152532</v>
@@ -2144,7 +3179,7 @@
         <v>1</v>
       </c>
       <c r="P15" s="0" t="s">
-        <v>108</v>
+        <v>453</v>
       </c>
     </row>
     <row r="16">
@@ -2194,7 +3229,7 @@
         <v>1</v>
       </c>
       <c r="P16" s="0" t="s">
-        <v>109</v>
+        <v>454</v>
       </c>
     </row>
     <row r="17">
@@ -2244,7 +3279,7 @@
         <v>1</v>
       </c>
       <c r="P17" s="0" t="s">
-        <v>110</v>
+        <v>455</v>
       </c>
     </row>
     <row r="18">
@@ -2294,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="P18" s="0" t="s">
-        <v>111</v>
+        <v>456</v>
       </c>
     </row>
     <row r="19">
@@ -2344,7 +3379,7 @@
         <v>1</v>
       </c>
       <c r="P19" s="0" t="s">
-        <v>112</v>
+        <v>457</v>
       </c>
     </row>
     <row r="20">
@@ -2394,7 +3429,7 @@
         <v>1</v>
       </c>
       <c r="P20" s="0" t="s">
-        <v>113</v>
+        <v>458</v>
       </c>
     </row>
     <row r="21">
@@ -2426,7 +3461,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="0">
-        <v>1823.4795250269992</v>
+        <v>1823.4795250269983</v>
       </c>
       <c r="K21" s="0">
         <v>0.99911347890930613</v>
@@ -2444,7 +3479,7 @@
         <v>1</v>
       </c>
       <c r="P21" s="0" t="s">
-        <v>114</v>
+        <v>459</v>
       </c>
     </row>
     <row r="22">
@@ -2494,7 +3529,7 @@
         <v>1</v>
       </c>
       <c r="P22" s="0" t="s">
-        <v>115</v>
+        <v>460</v>
       </c>
     </row>
     <row r="23">
@@ -2544,7 +3579,7 @@
         <v>1</v>
       </c>
       <c r="P23" s="0" t="s">
-        <v>116</v>
+        <v>461</v>
       </c>
     </row>
     <row r="24">
@@ -2594,7 +3629,7 @@
         <v>1</v>
       </c>
       <c r="P24" s="0" t="s">
-        <v>117</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25">
@@ -2626,10 +3661,10 @@
         <v>1</v>
       </c>
       <c r="J25" s="0">
-        <v>2.7950992263799268</v>
+        <v>2.7950992263799259</v>
       </c>
       <c r="K25" s="0">
-        <v>0.52356504953545402</v>
+        <v>0.52356504953545424</v>
       </c>
       <c r="L25" s="0">
         <v>10</v>
@@ -2644,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="P25" s="0" t="s">
-        <v>118</v>
+        <v>463</v>
       </c>
     </row>
     <row r="26">
@@ -2676,7 +3711,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="0">
-        <v>1.5314082944005136</v>
+        <v>1.5314082944005125</v>
       </c>
       <c r="K26" s="0">
         <v>0.65872871479047057</v>
@@ -2694,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="P26" s="0" t="s">
-        <v>119</v>
+        <v>464</v>
       </c>
     </row>
     <row r="27">
@@ -2726,7 +3761,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="0">
-        <v>1734.3440438348966</v>
+        <v>1734.3440438348973</v>
       </c>
       <c r="K27" s="0">
         <v>0.98840687198923027</v>
@@ -2744,7 +3779,7 @@
         <v>1</v>
       </c>
       <c r="P27" s="0" t="s">
-        <v>120</v>
+        <v>465</v>
       </c>
     </row>
     <row r="28">
@@ -2776,7 +3811,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="0">
-        <v>30.482339810018175</v>
+        <v>30.482339810018182</v>
       </c>
       <c r="K28" s="0">
         <v>0.91343665817982434</v>
@@ -2794,7 +3829,7 @@
         <v>1</v>
       </c>
       <c r="P28" s="0" t="s">
-        <v>121</v>
+        <v>466</v>
       </c>
     </row>
     <row r="29">
@@ -2844,7 +3879,7 @@
         <v>1</v>
       </c>
       <c r="P29" s="0" t="s">
-        <v>122</v>
+        <v>467</v>
       </c>
     </row>
     <row r="30">
@@ -2894,7 +3929,7 @@
         <v>1</v>
       </c>
       <c r="P30" s="0" t="s">
-        <v>123</v>
+        <v>468</v>
       </c>
     </row>
     <row r="31">
@@ -2944,7 +3979,7 @@
         <v>1</v>
       </c>
       <c r="P31" s="0" t="s">
-        <v>124</v>
+        <v>469</v>
       </c>
     </row>
     <row r="32">
@@ -2994,7 +4029,7 @@
         <v>1</v>
       </c>
       <c r="P32" s="0" t="s">
-        <v>125</v>
+        <v>470</v>
       </c>
     </row>
     <row r="33">
@@ -3044,7 +4079,7 @@
         <v>0</v>
       </c>
       <c r="P33" s="0" t="s">
-        <v>126</v>
+        <v>471</v>
       </c>
     </row>
     <row r="34">
@@ -3094,7 +4129,7 @@
         <v>1</v>
       </c>
       <c r="P34" s="0" t="s">
-        <v>127</v>
+        <v>472</v>
       </c>
     </row>
     <row r="35">
@@ -3144,7 +4179,7 @@
         <v>1</v>
       </c>
       <c r="P35" s="0" t="s">
-        <v>128</v>
+        <v>473</v>
       </c>
     </row>
     <row r="36">
@@ -3176,10 +4211,10 @@
         <v>1</v>
       </c>
       <c r="J36" s="0">
-        <v>1579.9052222710552</v>
+        <v>1579.905222271055</v>
       </c>
       <c r="K36" s="0">
-        <v>0.98483067773479882</v>
+        <v>0.98483067773479893</v>
       </c>
       <c r="L36" s="0">
         <v>61</v>
@@ -3194,7 +4229,7 @@
         <v>1</v>
       </c>
       <c r="P36" s="0" t="s">
-        <v>129</v>
+        <v>474</v>
       </c>
     </row>
     <row r="37">
@@ -3244,7 +4279,7 @@
         <v>1</v>
       </c>
       <c r="P37" s="0" t="s">
-        <v>130</v>
+        <v>475</v>
       </c>
     </row>
     <row r="38">
@@ -3294,7 +4329,7 @@
         <v>1</v>
       </c>
       <c r="P38" s="0" t="s">
-        <v>131</v>
+        <v>476</v>
       </c>
     </row>
     <row r="39">
@@ -3326,7 +4361,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="0">
-        <v>1626.3766943661206</v>
+        <v>1626.3766943661203</v>
       </c>
       <c r="K39" s="0">
         <v>0.99590425748323641</v>
@@ -3344,7 +4379,7 @@
         <v>1</v>
       </c>
       <c r="P39" s="0" t="s">
-        <v>132</v>
+        <v>477</v>
       </c>
     </row>
     <row r="40">
@@ -3394,7 +4429,7 @@
         <v>1</v>
       </c>
       <c r="P40" s="0" t="s">
-        <v>133</v>
+        <v>478</v>
       </c>
     </row>
     <row r="41">
@@ -3426,7 +4461,7 @@
         <v>1</v>
       </c>
       <c r="J41" s="0">
-        <v>1773.8686804768158</v>
+        <v>1773.8686804768167</v>
       </c>
       <c r="K41" s="0">
         <v>0.99904095147569161</v>
@@ -3444,7 +4479,7 @@
         <v>1</v>
       </c>
       <c r="P41" s="0" t="s">
-        <v>134</v>
+        <v>479</v>
       </c>
     </row>
     <row r="42">
@@ -3494,7 +4529,7 @@
         <v>1</v>
       </c>
       <c r="P42" s="0" t="s">
-        <v>135</v>
+        <v>480</v>
       </c>
     </row>
     <row r="43">
@@ -3544,7 +4579,7 @@
         <v>1</v>
       </c>
       <c r="P43" s="0" t="s">
-        <v>136</v>
+        <v>481</v>
       </c>
     </row>
     <row r="44">
@@ -3594,7 +4629,7 @@
         <v>1</v>
       </c>
       <c r="P44" s="0" t="s">
-        <v>137</v>
+        <v>482</v>
       </c>
     </row>
     <row r="45">
@@ -3644,7 +4679,7 @@
         <v>1</v>
       </c>
       <c r="P45" s="0" t="s">
-        <v>138</v>
+        <v>483</v>
       </c>
     </row>
     <row r="46">
@@ -3676,7 +4711,7 @@
         <v>1</v>
       </c>
       <c r="J46" s="0">
-        <v>2547.0621177642893</v>
+        <v>2547.0621177642888</v>
       </c>
       <c r="K46" s="0">
         <v>0.98728757077028462</v>
@@ -3694,7 +4729,7 @@
         <v>1</v>
       </c>
       <c r="P46" s="0" t="s">
-        <v>139</v>
+        <v>484</v>
       </c>
     </row>
     <row r="47">
@@ -3726,10 +4761,10 @@
         <v>1</v>
       </c>
       <c r="J47" s="0">
-        <v>661.15277973713592</v>
+        <v>661.15277973713546</v>
       </c>
       <c r="K47" s="0">
-        <v>0.97719631778190896</v>
+        <v>0.97719631778190885</v>
       </c>
       <c r="L47" s="0">
         <v>10</v>
@@ -3744,7 +4779,7 @@
         <v>1</v>
       </c>
       <c r="P47" s="0" t="s">
-        <v>140</v>
+        <v>485</v>
       </c>
     </row>
     <row r="48">
@@ -3776,7 +4811,7 @@
         <v>1</v>
       </c>
       <c r="J48" s="0">
-        <v>410.11071230444912</v>
+        <v>410.11071230444918</v>
       </c>
       <c r="K48" s="0">
         <v>0.9970395924818376</v>
@@ -3794,7 +4829,7 @@
         <v>1</v>
       </c>
       <c r="P48" s="0" t="s">
-        <v>141</v>
+        <v>486</v>
       </c>
     </row>
     <row r="49">
@@ -3826,10 +4861,10 @@
         <v>1</v>
       </c>
       <c r="J49" s="0">
-        <v>0.18849107545006841</v>
+        <v>0.18849107545006819</v>
       </c>
       <c r="K49" s="0">
-        <v>0.35407534428075049</v>
+        <v>0.3540753442807506</v>
       </c>
       <c r="L49" s="0">
         <v>8</v>
@@ -3844,7 +4879,7 @@
         <v>0</v>
       </c>
       <c r="P49" s="0" t="s">
-        <v>142</v>
+        <v>487</v>
       </c>
     </row>
     <row r="50">
@@ -3894,7 +4929,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="0" t="s">
-        <v>143</v>
+        <v>488</v>
       </c>
     </row>
     <row r="51">
@@ -3944,7 +4979,7 @@
         <v>1</v>
       </c>
       <c r="P51" s="0" t="s">
-        <v>144</v>
+        <v>489</v>
       </c>
     </row>
     <row r="52">
@@ -3994,7 +5029,7 @@
         <v>1</v>
       </c>
       <c r="P52" s="0" t="s">
-        <v>145</v>
+        <v>490</v>
       </c>
     </row>
     <row r="53">
@@ -4044,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="P53" s="0" t="s">
-        <v>146</v>
+        <v>491</v>
       </c>
     </row>
     <row r="54">
@@ -4094,7 +5129,7 @@
         <v>1</v>
       </c>
       <c r="P54" s="0" t="s">
-        <v>147</v>
+        <v>492</v>
       </c>
     </row>
     <row r="55">
@@ -4126,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="J55" s="0">
-        <v>1221.4178403983819</v>
+        <v>1221.4178403983815</v>
       </c>
       <c r="K55" s="0">
         <v>0.98234377379553039</v>
@@ -4144,7 +5179,7 @@
         <v>1</v>
       </c>
       <c r="P55" s="0" t="s">
-        <v>148</v>
+        <v>493</v>
       </c>
     </row>
     <row r="56">
@@ -4176,7 +5211,7 @@
         <v>1</v>
       </c>
       <c r="J56" s="0">
-        <v>1221.7889918170797</v>
+        <v>1221.788991817079</v>
       </c>
       <c r="K56" s="0">
         <v>0.99687357789713227</v>
@@ -4194,7 +5229,7 @@
         <v>1</v>
       </c>
       <c r="P56" s="0" t="s">
-        <v>149</v>
+        <v>494</v>
       </c>
     </row>
     <row r="57">
@@ -4226,7 +5261,7 @@
         <v>1</v>
       </c>
       <c r="J57" s="0">
-        <v>1513.2397793772052</v>
+        <v>1513.2397793772054</v>
       </c>
       <c r="K57" s="0">
         <v>0.99808716542823806</v>
@@ -4244,7 +5279,7 @@
         <v>1</v>
       </c>
       <c r="P57" s="0" t="s">
-        <v>150</v>
+        <v>495</v>
       </c>
     </row>
     <row r="58">
@@ -4294,7 +5329,7 @@
         <v>1</v>
       </c>
       <c r="P58" s="0" t="s">
-        <v>151</v>
+        <v>496</v>
       </c>
     </row>
     <row r="59">
@@ -4344,7 +5379,7 @@
         <v>1</v>
       </c>
       <c r="P59" s="0" t="s">
-        <v>152</v>
+        <v>497</v>
       </c>
     </row>
     <row r="60">
@@ -4376,7 +5411,7 @@
         <v>1</v>
       </c>
       <c r="J60" s="0">
-        <v>1501.9149999033621</v>
+        <v>1501.9149999033616</v>
       </c>
       <c r="K60" s="0">
         <v>0.9937649828049917</v>
@@ -4394,7 +5429,7 @@
         <v>1</v>
       </c>
       <c r="P60" s="0" t="s">
-        <v>153</v>
+        <v>498</v>
       </c>
     </row>
     <row r="61">
@@ -4426,10 +5461,10 @@
         <v>1</v>
       </c>
       <c r="J61" s="0">
-        <v>214.00773709081108</v>
+        <v>214.00773709081099</v>
       </c>
       <c r="K61" s="0">
-        <v>0.77197748027409008</v>
+        <v>0.77197748027409019</v>
       </c>
       <c r="L61" s="0">
         <v>10</v>
@@ -4444,7 +5479,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="0" t="s">
-        <v>154</v>
+        <v>499</v>
       </c>
     </row>
     <row r="62">
@@ -4476,7 +5511,7 @@
         <v>1</v>
       </c>
       <c r="J62" s="0">
-        <v>1957.5180273677322</v>
+        <v>1957.5180273677331</v>
       </c>
       <c r="K62" s="0">
         <v>0.99272218047441951</v>
@@ -4494,7 +5529,7 @@
         <v>1</v>
       </c>
       <c r="P62" s="0" t="s">
-        <v>155</v>
+        <v>500</v>
       </c>
     </row>
     <row r="63">
@@ -4544,7 +5579,7 @@
         <v>1</v>
       </c>
       <c r="P63" s="0" t="s">
-        <v>156</v>
+        <v>501</v>
       </c>
     </row>
     <row r="64">
@@ -4594,7 +5629,7 @@
         <v>1</v>
       </c>
       <c r="P64" s="0" t="s">
-        <v>157</v>
+        <v>502</v>
       </c>
     </row>
     <row r="65">
@@ -4626,7 +5661,7 @@
         <v>1</v>
       </c>
       <c r="J65" s="0">
-        <v>965.24514797176607</v>
+        <v>965.24514797176596</v>
       </c>
       <c r="K65" s="0">
         <v>0.93672171151202366</v>
@@ -4644,7 +5679,7 @@
         <v>1</v>
       </c>
       <c r="P65" s="0" t="s">
-        <v>158</v>
+        <v>503</v>
       </c>
     </row>
     <row r="66">
@@ -4694,7 +5729,7 @@
         <v>1</v>
       </c>
       <c r="P66" s="0" t="s">
-        <v>159</v>
+        <v>504</v>
       </c>
     </row>
     <row r="67">
@@ -4726,7 +5761,7 @@
         <v>1</v>
       </c>
       <c r="J67" s="0">
-        <v>848.28858262813799</v>
+        <v>848.2885826281381</v>
       </c>
       <c r="K67" s="0">
         <v>0.99868044006558299</v>
@@ -4744,7 +5779,7 @@
         <v>1</v>
       </c>
       <c r="P67" s="0" t="s">
-        <v>160</v>
+        <v>505</v>
       </c>
     </row>
     <row r="68">
@@ -4794,7 +5829,7 @@
         <v>1</v>
       </c>
       <c r="P68" s="0" t="s">
-        <v>161</v>
+        <v>506</v>
       </c>
     </row>
     <row r="69">
@@ -4844,7 +5879,7 @@
         <v>1</v>
       </c>
       <c r="P69" s="0" t="s">
-        <v>162</v>
+        <v>507</v>
       </c>
     </row>
     <row r="70">
@@ -4894,7 +5929,7 @@
         <v>1</v>
       </c>
       <c r="P70" s="0" t="s">
-        <v>163</v>
+        <v>508</v>
       </c>
     </row>
     <row r="71">
@@ -4926,7 +5961,7 @@
         <v>1</v>
       </c>
       <c r="J71" s="0">
-        <v>2205.8138631608372</v>
+        <v>2205.8138631608363</v>
       </c>
       <c r="K71" s="0">
         <v>0.99856334426500071</v>
@@ -4944,7 +5979,7 @@
         <v>1</v>
       </c>
       <c r="P71" s="0" t="s">
-        <v>164</v>
+        <v>509</v>
       </c>
     </row>
     <row r="72">
@@ -4976,7 +6011,7 @@
         <v>1</v>
       </c>
       <c r="J72" s="0">
-        <v>2570.9266181484913</v>
+        <v>2570.92661814849</v>
       </c>
       <c r="K72" s="0">
         <v>0.9955328474633357</v>
@@ -4994,7 +6029,7 @@
         <v>1</v>
       </c>
       <c r="P72" s="0" t="s">
-        <v>165</v>
+        <v>510</v>
       </c>
     </row>
     <row r="73">
@@ -5026,7 +6061,7 @@
         <v>1</v>
       </c>
       <c r="J73" s="0">
-        <v>1532.77289006665</v>
+        <v>1532.7728900666498</v>
       </c>
       <c r="K73" s="0">
         <v>0.99585654454348238</v>
@@ -5044,7 +6079,7 @@
         <v>1</v>
       </c>
       <c r="P73" s="0" t="s">
-        <v>166</v>
+        <v>511</v>
       </c>
     </row>
     <row r="74">
@@ -5094,7 +6129,7 @@
         <v>1</v>
       </c>
       <c r="P74" s="0" t="s">
-        <v>167</v>
+        <v>512</v>
       </c>
     </row>
     <row r="75">
@@ -5126,7 +6161,7 @@
         <v>1</v>
       </c>
       <c r="J75" s="0">
-        <v>2096.176488720449</v>
+        <v>2096.1764887204499</v>
       </c>
       <c r="K75" s="0">
         <v>0.99898513717814475</v>
@@ -5144,7 +6179,7 @@
         <v>1</v>
       </c>
       <c r="P75" s="0" t="s">
-        <v>168</v>
+        <v>513</v>
       </c>
     </row>
     <row r="76">
@@ -5194,7 +6229,7 @@
         <v>1</v>
       </c>
       <c r="P76" s="0" t="s">
-        <v>169</v>
+        <v>514</v>
       </c>
     </row>
     <row r="77">
@@ -5244,7 +6279,7 @@
         <v>1</v>
       </c>
       <c r="P77" s="0" t="s">
-        <v>170</v>
+        <v>515</v>
       </c>
     </row>
     <row r="78">
@@ -5276,7 +6311,7 @@
         <v>1</v>
       </c>
       <c r="J78" s="0">
-        <v>1652.0346967697353</v>
+        <v>1652.0346967697349</v>
       </c>
       <c r="K78" s="0">
         <v>0.99647618341908739</v>
@@ -5294,7 +6329,7 @@
         <v>1</v>
       </c>
       <c r="P78" s="0" t="s">
-        <v>171</v>
+        <v>516</v>
       </c>
     </row>
     <row r="79">
@@ -5344,7 +6379,7 @@
         <v>1</v>
       </c>
       <c r="P79" s="0" t="s">
-        <v>172</v>
+        <v>517</v>
       </c>
     </row>
     <row r="80">
@@ -5394,7 +6429,7 @@
         <v>1</v>
       </c>
       <c r="P80" s="0" t="s">
-        <v>173</v>
+        <v>518</v>
       </c>
     </row>
     <row r="81">
@@ -5444,7 +6479,7 @@
         <v>1</v>
       </c>
       <c r="P81" s="0" t="s">
-        <v>174</v>
+        <v>519</v>
       </c>
     </row>
     <row r="82">
@@ -5494,7 +6529,7 @@
         <v>1</v>
       </c>
       <c r="P82" s="0" t="s">
-        <v>175</v>
+        <v>520</v>
       </c>
     </row>
     <row r="83">
@@ -5526,7 +6561,7 @@
         <v>1</v>
       </c>
       <c r="J83" s="0">
-        <v>1865.4262458669398</v>
+        <v>1865.4262458669396</v>
       </c>
       <c r="K83" s="0">
         <v>0.99891606336650685</v>
@@ -5544,7 +6579,7 @@
         <v>1</v>
       </c>
       <c r="P83" s="0" t="s">
-        <v>176</v>
+        <v>521</v>
       </c>
     </row>
     <row r="84">
@@ -5594,7 +6629,7 @@
         <v>1</v>
       </c>
       <c r="P84" s="0" t="s">
-        <v>177</v>
+        <v>522</v>
       </c>
     </row>
     <row r="85">
@@ -5626,7 +6661,7 @@
         <v>1</v>
       </c>
       <c r="J85" s="0">
-        <v>1886.2575892376642</v>
+        <v>1886.2575892376635</v>
       </c>
       <c r="K85" s="0">
         <v>0.99855474168079894</v>
@@ -5644,7 +6679,7 @@
         <v>1</v>
       </c>
       <c r="P85" s="0" t="s">
-        <v>178</v>
+        <v>523</v>
       </c>
     </row>
     <row r="86">
@@ -5694,7 +6729,7 @@
         <v>1</v>
       </c>
       <c r="P86" s="0" t="s">
-        <v>179</v>
+        <v>524</v>
       </c>
     </row>
     <row r="87">
@@ -5726,7 +6761,7 @@
         <v>1</v>
       </c>
       <c r="J87" s="0">
-        <v>2415.0999901258906</v>
+        <v>2415.0999901258897</v>
       </c>
       <c r="K87" s="0">
         <v>0.99813014732030969</v>
@@ -5744,7 +6779,7 @@
         <v>1</v>
       </c>
       <c r="P87" s="0" t="s">
-        <v>180</v>
+        <v>525</v>
       </c>
     </row>
     <row r="88">
@@ -5776,7 +6811,7 @@
         <v>1</v>
       </c>
       <c r="J88" s="0">
-        <v>2259.2010433261521</v>
+        <v>2259.2010433261526</v>
       </c>
       <c r="K88" s="0">
         <v>0.99728639202050262</v>
@@ -5794,7 +6829,7 @@
         <v>1</v>
       </c>
       <c r="P88" s="0" t="s">
-        <v>181</v>
+        <v>526</v>
       </c>
     </row>
     <row r="89">
@@ -5844,7 +6879,7 @@
         <v>1</v>
       </c>
       <c r="P89" s="0" t="s">
-        <v>182</v>
+        <v>527</v>
       </c>
     </row>
     <row r="90">
@@ -5876,7 +6911,7 @@
         <v>1</v>
       </c>
       <c r="J90" s="0">
-        <v>1913.6401189378073</v>
+        <v>1913.640118937808</v>
       </c>
       <c r="K90" s="0">
         <v>0.99464925416056194</v>
@@ -5894,7 +6929,7 @@
         <v>1</v>
       </c>
       <c r="P90" s="0" t="s">
-        <v>183</v>
+        <v>528</v>
       </c>
     </row>
     <row r="91">
@@ -5944,7 +6979,7 @@
         <v>1</v>
       </c>
       <c r="P91" s="0" t="s">
-        <v>184</v>
+        <v>529</v>
       </c>
     </row>
     <row r="92">
@@ -5976,7 +7011,7 @@
         <v>1</v>
       </c>
       <c r="J92" s="0">
-        <v>2162.0251268629399</v>
+        <v>2162.025126862939</v>
       </c>
       <c r="K92" s="0">
         <v>0.99752640066888976</v>
@@ -5994,7 +7029,7 @@
         <v>1</v>
       </c>
       <c r="P92" s="0" t="s">
-        <v>185</v>
+        <v>530</v>
       </c>
     </row>
     <row r="93">
@@ -6026,7 +7061,7 @@
         <v>1</v>
       </c>
       <c r="J93" s="0">
-        <v>1763.6262685179177</v>
+        <v>1763.6262685179174</v>
       </c>
       <c r="K93" s="0">
         <v>0.9987963878643974</v>
@@ -6044,7 +7079,7 @@
         <v>1</v>
       </c>
       <c r="P93" s="0" t="s">
-        <v>186</v>
+        <v>531</v>
       </c>
     </row>
     <row r="94">
@@ -6094,7 +7129,7 @@
         <v>1</v>
       </c>
       <c r="P94" s="0" t="s">
-        <v>187</v>
+        <v>532</v>
       </c>
     </row>
     <row r="95">
@@ -6144,7 +7179,7 @@
         <v>1</v>
       </c>
       <c r="P95" s="0" t="s">
-        <v>188</v>
+        <v>533</v>
       </c>
     </row>
     <row r="96">
@@ -6194,7 +7229,7 @@
         <v>1</v>
       </c>
       <c r="P96" s="0" t="s">
-        <v>189</v>
+        <v>534</v>
       </c>
     </row>
     <row r="97">
@@ -6244,7 +7279,7 @@
         <v>1</v>
       </c>
       <c r="P97" s="0" t="s">
-        <v>190</v>
+        <v>535</v>
       </c>
     </row>
     <row r="98">
@@ -6276,7 +7311,7 @@
         <v>1</v>
       </c>
       <c r="J98" s="0">
-        <v>1375.0681772061591</v>
+        <v>1375.0681772061589</v>
       </c>
       <c r="K98" s="0">
         <v>0.99863899384873867</v>
@@ -6294,7 +7329,7 @@
         <v>1</v>
       </c>
       <c r="P98" s="0" t="s">
-        <v>191</v>
+        <v>536</v>
       </c>
     </row>
     <row r="99">
@@ -6326,7 +7361,7 @@
         <v>1</v>
       </c>
       <c r="J99" s="0">
-        <v>2833.3640217794336</v>
+        <v>2833.3640217794332</v>
       </c>
       <c r="K99" s="0">
         <v>0.99610968578678283</v>
@@ -6344,7 +7379,7 @@
         <v>1</v>
       </c>
       <c r="P99" s="0" t="s">
-        <v>192</v>
+        <v>537</v>
       </c>
     </row>
     <row r="100">
@@ -6394,7 +7429,7 @@
         <v>1</v>
       </c>
       <c r="P100" s="0" t="s">
-        <v>193</v>
+        <v>538</v>
       </c>
     </row>
     <row r="101">
@@ -6426,7 +7461,7 @@
         <v>1</v>
       </c>
       <c r="J101" s="0">
-        <v>633.64562852100642</v>
+        <v>633.6456285210063</v>
       </c>
       <c r="K101" s="0">
         <v>0.99171960836137507</v>
@@ -6444,7 +7479,7 @@
         <v>1</v>
       </c>
       <c r="P101" s="0" t="s">
-        <v>194</v>
+        <v>539</v>
       </c>
     </row>
     <row r="102">
@@ -6494,7 +7529,7 @@
         <v>0</v>
       </c>
       <c r="P102" s="0" t="s">
-        <v>195</v>
+        <v>540</v>
       </c>
     </row>
     <row r="103">
@@ -6544,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="P103" s="0" t="s">
-        <v>196</v>
+        <v>541</v>
       </c>
     </row>
     <row r="104">
@@ -6576,7 +7611,7 @@
         <v>1</v>
       </c>
       <c r="J104" s="0">
-        <v>1229.6089370907914</v>
+        <v>1229.6089370907905</v>
       </c>
       <c r="K104" s="0">
         <v>0.99134266664328308</v>
@@ -6594,7 +7629,7 @@
         <v>1</v>
       </c>
       <c r="P104" s="0" t="s">
-        <v>197</v>
+        <v>542</v>
       </c>
     </row>
     <row r="105">
@@ -6626,7 +7661,7 @@
         <v>1</v>
       </c>
       <c r="J105" s="0">
-        <v>1910.12507526124</v>
+        <v>1910.1250752612396</v>
       </c>
       <c r="K105" s="0">
         <v>0.99808579308196443</v>
@@ -6644,7 +7679,7 @@
         <v>1</v>
       </c>
       <c r="P105" s="0" t="s">
-        <v>198</v>
+        <v>543</v>
       </c>
     </row>
     <row r="106">
@@ -6694,7 +7729,7 @@
         <v>0</v>
       </c>
       <c r="P106" s="0" t="s">
-        <v>199</v>
+        <v>544</v>
       </c>
     </row>
     <row r="107">
@@ -6726,7 +7761,7 @@
         <v>1</v>
       </c>
       <c r="J107" s="0">
-        <v>664.83588567874654</v>
+        <v>664.83588567874665</v>
       </c>
       <c r="K107" s="0">
         <v>0.99702641881935639</v>
@@ -6744,7 +7779,7 @@
         <v>1</v>
       </c>
       <c r="P107" s="0" t="s">
-        <v>200</v>
+        <v>545</v>
       </c>
     </row>
     <row r="108">
@@ -6776,7 +7811,7 @@
         <v>1</v>
       </c>
       <c r="J108" s="0">
-        <v>1938.4777163485373</v>
+        <v>1938.4777163485369</v>
       </c>
       <c r="K108" s="0">
         <v>0.99628352391200414</v>
@@ -6794,7 +7829,7 @@
         <v>1</v>
       </c>
       <c r="P108" s="0" t="s">
-        <v>201</v>
+        <v>546</v>
       </c>
     </row>
     <row r="109">
@@ -6844,7 +7879,7 @@
         <v>1</v>
       </c>
       <c r="P109" s="0" t="s">
-        <v>202</v>
+        <v>547</v>
       </c>
     </row>
     <row r="110">
@@ -6894,7 +7929,7 @@
         <v>1</v>
       </c>
       <c r="P110" s="0" t="s">
-        <v>203</v>
+        <v>548</v>
       </c>
     </row>
     <row r="111">
@@ -6926,7 +7961,7 @@
         <v>1</v>
       </c>
       <c r="J111" s="0">
-        <v>793.91322499029854</v>
+        <v>793.91322499029809</v>
       </c>
       <c r="K111" s="0">
         <v>0.98874043350771046</v>
@@ -6944,7 +7979,7 @@
         <v>1</v>
       </c>
       <c r="P111" s="0" t="s">
-        <v>204</v>
+        <v>549</v>
       </c>
     </row>
     <row r="112">
@@ -6994,7 +8029,7 @@
         <v>1</v>
       </c>
       <c r="P112" s="0" t="s">
-        <v>205</v>
+        <v>550</v>
       </c>
     </row>
     <row r="113">
@@ -7044,7 +8079,7 @@
         <v>1</v>
       </c>
       <c r="P113" s="0" t="s">
-        <v>206</v>
+        <v>551</v>
       </c>
     </row>
     <row r="114">
@@ -7094,7 +8129,7 @@
         <v>1</v>
       </c>
       <c r="P114" s="0" t="s">
-        <v>207</v>
+        <v>552</v>
       </c>
     </row>
     <row r="115">
@@ -7126,7 +8161,7 @@
         <v>1</v>
       </c>
       <c r="J115" s="0">
-        <v>409.65343465817801</v>
+        <v>409.65343465817807</v>
       </c>
       <c r="K115" s="0">
         <v>0.89114697267021703</v>
@@ -7144,7 +8179,7 @@
         <v>0</v>
       </c>
       <c r="P115" s="0" t="s">
-        <v>208</v>
+        <v>553</v>
       </c>
     </row>
     <row r="116">
@@ -7176,7 +8211,7 @@
         <v>1</v>
       </c>
       <c r="J116" s="0">
-        <v>1369.3777090845317</v>
+        <v>1369.377709084532</v>
       </c>
       <c r="K116" s="0">
         <v>0.96852539418740868</v>
@@ -7194,7 +8229,7 @@
         <v>1</v>
       </c>
       <c r="P116" s="0" t="s">
-        <v>209</v>
+        <v>554</v>
       </c>
     </row>
     <row r="117">
@@ -7244,7 +8279,7 @@
         <v>1</v>
       </c>
       <c r="P117" s="0" t="s">
-        <v>210</v>
+        <v>555</v>
       </c>
     </row>
     <row r="118">
@@ -7276,7 +8311,7 @@
         <v>1</v>
       </c>
       <c r="J118" s="0">
-        <v>1258.2883952862558</v>
+        <v>1258.288395286256</v>
       </c>
       <c r="K118" s="0">
         <v>0.98999036685482322</v>
@@ -7294,7 +8329,7 @@
         <v>1</v>
       </c>
       <c r="P118" s="0" t="s">
-        <v>211</v>
+        <v>556</v>
       </c>
     </row>
     <row r="119">
@@ -7344,7 +8379,7 @@
         <v>1</v>
       </c>
       <c r="P119" s="0" t="s">
-        <v>212</v>
+        <v>557</v>
       </c>
     </row>
     <row r="120">
@@ -7376,7 +8411,7 @@
         <v>1</v>
       </c>
       <c r="J120" s="0">
-        <v>926.95175513804259</v>
+        <v>926.95175513804236</v>
       </c>
       <c r="K120" s="0">
         <v>0.97991806331277287</v>
@@ -7394,7 +8429,7 @@
         <v>1</v>
       </c>
       <c r="P120" s="0" t="s">
-        <v>213</v>
+        <v>558</v>
       </c>
     </row>
     <row r="121">
@@ -7444,7 +8479,7 @@
         <v>1</v>
       </c>
       <c r="P121" s="0" t="s">
-        <v>214</v>
+        <v>559</v>
       </c>
     </row>
     <row r="122">
@@ -7494,7 +8529,7 @@
         <v>1</v>
       </c>
       <c r="P122" s="0" t="s">
-        <v>215</v>
+        <v>560</v>
       </c>
     </row>
     <row r="123">
@@ -7544,7 +8579,7 @@
         <v>1</v>
       </c>
       <c r="P123" s="0" t="s">
-        <v>216</v>
+        <v>561</v>
       </c>
     </row>
     <row r="124">
@@ -7594,7 +8629,7 @@
         <v>1</v>
       </c>
       <c r="P124" s="0" t="s">
-        <v>217</v>
+        <v>562</v>
       </c>
     </row>
     <row r="125">
@@ -7644,7 +8679,7 @@
         <v>1</v>
       </c>
       <c r="P125" s="0" t="s">
-        <v>218</v>
+        <v>563</v>
       </c>
     </row>
     <row r="126">
@@ -7676,7 +8711,7 @@
         <v>1</v>
       </c>
       <c r="J126" s="0">
-        <v>1786.6511653536056</v>
+        <v>1786.6511653536054</v>
       </c>
       <c r="K126" s="0">
         <v>0.98558158596822099</v>
@@ -7694,7 +8729,7 @@
         <v>1</v>
       </c>
       <c r="P126" s="0" t="s">
-        <v>219</v>
+        <v>564</v>
       </c>
     </row>
     <row r="127">
@@ -7726,7 +8761,7 @@
         <v>1</v>
       </c>
       <c r="J127" s="0">
-        <v>1639.3717147377795</v>
+        <v>1639.3717147377788</v>
       </c>
       <c r="K127" s="0">
         <v>0.99955157487274549</v>
@@ -7744,7 +8779,7 @@
         <v>1</v>
       </c>
       <c r="P127" s="0" t="s">
-        <v>220</v>
+        <v>565</v>
       </c>
     </row>
     <row r="128">
@@ -7794,7 +8829,7 @@
         <v>1</v>
       </c>
       <c r="P128" s="0" t="s">
-        <v>221</v>
+        <v>566</v>
       </c>
     </row>
     <row r="129">
@@ -7826,7 +8861,7 @@
         <v>1</v>
       </c>
       <c r="J129" s="0">
-        <v>2623.734741902274</v>
+        <v>2623.7347419022735</v>
       </c>
       <c r="K129" s="0">
         <v>0.9944157937375373</v>
@@ -7844,7 +8879,7 @@
         <v>1</v>
       </c>
       <c r="P129" s="0" t="s">
-        <v>222</v>
+        <v>567</v>
       </c>
     </row>
     <row r="130">
@@ -7876,7 +8911,7 @@
         <v>1</v>
       </c>
       <c r="J130" s="0">
-        <v>1360.8128554388545</v>
+        <v>1360.8128554388543</v>
       </c>
       <c r="K130" s="0">
         <v>0.99110679854132122</v>
@@ -7894,7 +8929,7 @@
         <v>1</v>
       </c>
       <c r="P130" s="0" t="s">
-        <v>223</v>
+        <v>568</v>
       </c>
     </row>
     <row r="131">
@@ -7944,7 +8979,7 @@
         <v>1</v>
       </c>
       <c r="P131" s="0" t="s">
-        <v>224</v>
+        <v>569</v>
       </c>
     </row>
     <row r="132">
@@ -7994,7 +9029,7 @@
         <v>1</v>
       </c>
       <c r="P132" s="0" t="s">
-        <v>225</v>
+        <v>570</v>
       </c>
     </row>
     <row r="133">
@@ -8044,7 +9079,7 @@
         <v>1</v>
       </c>
       <c r="P133" s="0" t="s">
-        <v>226</v>
+        <v>571</v>
       </c>
     </row>
     <row r="134">
@@ -8079,7 +9114,7 @@
         <v>1597.8522936150403</v>
       </c>
       <c r="K134" s="0">
-        <v>0.991332106869937</v>
+        <v>0.99133210686993689</v>
       </c>
       <c r="L134" s="0">
         <v>59</v>
@@ -8094,7 +9129,7 @@
         <v>1</v>
       </c>
       <c r="P134" s="0" t="s">
-        <v>227</v>
+        <v>572</v>
       </c>
     </row>
     <row r="135">
@@ -8144,7 +9179,7 @@
         <v>1</v>
       </c>
       <c r="P135" s="0" t="s">
-        <v>228</v>
+        <v>573</v>
       </c>
     </row>
     <row r="136">
@@ -8194,7 +9229,7 @@
         <v>1</v>
       </c>
       <c r="P136" s="0" t="s">
-        <v>229</v>
+        <v>574</v>
       </c>
     </row>
     <row r="137">
@@ -8226,7 +9261,7 @@
         <v>1</v>
       </c>
       <c r="J137" s="0">
-        <v>1710.9126759468113</v>
+        <v>1710.9126759468109</v>
       </c>
       <c r="K137" s="0">
         <v>0.99940800704431654</v>
@@ -8244,7 +9279,7 @@
         <v>1</v>
       </c>
       <c r="P137" s="0" t="s">
-        <v>230</v>
+        <v>575</v>
       </c>
     </row>
     <row r="138">
@@ -8294,7 +9329,7 @@
         <v>1</v>
       </c>
       <c r="P138" s="0" t="s">
-        <v>231</v>
+        <v>576</v>
       </c>
     </row>
     <row r="139">
@@ -8344,7 +9379,7 @@
         <v>1</v>
       </c>
       <c r="P139" s="0" t="s">
-        <v>232</v>
+        <v>577</v>
       </c>
     </row>
     <row r="140">
@@ -8376,7 +9411,7 @@
         <v>1</v>
       </c>
       <c r="J140" s="0">
-        <v>1478.7946090480507</v>
+        <v>1478.7946090480509</v>
       </c>
       <c r="K140" s="0">
         <v>0.99616361326427849</v>
@@ -8394,7 +9429,7 @@
         <v>1</v>
       </c>
       <c r="P140" s="0" t="s">
-        <v>233</v>
+        <v>578</v>
       </c>
     </row>
     <row r="141">
@@ -8444,7 +9479,7 @@
         <v>1</v>
       </c>
       <c r="P141" s="0" t="s">
-        <v>234</v>
+        <v>579</v>
       </c>
     </row>
     <row r="142">
@@ -8494,7 +9529,7 @@
         <v>1</v>
       </c>
       <c r="P142" s="0" t="s">
-        <v>235</v>
+        <v>580</v>
       </c>
     </row>
     <row r="143">
@@ -8544,7 +9579,7 @@
         <v>1</v>
       </c>
       <c r="P143" s="0" t="s">
-        <v>236</v>
+        <v>581</v>
       </c>
     </row>
     <row r="144">
@@ -8576,7 +9611,7 @@
         <v>1</v>
       </c>
       <c r="J144" s="0">
-        <v>1274.171945561724</v>
+        <v>1274.1719455617238</v>
       </c>
       <c r="K144" s="0">
         <v>0.9991382800326245</v>
@@ -8594,7 +9629,7 @@
         <v>1</v>
       </c>
       <c r="P144" s="0" t="s">
-        <v>237</v>
+        <v>582</v>
       </c>
     </row>
     <row r="145">
@@ -8626,7 +9661,7 @@
         <v>1</v>
       </c>
       <c r="J145" s="0">
-        <v>1900.0974708825636</v>
+        <v>1900.0974708825634</v>
       </c>
       <c r="K145" s="0">
         <v>0.99728616615662558</v>
@@ -8644,7 +9679,7 @@
         <v>1</v>
       </c>
       <c r="P145" s="0" t="s">
-        <v>238</v>
+        <v>583</v>
       </c>
     </row>
     <row r="146">
@@ -8694,7 +9729,7 @@
         <v>1</v>
       </c>
       <c r="P146" s="0" t="s">
-        <v>239</v>
+        <v>584</v>
       </c>
     </row>
     <row r="147">
@@ -8744,7 +9779,7 @@
         <v>1</v>
       </c>
       <c r="P147" s="0" t="s">
-        <v>240</v>
+        <v>585</v>
       </c>
     </row>
     <row r="148">
@@ -8776,7 +9811,7 @@
         <v>1</v>
       </c>
       <c r="J148" s="0">
-        <v>1121.5213782616102</v>
+        <v>1121.5213782616097</v>
       </c>
       <c r="K148" s="0">
         <v>0.99887580468185711</v>
@@ -8794,7 +9829,7 @@
         <v>1</v>
       </c>
       <c r="P148" s="0" t="s">
-        <v>241</v>
+        <v>586</v>
       </c>
     </row>
     <row r="149">
@@ -8844,7 +9879,7 @@
         <v>1</v>
       </c>
       <c r="P149" s="0" t="s">
-        <v>242</v>
+        <v>587</v>
       </c>
     </row>
     <row r="150">
@@ -8879,7 +9914,7 @@
         <v>1138.8487655225947</v>
       </c>
       <c r="K150" s="0">
-        <v>0.98903905155448857</v>
+        <v>0.98903905155448868</v>
       </c>
       <c r="L150" s="0">
         <v>8</v>
@@ -8894,7 +9929,7 @@
         <v>1</v>
       </c>
       <c r="P150" s="0" t="s">
-        <v>243</v>
+        <v>588</v>
       </c>
     </row>
     <row r="151">
@@ -8926,7 +9961,7 @@
         <v>1</v>
       </c>
       <c r="J151" s="0">
-        <v>1825.9679400029324</v>
+        <v>1825.9679400029329</v>
       </c>
       <c r="K151" s="0">
         <v>0.99594007129911144</v>
@@ -8944,7 +9979,7 @@
         <v>1</v>
       </c>
       <c r="P151" s="0" t="s">
-        <v>244</v>
+        <v>589</v>
       </c>
     </row>
     <row r="152">
@@ -8994,7 +10029,7 @@
         <v>1</v>
       </c>
       <c r="P152" s="0" t="s">
-        <v>245</v>
+        <v>590</v>
       </c>
     </row>
     <row r="153">
@@ -9044,7 +10079,7 @@
         <v>1</v>
       </c>
       <c r="P153" s="0" t="s">
-        <v>246</v>
+        <v>591</v>
       </c>
     </row>
     <row r="154">
@@ -9076,7 +10111,7 @@
         <v>1</v>
       </c>
       <c r="J154" s="0">
-        <v>1258.4838810786696</v>
+        <v>1258.4838810786698</v>
       </c>
       <c r="K154" s="0">
         <v>0.98430666834940672</v>
@@ -9094,7 +10129,7 @@
         <v>1</v>
       </c>
       <c r="P154" s="0" t="s">
-        <v>247</v>
+        <v>592</v>
       </c>
     </row>
     <row r="155">
@@ -9144,7 +10179,7 @@
         <v>1</v>
       </c>
       <c r="P155" s="0" t="s">
-        <v>248</v>
+        <v>593</v>
       </c>
     </row>
     <row r="156">
@@ -9194,7 +10229,7 @@
         <v>1</v>
       </c>
       <c r="P156" s="0" t="s">
-        <v>249</v>
+        <v>594</v>
       </c>
     </row>
     <row r="157">
@@ -9244,7 +10279,7 @@
         <v>1</v>
       </c>
       <c r="P157" s="0" t="s">
-        <v>250</v>
+        <v>595</v>
       </c>
     </row>
     <row r="158">
@@ -9294,7 +10329,7 @@
         <v>1</v>
       </c>
       <c r="P158" s="0" t="s">
-        <v>251</v>
+        <v>596</v>
       </c>
     </row>
     <row r="159">
@@ -9344,7 +10379,7 @@
         <v>1</v>
       </c>
       <c r="P159" s="0" t="s">
-        <v>252</v>
+        <v>597</v>
       </c>
     </row>
     <row r="160">
@@ -9394,7 +10429,7 @@
         <v>1</v>
       </c>
       <c r="P160" s="0" t="s">
-        <v>253</v>
+        <v>598</v>
       </c>
     </row>
     <row r="161">
@@ -9426,7 +10461,7 @@
         <v>1</v>
       </c>
       <c r="J161" s="0">
-        <v>2203.8311405343493</v>
+        <v>2203.8311405343502</v>
       </c>
       <c r="K161" s="0">
         <v>0.9965320898337009</v>
@@ -9444,7 +10479,7 @@
         <v>1</v>
       </c>
       <c r="P161" s="0" t="s">
-        <v>254</v>
+        <v>599</v>
       </c>
     </row>
     <row r="162">
@@ -9494,7 +10529,7 @@
         <v>1</v>
       </c>
       <c r="P162" s="0" t="s">
-        <v>255</v>
+        <v>600</v>
       </c>
     </row>
     <row r="163">
@@ -9526,7 +10561,7 @@
         <v>1</v>
       </c>
       <c r="J163" s="0">
-        <v>0.099320619344615946</v>
+        <v>0.09932061934461589</v>
       </c>
       <c r="K163" s="0">
         <v>0.020129591885226894</v>
@@ -9544,7 +10579,7 @@
         <v>0</v>
       </c>
       <c r="P163" s="0" t="s">
-        <v>256</v>
+        <v>601</v>
       </c>
     </row>
     <row r="164">
@@ -9594,7 +10629,7 @@
         <v>1</v>
       </c>
       <c r="P164" s="0" t="s">
-        <v>257</v>
+        <v>602</v>
       </c>
     </row>
     <row r="165">
@@ -9626,7 +10661,7 @@
         <v>1</v>
       </c>
       <c r="J165" s="0">
-        <v>1096.4725247574447</v>
+        <v>1096.4725247574445</v>
       </c>
       <c r="K165" s="0">
         <v>0.99012845718378428</v>
@@ -9644,7 +10679,7 @@
         <v>1</v>
       </c>
       <c r="P165" s="0" t="s">
-        <v>258</v>
+        <v>603</v>
       </c>
     </row>
     <row r="166">
@@ -9694,7 +10729,7 @@
         <v>1</v>
       </c>
       <c r="P166" s="0" t="s">
-        <v>259</v>
+        <v>604</v>
       </c>
     </row>
     <row r="167">
@@ -9744,7 +10779,7 @@
         <v>1</v>
       </c>
       <c r="P167" s="0" t="s">
-        <v>260</v>
+        <v>605</v>
       </c>
     </row>
     <row r="168">
@@ -9776,7 +10811,7 @@
         <v>1</v>
       </c>
       <c r="J168" s="0">
-        <v>1258.4838810786696</v>
+        <v>1258.4838810786698</v>
       </c>
       <c r="K168" s="0">
         <v>0.98430666834940672</v>
@@ -9794,7 +10829,7 @@
         <v>1</v>
       </c>
       <c r="P168" s="0" t="s">
-        <v>261</v>
+        <v>606</v>
       </c>
     </row>
     <row r="169">
@@ -9844,7 +10879,7 @@
         <v>1</v>
       </c>
       <c r="P169" s="0" t="s">
-        <v>262</v>
+        <v>607</v>
       </c>
     </row>
     <row r="170">
@@ -9894,7 +10929,7 @@
         <v>1</v>
       </c>
       <c r="P170" s="0" t="s">
-        <v>263</v>
+        <v>608</v>
       </c>
     </row>
     <row r="171">
@@ -9944,7 +10979,7 @@
         <v>1</v>
       </c>
       <c r="P171" s="0" t="s">
-        <v>264</v>
+        <v>609</v>
       </c>
     </row>
     <row r="172">
@@ -9994,7 +11029,7 @@
         <v>1</v>
       </c>
       <c r="P172" s="0" t="s">
-        <v>265</v>
+        <v>610</v>
       </c>
     </row>
     <row r="173">
@@ -10044,7 +11079,7 @@
         <v>1</v>
       </c>
       <c r="P173" s="0" t="s">
-        <v>266</v>
+        <v>611</v>
       </c>
     </row>
     <row r="174">
@@ -10094,7 +11129,7 @@
         <v>1</v>
       </c>
       <c r="P174" s="0" t="s">
-        <v>267</v>
+        <v>612</v>
       </c>
     </row>
     <row r="175">
@@ -10126,7 +11161,7 @@
         <v>1</v>
       </c>
       <c r="J175" s="0">
-        <v>2203.8311405343493</v>
+        <v>2203.8311405343502</v>
       </c>
       <c r="K175" s="0">
         <v>0.9965320898337009</v>
@@ -10144,7 +11179,7 @@
         <v>1</v>
       </c>
       <c r="P175" s="0" t="s">
-        <v>268</v>
+        <v>613</v>
       </c>
     </row>
     <row r="176">
@@ -10194,7 +11229,7 @@
         <v>1</v>
       </c>
       <c r="P176" s="0" t="s">
-        <v>269</v>
+        <v>614</v>
       </c>
     </row>
     <row r="177">
@@ -10226,7 +11261,7 @@
         <v>1</v>
       </c>
       <c r="J177" s="0">
-        <v>0.099320619344615946</v>
+        <v>0.09932061934461589</v>
       </c>
       <c r="K177" s="0">
         <v>0.020129591885226894</v>
@@ -10244,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="P177" s="0" t="s">
-        <v>270</v>
+        <v>615</v>
       </c>
     </row>
     <row r="178">
@@ -10294,7 +11329,7 @@
         <v>1</v>
       </c>
       <c r="P178" s="0" t="s">
-        <v>271</v>
+        <v>616</v>
       </c>
     </row>
     <row r="179">
@@ -10344,7 +11379,7 @@
         <v>1</v>
       </c>
       <c r="P179" s="0" t="s">
-        <v>272</v>
+        <v>617</v>
       </c>
     </row>
     <row r="180">
@@ -10394,7 +11429,7 @@
         <v>1</v>
       </c>
       <c r="P180" s="0" t="s">
-        <v>273</v>
+        <v>618</v>
       </c>
     </row>
     <row r="181">
@@ -10426,7 +11461,7 @@
         <v>1</v>
       </c>
       <c r="J181" s="0">
-        <v>1056.3808174752112</v>
+        <v>1056.3808174752107</v>
       </c>
       <c r="K181" s="0">
         <v>0.94283269905406642</v>
@@ -10444,7 +11479,7 @@
         <v>1</v>
       </c>
       <c r="P181" s="0" t="s">
-        <v>274</v>
+        <v>619</v>
       </c>
     </row>
     <row r="182">
@@ -10494,7 +11529,7 @@
         <v>1</v>
       </c>
       <c r="P182" s="0" t="s">
-        <v>275</v>
+        <v>620</v>
       </c>
     </row>
     <row r="183">
@@ -10526,7 +11561,7 @@
         <v>1</v>
       </c>
       <c r="J183" s="0">
-        <v>1845.4900300889026</v>
+        <v>1845.4900300889033</v>
       </c>
       <c r="K183" s="0">
         <v>0.99472905346913398</v>
@@ -10544,7 +11579,7 @@
         <v>1</v>
       </c>
       <c r="P183" s="0" t="s">
-        <v>276</v>
+        <v>621</v>
       </c>
     </row>
     <row r="184">
@@ -10576,7 +11611,7 @@
         <v>1</v>
       </c>
       <c r="J184" s="0">
-        <v>2440.3213240975706</v>
+        <v>2440.3213240975715</v>
       </c>
       <c r="K184" s="0">
         <v>0.99730254767897886</v>
@@ -10594,7 +11629,7 @@
         <v>1</v>
       </c>
       <c r="P184" s="0" t="s">
-        <v>277</v>
+        <v>622</v>
       </c>
     </row>
     <row r="185">
@@ -10644,7 +11679,7 @@
         <v>1</v>
       </c>
       <c r="P185" s="0" t="s">
-        <v>278</v>
+        <v>623</v>
       </c>
     </row>
     <row r="186">
@@ -10694,7 +11729,7 @@
         <v>1</v>
       </c>
       <c r="P186" s="0" t="s">
-        <v>279</v>
+        <v>624</v>
       </c>
     </row>
     <row r="187">
@@ -10726,7 +11761,7 @@
         <v>1</v>
       </c>
       <c r="J187" s="0">
-        <v>1957.1803218846953</v>
+        <v>1957.1803218846944</v>
       </c>
       <c r="K187" s="0">
         <v>0.99710136630858937</v>
@@ -10744,7 +11779,7 @@
         <v>1</v>
       </c>
       <c r="P187" s="0" t="s">
-        <v>280</v>
+        <v>625</v>
       </c>
     </row>
     <row r="188">
@@ -10776,7 +11811,7 @@
         <v>1</v>
       </c>
       <c r="J188" s="0">
-        <v>2100.6071929166155</v>
+        <v>2100.607192916616</v>
       </c>
       <c r="K188" s="0">
         <v>0.99678014918195579</v>
@@ -10794,7 +11829,7 @@
         <v>1</v>
       </c>
       <c r="P188" s="0" t="s">
-        <v>281</v>
+        <v>626</v>
       </c>
     </row>
     <row r="189">
@@ -10844,7 +11879,7 @@
         <v>1</v>
       </c>
       <c r="P189" s="0" t="s">
-        <v>282</v>
+        <v>627</v>
       </c>
     </row>
     <row r="190">
@@ -10894,7 +11929,7 @@
         <v>1</v>
       </c>
       <c r="P190" s="0" t="s">
-        <v>283</v>
+        <v>628</v>
       </c>
     </row>
     <row r="191">
@@ -10944,7 +11979,7 @@
         <v>1</v>
       </c>
       <c r="P191" s="0" t="s">
-        <v>284</v>
+        <v>629</v>
       </c>
     </row>
     <row r="192">
@@ -10979,7 +12014,7 @@
         <v>1616.1367703976414</v>
       </c>
       <c r="K192" s="0">
-        <v>0.97152799656703037</v>
+        <v>0.97152799656703048</v>
       </c>
       <c r="L192" s="0">
         <v>68</v>
@@ -10994,7 +12029,7 @@
         <v>1</v>
       </c>
       <c r="P192" s="0" t="s">
-        <v>285</v>
+        <v>630</v>
       </c>
     </row>
     <row r="193">
@@ -11026,7 +12061,7 @@
         <v>1</v>
       </c>
       <c r="J193" s="0">
-        <v>1056.3808174752112</v>
+        <v>1056.3808174752107</v>
       </c>
       <c r="K193" s="0">
         <v>0.94283269905406642</v>
@@ -11044,7 +12079,7 @@
         <v>1</v>
       </c>
       <c r="P193" s="0" t="s">
-        <v>286</v>
+        <v>631</v>
       </c>
     </row>
     <row r="194">
@@ -11094,7 +12129,7 @@
         <v>1</v>
       </c>
       <c r="P194" s="0" t="s">
-        <v>287</v>
+        <v>632</v>
       </c>
     </row>
     <row r="195">
@@ -11126,7 +12161,7 @@
         <v>1</v>
       </c>
       <c r="J195" s="0">
-        <v>2440.3213240975706</v>
+        <v>2440.3213240975715</v>
       </c>
       <c r="K195" s="0">
         <v>0.99730254767897886</v>
@@ -11144,7 +12179,7 @@
         <v>1</v>
       </c>
       <c r="P195" s="0" t="s">
-        <v>288</v>
+        <v>633</v>
       </c>
     </row>
     <row r="196">
@@ -11194,7 +12229,7 @@
         <v>1</v>
       </c>
       <c r="P196" s="0" t="s">
-        <v>289</v>
+        <v>634</v>
       </c>
     </row>
     <row r="197">
@@ -11244,7 +12279,7 @@
         <v>1</v>
       </c>
       <c r="P197" s="0" t="s">
-        <v>290</v>
+        <v>635</v>
       </c>
     </row>
     <row r="198">
@@ -11276,7 +12311,7 @@
         <v>1</v>
       </c>
       <c r="J198" s="0">
-        <v>1957.1803218846953</v>
+        <v>1957.1803218846944</v>
       </c>
       <c r="K198" s="0">
         <v>0.99710136630858937</v>
@@ -11294,7 +12329,7 @@
         <v>1</v>
       </c>
       <c r="P198" s="0" t="s">
-        <v>291</v>
+        <v>636</v>
       </c>
     </row>
     <row r="199">
@@ -11326,7 +12361,7 @@
         <v>1</v>
       </c>
       <c r="J199" s="0">
-        <v>2335.8882071409444</v>
+        <v>2335.8882071409457</v>
       </c>
       <c r="K199" s="0">
         <v>0.99474605101124125</v>
@@ -11344,7 +12379,7 @@
         <v>1</v>
       </c>
       <c r="P199" s="0" t="s">
-        <v>292</v>
+        <v>637</v>
       </c>
     </row>
     <row r="200">
@@ -11376,7 +12411,7 @@
         <v>1</v>
       </c>
       <c r="J200" s="0">
-        <v>2100.6071929166155</v>
+        <v>2100.607192916616</v>
       </c>
       <c r="K200" s="0">
         <v>0.99678014918195579</v>
@@ -11394,7 +12429,7 @@
         <v>1</v>
       </c>
       <c r="P200" s="0" t="s">
-        <v>293</v>
+        <v>638</v>
       </c>
     </row>
     <row r="201">
@@ -11429,7 +12464,7 @@
         <v>1297.3670999915848</v>
       </c>
       <c r="K201" s="0">
-        <v>0.98822650020533376</v>
+        <v>0.98822650020533387</v>
       </c>
       <c r="L201" s="0">
         <v>50</v>
@@ -11444,7 +12479,7 @@
         <v>1</v>
       </c>
       <c r="P201" s="0" t="s">
-        <v>294</v>
+        <v>639</v>
       </c>
     </row>
     <row r="202">
@@ -11494,7 +12529,7 @@
         <v>1</v>
       </c>
       <c r="P202" s="0" t="s">
-        <v>295</v>
+        <v>640</v>
       </c>
     </row>
     <row r="203">
@@ -11544,7 +12579,7 @@
         <v>1</v>
       </c>
       <c r="P203" s="0" t="s">
-        <v>296</v>
+        <v>641</v>
       </c>
     </row>
     <row r="204">
@@ -11576,7 +12611,7 @@
         <v>1</v>
       </c>
       <c r="J204" s="0">
-        <v>1599.6399572794105</v>
+        <v>1599.6399572794114</v>
       </c>
       <c r="K204" s="0">
         <v>0.99901196054217112</v>
@@ -11594,7 +12629,7 @@
         <v>1</v>
       </c>
       <c r="P204" s="0" t="s">
-        <v>297</v>
+        <v>642</v>
       </c>
     </row>
     <row r="205">
@@ -11644,7 +12679,7 @@
         <v>0</v>
       </c>
       <c r="P205" s="0" t="s">
-        <v>298</v>
+        <v>643</v>
       </c>
     </row>
     <row r="206">
@@ -11694,7 +12729,7 @@
         <v>1</v>
       </c>
       <c r="P206" s="0" t="s">
-        <v>299</v>
+        <v>644</v>
       </c>
     </row>
     <row r="207">
@@ -11726,7 +12761,7 @@
         <v>1</v>
       </c>
       <c r="J207" s="0">
-        <v>2396.349660329468</v>
+        <v>2396.3496603294684</v>
       </c>
       <c r="K207" s="0">
         <v>0.99886183274992047</v>
@@ -11744,7 +12779,7 @@
         <v>1</v>
       </c>
       <c r="P207" s="0" t="s">
-        <v>300</v>
+        <v>645</v>
       </c>
     </row>
     <row r="208">
@@ -11776,7 +12811,7 @@
         <v>1</v>
       </c>
       <c r="J208" s="0">
-        <v>1691.1787902311646</v>
+        <v>1691.1787902311642</v>
       </c>
       <c r="K208" s="0">
         <v>0.99903116195667208</v>
@@ -11794,7 +12829,7 @@
         <v>1</v>
       </c>
       <c r="P208" s="0" t="s">
-        <v>301</v>
+        <v>646</v>
       </c>
     </row>
     <row r="209">
@@ -11826,7 +12861,7 @@
         <v>1</v>
       </c>
       <c r="J209" s="0">
-        <v>1227.7760254013131</v>
+        <v>1227.7760254013128</v>
       </c>
       <c r="K209" s="0">
         <v>0.99646754195860721</v>
@@ -11844,7 +12879,7 @@
         <v>1</v>
       </c>
       <c r="P209" s="0" t="s">
-        <v>302</v>
+        <v>647</v>
       </c>
     </row>
     <row r="210">
@@ -11894,7 +12929,7 @@
         <v>1</v>
       </c>
       <c r="P210" s="0" t="s">
-        <v>303</v>
+        <v>648</v>
       </c>
     </row>
     <row r="211">
@@ -11926,7 +12961,7 @@
         <v>1</v>
       </c>
       <c r="J211" s="0">
-        <v>2555.8481455882634</v>
+        <v>2555.8481455882638</v>
       </c>
       <c r="K211" s="0">
         <v>0.99755119035843598</v>
@@ -11944,7 +12979,7 @@
         <v>1</v>
       </c>
       <c r="P211" s="0" t="s">
-        <v>304</v>
+        <v>649</v>
       </c>
     </row>
     <row r="212">
@@ -11976,7 +13011,7 @@
         <v>1</v>
       </c>
       <c r="J212" s="0">
-        <v>1581.0258855824488</v>
+        <v>1581.0258855824493</v>
       </c>
       <c r="K212" s="0">
         <v>0.98885888391854771</v>
@@ -11994,7 +13029,7 @@
         <v>1</v>
       </c>
       <c r="P212" s="0" t="s">
-        <v>305</v>
+        <v>650</v>
       </c>
     </row>
     <row r="213">
@@ -12026,10 +13061,10 @@
         <v>1</v>
       </c>
       <c r="J213" s="0">
-        <v>671.60786031937676</v>
+        <v>671.60786031937664</v>
       </c>
       <c r="K213" s="0">
-        <v>0.92369673766876226</v>
+        <v>0.92369673766876237</v>
       </c>
       <c r="L213" s="0">
         <v>9</v>
@@ -12044,7 +13079,7 @@
         <v>1</v>
       </c>
       <c r="P213" s="0" t="s">
-        <v>306</v>
+        <v>651</v>
       </c>
     </row>
     <row r="214">
@@ -12076,7 +13111,7 @@
         <v>1</v>
       </c>
       <c r="J214" s="0">
-        <v>1613.7008931305202</v>
+        <v>1613.7008931305206</v>
       </c>
       <c r="K214" s="0">
         <v>0.99901196054217112</v>
@@ -12094,7 +13129,7 @@
         <v>1</v>
       </c>
       <c r="P214" s="0" t="s">
-        <v>307</v>
+        <v>652</v>
       </c>
     </row>
     <row r="215">
@@ -12126,7 +13161,7 @@
         <v>1</v>
       </c>
       <c r="J215" s="0">
-        <v>0.071295859169552167</v>
+        <v>0.071295859169552195</v>
       </c>
       <c r="K215" s="0">
         <v>0.037906748812158497</v>
@@ -12144,7 +13179,7 @@
         <v>0</v>
       </c>
       <c r="P215" s="0" t="s">
-        <v>308</v>
+        <v>653</v>
       </c>
     </row>
     <row r="216">
@@ -12176,7 +13211,7 @@
         <v>1</v>
       </c>
       <c r="J216" s="0">
-        <v>687.04184450431717</v>
+        <v>687.0418445043174</v>
       </c>
       <c r="K216" s="0">
         <v>0.98797397859549474</v>
@@ -12194,7 +13229,7 @@
         <v>1</v>
       </c>
       <c r="P216" s="0" t="s">
-        <v>309</v>
+        <v>654</v>
       </c>
     </row>
     <row r="217">
@@ -12244,7 +13279,7 @@
         <v>1</v>
       </c>
       <c r="P217" s="0" t="s">
-        <v>310</v>
+        <v>655</v>
       </c>
     </row>
     <row r="218">
@@ -12294,7 +13329,7 @@
         <v>0</v>
       </c>
       <c r="P218" s="0" t="s">
-        <v>311</v>
+        <v>656</v>
       </c>
     </row>
     <row r="219">
@@ -12344,7 +13379,7 @@
         <v>1</v>
       </c>
       <c r="P219" s="0" t="s">
-        <v>312</v>
+        <v>657</v>
       </c>
     </row>
     <row r="220">
@@ -12376,7 +13411,7 @@
         <v>1</v>
       </c>
       <c r="J220" s="0">
-        <v>2396.349660329468</v>
+        <v>2396.3496603294684</v>
       </c>
       <c r="K220" s="0">
         <v>0.99886183274992047</v>
@@ -12394,7 +13429,7 @@
         <v>1</v>
       </c>
       <c r="P220" s="0" t="s">
-        <v>313</v>
+        <v>658</v>
       </c>
     </row>
     <row r="221">
@@ -12426,7 +13461,7 @@
         <v>1</v>
       </c>
       <c r="J221" s="0">
-        <v>1691.1787902311646</v>
+        <v>1691.1787902311642</v>
       </c>
       <c r="K221" s="0">
         <v>0.99903116195667208</v>
@@ -12444,7 +13479,7 @@
         <v>1</v>
       </c>
       <c r="P221" s="0" t="s">
-        <v>314</v>
+        <v>659</v>
       </c>
     </row>
     <row r="222">
@@ -12476,7 +13511,7 @@
         <v>1</v>
       </c>
       <c r="J222" s="0">
-        <v>1227.7760254013131</v>
+        <v>1227.7760254013128</v>
       </c>
       <c r="K222" s="0">
         <v>0.99646754195860721</v>
@@ -12494,7 +13529,7 @@
         <v>1</v>
       </c>
       <c r="P222" s="0" t="s">
-        <v>315</v>
+        <v>660</v>
       </c>
     </row>
     <row r="223">
@@ -12544,7 +13579,7 @@
         <v>1</v>
       </c>
       <c r="P223" s="0" t="s">
-        <v>316</v>
+        <v>661</v>
       </c>
     </row>
     <row r="224">
@@ -12576,7 +13611,7 @@
         <v>1</v>
       </c>
       <c r="J224" s="0">
-        <v>2555.8481455882634</v>
+        <v>2555.8481455882638</v>
       </c>
       <c r="K224" s="0">
         <v>0.99755119035843598</v>
@@ -12594,7 +13629,7 @@
         <v>1</v>
       </c>
       <c r="P224" s="0" t="s">
-        <v>317</v>
+        <v>662</v>
       </c>
     </row>
     <row r="225">
@@ -12626,7 +13661,7 @@
         <v>1</v>
       </c>
       <c r="J225" s="0">
-        <v>1581.0258855824488</v>
+        <v>1581.0258855824493</v>
       </c>
       <c r="K225" s="0">
         <v>0.98885888391854771</v>
@@ -12644,7 +13679,7 @@
         <v>1</v>
       </c>
       <c r="P225" s="0" t="s">
-        <v>318</v>
+        <v>663</v>
       </c>
     </row>
     <row r="226">
@@ -12676,10 +13711,10 @@
         <v>1</v>
       </c>
       <c r="J226" s="0">
-        <v>671.60786031937676</v>
+        <v>671.60786031937664</v>
       </c>
       <c r="K226" s="0">
-        <v>0.92369673766876226</v>
+        <v>0.92369673766876237</v>
       </c>
       <c r="L226" s="0">
         <v>9</v>
@@ -12694,7 +13729,7 @@
         <v>1</v>
       </c>
       <c r="P226" s="0" t="s">
-        <v>319</v>
+        <v>664</v>
       </c>
     </row>
     <row r="227">
@@ -12726,7 +13761,7 @@
         <v>1</v>
       </c>
       <c r="J227" s="0">
-        <v>1613.7008931305202</v>
+        <v>1613.7008931305206</v>
       </c>
       <c r="K227" s="0">
         <v>0.99901196054217112</v>
@@ -12744,7 +13779,7 @@
         <v>1</v>
       </c>
       <c r="P227" s="0" t="s">
-        <v>320</v>
+        <v>665</v>
       </c>
     </row>
     <row r="228">
@@ -12790,7 +13825,7 @@
         <v>0</v>
       </c>
       <c r="P228" s="0" t="s">
-        <v>321</v>
+        <v>666</v>
       </c>
     </row>
     <row r="229">
@@ -12822,7 +13857,7 @@
         <v>1</v>
       </c>
       <c r="J229" s="0">
-        <v>687.04184450431717</v>
+        <v>687.0418445043174</v>
       </c>
       <c r="K229" s="0">
         <v>0.98797397859549474</v>
@@ -12840,7 +13875,7 @@
         <v>1</v>
       </c>
       <c r="P229" s="0" t="s">
-        <v>322</v>
+        <v>667</v>
       </c>
     </row>
     <row r="230">
@@ -12890,7 +13925,7 @@
         <v>1</v>
       </c>
       <c r="P230" s="0" t="s">
-        <v>323</v>
+        <v>668</v>
       </c>
     </row>
     <row r="231">
@@ -12922,7 +13957,7 @@
         <v>1</v>
       </c>
       <c r="J231" s="0">
-        <v>2449.1530928682232</v>
+        <v>2449.1530928682228</v>
       </c>
       <c r="K231" s="0">
         <v>0.99623844745019052</v>
@@ -12940,7 +13975,7 @@
         <v>1</v>
       </c>
       <c r="P231" s="0" t="s">
-        <v>324</v>
+        <v>669</v>
       </c>
     </row>
     <row r="232">
@@ -12990,7 +14025,7 @@
         <v>1</v>
       </c>
       <c r="P232" s="0" t="s">
-        <v>325</v>
+        <v>670</v>
       </c>
     </row>
     <row r="233">
@@ -13040,7 +14075,7 @@
         <v>1</v>
       </c>
       <c r="P233" s="0" t="s">
-        <v>326</v>
+        <v>671</v>
       </c>
     </row>
     <row r="234">
@@ -13090,7 +14125,7 @@
         <v>1</v>
       </c>
       <c r="P234" s="0" t="s">
-        <v>327</v>
+        <v>672</v>
       </c>
     </row>
     <row r="235">
@@ -13122,7 +14157,7 @@
         <v>1</v>
       </c>
       <c r="J235" s="0">
-        <v>1455.5117433463759</v>
+        <v>1455.5117433463756</v>
       </c>
       <c r="K235" s="0">
         <v>0.99751373845169589</v>
@@ -13140,7 +14175,7 @@
         <v>1</v>
       </c>
       <c r="P235" s="0" t="s">
-        <v>328</v>
+        <v>673</v>
       </c>
     </row>
     <row r="236">
@@ -13172,7 +14207,7 @@
         <v>1</v>
       </c>
       <c r="J236" s="0">
-        <v>2874.8707020139023</v>
+        <v>2874.8707020139027</v>
       </c>
       <c r="K236" s="0">
         <v>0.99333099931874025</v>
@@ -13190,7 +14225,7 @@
         <v>1</v>
       </c>
       <c r="P236" s="0" t="s">
-        <v>329</v>
+        <v>674</v>
       </c>
     </row>
     <row r="237">
@@ -13222,7 +14257,7 @@
         <v>1</v>
       </c>
       <c r="J237" s="0">
-        <v>1491.4889605688461</v>
+        <v>1491.4889605688463</v>
       </c>
       <c r="K237" s="0">
         <v>0.99643534655967825</v>
@@ -13240,7 +14275,7 @@
         <v>1</v>
       </c>
       <c r="P237" s="0" t="s">
-        <v>330</v>
+        <v>675</v>
       </c>
     </row>
     <row r="238">
@@ -13272,7 +14307,7 @@
         <v>1</v>
       </c>
       <c r="J238" s="0">
-        <v>1678.4082934635874</v>
+        <v>1678.4082934635876</v>
       </c>
       <c r="K238" s="0">
         <v>0.99709226984163923</v>
@@ -13290,7 +14325,7 @@
         <v>1</v>
       </c>
       <c r="P238" s="0" t="s">
-        <v>331</v>
+        <v>676</v>
       </c>
     </row>
     <row r="239">
@@ -13340,7 +14375,7 @@
         <v>1</v>
       </c>
       <c r="P239" s="0" t="s">
-        <v>332</v>
+        <v>677</v>
       </c>
     </row>
     <row r="240">
@@ -13390,7 +14425,7 @@
         <v>1</v>
       </c>
       <c r="P240" s="0" t="s">
-        <v>333</v>
+        <v>678</v>
       </c>
     </row>
     <row r="241">
@@ -13422,7 +14457,7 @@
         <v>1</v>
       </c>
       <c r="J241" s="0">
-        <v>2525.5924972922203</v>
+        <v>2525.5924972922198</v>
       </c>
       <c r="K241" s="0">
         <v>0.99685333603197013</v>
@@ -13440,7 +14475,7 @@
         <v>1</v>
       </c>
       <c r="P241" s="0" t="s">
-        <v>334</v>
+        <v>679</v>
       </c>
     </row>
     <row r="242">
@@ -13490,7 +14525,7 @@
         <v>1</v>
       </c>
       <c r="P242" s="0" t="s">
-        <v>335</v>
+        <v>680</v>
       </c>
     </row>
     <row r="243">
@@ -13540,7 +14575,7 @@
         <v>1</v>
       </c>
       <c r="P243" s="0" t="s">
-        <v>336</v>
+        <v>681</v>
       </c>
     </row>
     <row r="244">
@@ -13590,7 +14625,7 @@
         <v>1</v>
       </c>
       <c r="P244" s="0" t="s">
-        <v>337</v>
+        <v>682</v>
       </c>
     </row>
     <row r="245">
@@ -13622,7 +14657,7 @@
         <v>1</v>
       </c>
       <c r="J245" s="0">
-        <v>1455.5117433463759</v>
+        <v>1455.5117433463756</v>
       </c>
       <c r="K245" s="0">
         <v>0.99751373845169589</v>
@@ -13640,7 +14675,7 @@
         <v>1</v>
       </c>
       <c r="P245" s="0" t="s">
-        <v>338</v>
+        <v>683</v>
       </c>
     </row>
     <row r="246">
@@ -13672,7 +14707,7 @@
         <v>1</v>
       </c>
       <c r="J246" s="0">
-        <v>2874.8707020139023</v>
+        <v>2874.8707020139027</v>
       </c>
       <c r="K246" s="0">
         <v>0.99333099931874025</v>
@@ -13690,7 +14725,7 @@
         <v>1</v>
       </c>
       <c r="P246" s="0" t="s">
-        <v>339</v>
+        <v>684</v>
       </c>
     </row>
     <row r="247">
@@ -13722,7 +14757,7 @@
         <v>1</v>
       </c>
       <c r="J247" s="0">
-        <v>1491.4889605688461</v>
+        <v>1491.4889605688463</v>
       </c>
       <c r="K247" s="0">
         <v>0.99643534655967825</v>
@@ -13740,7 +14775,7 @@
         <v>1</v>
       </c>
       <c r="P247" s="0" t="s">
-        <v>340</v>
+        <v>685</v>
       </c>
     </row>
     <row r="248">
@@ -13790,7 +14825,7 @@
         <v>1</v>
       </c>
       <c r="P248" s="0" t="s">
-        <v>341</v>
+        <v>686</v>
       </c>
     </row>
     <row r="249">
@@ -13840,7 +14875,7 @@
         <v>1</v>
       </c>
       <c r="P249" s="0" t="s">
-        <v>342</v>
+        <v>687</v>
       </c>
     </row>
     <row r="250">
@@ -13890,7 +14925,7 @@
         <v>1</v>
       </c>
       <c r="P250" s="0" t="s">
-        <v>343</v>
+        <v>688</v>
       </c>
     </row>
     <row r="251">
@@ -13936,7 +14971,7 @@
         <v>0</v>
       </c>
       <c r="P251" s="0" t="s">
-        <v>344</v>
+        <v>689</v>
       </c>
     </row>
     <row r="252">
@@ -13968,7 +15003,7 @@
         <v>1</v>
       </c>
       <c r="J252" s="0">
-        <v>192.42091061333258</v>
+        <v>192.42091061333255</v>
       </c>
       <c r="K252" s="0">
         <v>0.9036431974225605</v>
@@ -13986,7 +15021,7 @@
         <v>1</v>
       </c>
       <c r="P252" s="0" t="s">
-        <v>345</v>
+        <v>690</v>
       </c>
     </row>
     <row r="253">
@@ -14036,7 +15071,7 @@
         <v>1</v>
       </c>
       <c r="P253" s="0" t="s">
-        <v>346</v>
+        <v>691</v>
       </c>
     </row>
     <row r="254">
@@ -14068,7 +15103,7 @@
         <v>1</v>
       </c>
       <c r="J254" s="0">
-        <v>384.45618045661763</v>
+        <v>384.4561804566178</v>
       </c>
       <c r="K254" s="0">
         <v>0.95313019401259691</v>
@@ -14086,7 +15121,7 @@
         <v>1</v>
       </c>
       <c r="P254" s="0" t="s">
-        <v>347</v>
+        <v>692</v>
       </c>
     </row>
     <row r="255">
@@ -14118,7 +15153,7 @@
         <v>1</v>
       </c>
       <c r="J255" s="0">
-        <v>1418.6837585694998</v>
+        <v>1418.6837585695</v>
       </c>
       <c r="K255" s="0">
         <v>0.99586902087078955</v>
@@ -14136,7 +15171,7 @@
         <v>1</v>
       </c>
       <c r="P255" s="0" t="s">
-        <v>348</v>
+        <v>693</v>
       </c>
     </row>
     <row r="256">
@@ -14182,7 +15217,7 @@
         <v>0</v>
       </c>
       <c r="P256" s="0" t="s">
-        <v>349</v>
+        <v>694</v>
       </c>
     </row>
     <row r="257">
@@ -14232,7 +15267,7 @@
         <v>1</v>
       </c>
       <c r="P257" s="0" t="s">
-        <v>350</v>
+        <v>695</v>
       </c>
     </row>
     <row r="258">
@@ -14267,7 +15302,7 @@
         <v>352.39259393633017</v>
       </c>
       <c r="K258" s="0">
-        <v>0.85855513162245079</v>
+        <v>0.85855513162245067</v>
       </c>
       <c r="L258" s="0">
         <v>10</v>
@@ -14282,7 +15317,7 @@
         <v>0</v>
       </c>
       <c r="P258" s="0" t="s">
-        <v>351</v>
+        <v>696</v>
       </c>
     </row>
     <row r="259">
@@ -14314,7 +15349,7 @@
         <v>1</v>
       </c>
       <c r="J259" s="0">
-        <v>512.91097720683888</v>
+        <v>512.91097720683877</v>
       </c>
       <c r="K259" s="0">
         <v>0.94181864623289824</v>
@@ -14332,7 +15367,7 @@
         <v>1</v>
       </c>
       <c r="P259" s="0" t="s">
-        <v>352</v>
+        <v>697</v>
       </c>
     </row>
     <row r="260">
@@ -14364,7 +15399,7 @@
         <v>1</v>
       </c>
       <c r="J260" s="0">
-        <v>11.400674139040884</v>
+        <v>11.400674139040882</v>
       </c>
       <c r="K260" s="0">
         <v>0.83576028153114834</v>
@@ -14382,7 +15417,7 @@
         <v>0</v>
       </c>
       <c r="P260" s="0" t="s">
-        <v>353</v>
+        <v>698</v>
       </c>
     </row>
     <row r="261">
@@ -14414,7 +15449,7 @@
         <v>1</v>
       </c>
       <c r="J261" s="0">
-        <v>254.43728349564017</v>
+        <v>254.4372834956402</v>
       </c>
       <c r="K261" s="0">
         <v>0.95447799898686769</v>
@@ -14432,7 +15467,7 @@
         <v>1</v>
       </c>
       <c r="P261" s="0" t="s">
-        <v>354</v>
+        <v>699</v>
       </c>
     </row>
     <row r="262">
@@ -14464,10 +15499,10 @@
         <v>1</v>
       </c>
       <c r="J262" s="0">
-        <v>398.49379114531337</v>
+        <v>398.49379114531348</v>
       </c>
       <c r="K262" s="0">
-        <v>0.979989027928726</v>
+        <v>0.97998902792872589</v>
       </c>
       <c r="L262" s="0">
         <v>9</v>
@@ -14482,7 +15517,7 @@
         <v>1</v>
       </c>
       <c r="P262" s="0" t="s">
-        <v>355</v>
+        <v>700</v>
       </c>
     </row>
     <row r="263">
@@ -14532,7 +15567,7 @@
         <v>0</v>
       </c>
       <c r="P263" s="0" t="s">
-        <v>356</v>
+        <v>701</v>
       </c>
     </row>
     <row r="264">
@@ -14567,7 +15602,7 @@
         <v>45.187736026753143</v>
       </c>
       <c r="K264" s="0">
-        <v>0.95383363988415848</v>
+        <v>0.95383363988415859</v>
       </c>
       <c r="L264" s="0">
         <v>10</v>
@@ -14582,7 +15617,7 @@
         <v>1</v>
       </c>
       <c r="P264" s="0" t="s">
-        <v>357</v>
+        <v>702</v>
       </c>
     </row>
     <row r="265">
@@ -14614,7 +15649,7 @@
         <v>1</v>
       </c>
       <c r="J265" s="0">
-        <v>3.3534192222269947</v>
+        <v>3.3534192222269978</v>
       </c>
       <c r="K265" s="0">
         <v>0.9093946230277079</v>
@@ -14632,7 +15667,7 @@
         <v>1</v>
       </c>
       <c r="P265" s="0" t="s">
-        <v>358</v>
+        <v>703</v>
       </c>
     </row>
     <row r="266">
@@ -14682,7 +15717,7 @@
         <v>0</v>
       </c>
       <c r="P266" s="0" t="s">
-        <v>359</v>
+        <v>704</v>
       </c>
     </row>
     <row r="267">
@@ -14714,10 +15749,10 @@
         <v>1</v>
       </c>
       <c r="J267" s="0">
-        <v>13.133910480212798</v>
+        <v>13.133910480212791</v>
       </c>
       <c r="K267" s="0">
-        <v>0.80613579804165703</v>
+        <v>0.80613579804165692</v>
       </c>
       <c r="L267" s="0">
         <v>10</v>
@@ -14732,7 +15767,7 @@
         <v>0</v>
       </c>
       <c r="P267" s="0" t="s">
-        <v>360</v>
+        <v>705</v>
       </c>
     </row>
     <row r="268">
@@ -14764,10 +15799,10 @@
         <v>1</v>
       </c>
       <c r="J268" s="0">
-        <v>268.1397124491661</v>
+        <v>268.13971244916615</v>
       </c>
       <c r="K268" s="0">
-        <v>0.95938899466819394</v>
+        <v>0.95938899466819383</v>
       </c>
       <c r="L268" s="0">
         <v>10</v>
@@ -14782,7 +15817,7 @@
         <v>1</v>
       </c>
       <c r="P268" s="0" t="s">
-        <v>361</v>
+        <v>706</v>
       </c>
     </row>
     <row r="269">
@@ -14832,7 +15867,7 @@
         <v>0</v>
       </c>
       <c r="P269" s="0" t="s">
-        <v>362</v>
+        <v>707</v>
       </c>
     </row>
     <row r="270">
@@ -14882,7 +15917,7 @@
         <v>1</v>
       </c>
       <c r="P270" s="0" t="s">
-        <v>363</v>
+        <v>708</v>
       </c>
     </row>
     <row r="271">
@@ -14914,7 +15949,7 @@
         <v>1</v>
       </c>
       <c r="J271" s="0">
-        <v>570.94068302014318</v>
+        <v>570.94068302014284</v>
       </c>
       <c r="K271" s="0">
         <v>0.95926162197996057</v>
@@ -14932,7 +15967,7 @@
         <v>1</v>
       </c>
       <c r="P271" s="0" t="s">
-        <v>364</v>
+        <v>709</v>
       </c>
     </row>
     <row r="272">
@@ -14982,7 +16017,7 @@
         <v>1</v>
       </c>
       <c r="P272" s="0" t="s">
-        <v>365</v>
+        <v>710</v>
       </c>
     </row>
     <row r="273">
@@ -15028,7 +16063,7 @@
         <v>0</v>
       </c>
       <c r="P273" s="0" t="s">
-        <v>366</v>
+        <v>711</v>
       </c>
     </row>
     <row r="274">
@@ -15078,7 +16113,7 @@
         <v>1</v>
       </c>
       <c r="P274" s="0" t="s">
-        <v>367</v>
+        <v>712</v>
       </c>
     </row>
     <row r="275">
@@ -15110,10 +16145,10 @@
         <v>1</v>
       </c>
       <c r="J275" s="0">
-        <v>529.45708310298039</v>
+        <v>529.4570831029805</v>
       </c>
       <c r="K275" s="0">
-        <v>0.87168098261109472</v>
+        <v>0.87168098261109483</v>
       </c>
       <c r="L275" s="0">
         <v>10</v>
@@ -15128,7 +16163,7 @@
         <v>0</v>
       </c>
       <c r="P275" s="0" t="s">
-        <v>368</v>
+        <v>713</v>
       </c>
     </row>
     <row r="276">
@@ -15160,7 +16195,7 @@
         <v>1</v>
       </c>
       <c r="J276" s="0">
-        <v>758.06535201219174</v>
+        <v>758.06535201219162</v>
       </c>
       <c r="K276" s="0">
         <v>0.99670764581294224</v>
@@ -15178,7 +16213,7 @@
         <v>1</v>
       </c>
       <c r="P276" s="0" t="s">
-        <v>369</v>
+        <v>714</v>
       </c>
     </row>
     <row r="277">
@@ -15210,7 +16245,7 @@
         <v>1</v>
       </c>
       <c r="J277" s="0">
-        <v>315.48003614417814</v>
+        <v>315.4800361441782</v>
       </c>
       <c r="K277" s="0">
         <v>0.92524688597342442</v>
@@ -15228,7 +16263,7 @@
         <v>1</v>
       </c>
       <c r="P277" s="0" t="s">
-        <v>370</v>
+        <v>715</v>
       </c>
     </row>
     <row r="278">
@@ -15278,7 +16313,7 @@
         <v>0</v>
       </c>
       <c r="P278" s="0" t="s">
-        <v>371</v>
+        <v>716</v>
       </c>
     </row>
     <row r="279">
@@ -15310,7 +16345,7 @@
         <v>1</v>
       </c>
       <c r="J279" s="0">
-        <v>323.04969785446519</v>
+        <v>323.04969785446508</v>
       </c>
       <c r="K279" s="0">
         <v>0.95107206324464433</v>
@@ -15328,7 +16363,7 @@
         <v>1</v>
       </c>
       <c r="P279" s="0" t="s">
-        <v>372</v>
+        <v>717</v>
       </c>
     </row>
     <row r="280">
@@ -15378,7 +16413,7 @@
         <v>1</v>
       </c>
       <c r="P280" s="0" t="s">
-        <v>373</v>
+        <v>718</v>
       </c>
     </row>
     <row r="281">
@@ -15428,7 +16463,7 @@
         <v>1</v>
       </c>
       <c r="P281" s="0" t="s">
-        <v>374</v>
+        <v>719</v>
       </c>
     </row>
     <row r="282">
@@ -15460,7 +16495,7 @@
         <v>1</v>
       </c>
       <c r="J282" s="0">
-        <v>1379.4400953307611</v>
+        <v>1379.4400953307616</v>
       </c>
       <c r="K282" s="0">
         <v>0.99831457480633468</v>
@@ -15478,7 +16513,7 @@
         <v>1</v>
       </c>
       <c r="P282" s="0" t="s">
-        <v>375</v>
+        <v>720</v>
       </c>
     </row>
     <row r="283">
@@ -15510,7 +16545,7 @@
         <v>1</v>
       </c>
       <c r="J283" s="0">
-        <v>1370.2590578219076</v>
+        <v>1370.2590578219078</v>
       </c>
       <c r="K283" s="0">
         <v>0.99669301763227647</v>
@@ -15528,7 +16563,7 @@
         <v>1</v>
       </c>
       <c r="P283" s="0" t="s">
-        <v>376</v>
+        <v>721</v>
       </c>
     </row>
     <row r="284">
@@ -15560,7 +16595,7 @@
         <v>1</v>
       </c>
       <c r="J284" s="0">
-        <v>2539.2521882687824</v>
+        <v>2539.252188268782</v>
       </c>
       <c r="K284" s="0">
         <v>0.9962700456575454</v>
@@ -15578,7 +16613,7 @@
         <v>1</v>
       </c>
       <c r="P284" s="0" t="s">
-        <v>377</v>
+        <v>722</v>
       </c>
     </row>
     <row r="285">
@@ -15628,7 +16663,7 @@
         <v>1</v>
       </c>
       <c r="P285" s="0" t="s">
-        <v>378</v>
+        <v>723</v>
       </c>
     </row>
     <row r="286">
@@ -15663,7 +16698,7 @@
         <v>2621.4672744778886</v>
       </c>
       <c r="K286" s="0">
-        <v>0.99501099374933311</v>
+        <v>0.99501099374933299</v>
       </c>
       <c r="L286" s="0">
         <v>50</v>
@@ -15678,7 +16713,7 @@
         <v>1</v>
       </c>
       <c r="P286" s="0" t="s">
-        <v>379</v>
+        <v>724</v>
       </c>
     </row>
     <row r="287">
@@ -15710,7 +16745,7 @@
         <v>1</v>
       </c>
       <c r="J287" s="0">
-        <v>2592.8762022801302</v>
+        <v>2592.8762022801297</v>
       </c>
       <c r="K287" s="0">
         <v>0.99309025398432471</v>
@@ -15728,7 +16763,7 @@
         <v>1</v>
       </c>
       <c r="P287" s="0" t="s">
-        <v>380</v>
+        <v>725</v>
       </c>
     </row>
     <row r="288">
@@ -15760,7 +16795,7 @@
         <v>1</v>
       </c>
       <c r="J288" s="0">
-        <v>1560.8194865800665</v>
+        <v>1560.8194865800663</v>
       </c>
       <c r="K288" s="0">
         <v>0.99555257962182553</v>
@@ -15778,7 +16813,7 @@
         <v>1</v>
       </c>
       <c r="P288" s="0" t="s">
-        <v>381</v>
+        <v>726</v>
       </c>
     </row>
     <row r="289">
@@ -15810,7 +16845,7 @@
         <v>1</v>
       </c>
       <c r="J289" s="0">
-        <v>2078.9998838732204</v>
+        <v>2078.9998838732208</v>
       </c>
       <c r="K289" s="0">
         <v>0.98474830893698151</v>
@@ -15828,7 +16863,7 @@
         <v>1</v>
       </c>
       <c r="P289" s="0" t="s">
-        <v>382</v>
+        <v>727</v>
       </c>
     </row>
     <row r="290">
@@ -15860,7 +16895,7 @@
         <v>1</v>
       </c>
       <c r="J290" s="0">
-        <v>1190.9117209662809</v>
+        <v>1190.9117209662807</v>
       </c>
       <c r="K290" s="0">
         <v>0.99761066638701845</v>
@@ -15878,7 +16913,7 @@
         <v>1</v>
       </c>
       <c r="P290" s="0" t="s">
-        <v>383</v>
+        <v>728</v>
       </c>
     </row>
     <row r="291">
@@ -15928,7 +16963,7 @@
         <v>1</v>
       </c>
       <c r="P291" s="0" t="s">
-        <v>384</v>
+        <v>729</v>
       </c>
     </row>
     <row r="292">
@@ -15978,7 +17013,7 @@
         <v>1</v>
       </c>
       <c r="P292" s="0" t="s">
-        <v>385</v>
+        <v>730</v>
       </c>
     </row>
     <row r="293">
@@ -16028,7 +17063,7 @@
         <v>1</v>
       </c>
       <c r="P293" s="0" t="s">
-        <v>386</v>
+        <v>731</v>
       </c>
     </row>
     <row r="294">
@@ -16060,7 +17095,7 @@
         <v>1</v>
       </c>
       <c r="J294" s="0">
-        <v>1088.1920475078391</v>
+        <v>1088.1920475078389</v>
       </c>
       <c r="K294" s="0">
         <v>0.96218147899027162</v>
@@ -16078,7 +17113,7 @@
         <v>1</v>
       </c>
       <c r="P294" s="0" t="s">
-        <v>387</v>
+        <v>732</v>
       </c>
     </row>
     <row r="295">
@@ -16128,7 +17163,7 @@
         <v>1</v>
       </c>
       <c r="P295" s="0" t="s">
-        <v>388</v>
+        <v>733</v>
       </c>
     </row>
     <row r="296">
@@ -16160,10 +17195,10 @@
         <v>1</v>
       </c>
       <c r="J296" s="0">
-        <v>1330.2709774134655</v>
+        <v>1330.2709774134648</v>
       </c>
       <c r="K296" s="0">
-        <v>0.99040059469464858</v>
+        <v>0.9904005946946487</v>
       </c>
       <c r="L296" s="0">
         <v>50</v>
@@ -16178,7 +17213,7 @@
         <v>1</v>
       </c>
       <c r="P296" s="0" t="s">
-        <v>389</v>
+        <v>734</v>
       </c>
     </row>
     <row r="297">
@@ -16210,7 +17245,7 @@
         <v>1</v>
       </c>
       <c r="J297" s="0">
-        <v>1566.5286936543673</v>
+        <v>1566.528693654368</v>
       </c>
       <c r="K297" s="0">
         <v>0.99278914480686276</v>
@@ -16228,7 +17263,7 @@
         <v>1</v>
       </c>
       <c r="P297" s="0" t="s">
-        <v>390</v>
+        <v>735</v>
       </c>
     </row>
     <row r="298">
@@ -16260,7 +17295,7 @@
         <v>1</v>
       </c>
       <c r="J298" s="0">
-        <v>1238.7382130834928</v>
+        <v>1238.7382130834931</v>
       </c>
       <c r="K298" s="0">
         <v>0.99789101373191746</v>
@@ -16278,7 +17313,7 @@
         <v>1</v>
       </c>
       <c r="P298" s="0" t="s">
-        <v>391</v>
+        <v>736</v>
       </c>
     </row>
     <row r="299">
@@ -16310,7 +17345,7 @@
         <v>1</v>
       </c>
       <c r="J299" s="0">
-        <v>2040.4546054087846</v>
+        <v>2040.4546054087825</v>
       </c>
       <c r="K299" s="0">
         <v>0.99247701698284152</v>
@@ -16328,7 +17363,7 @@
         <v>1</v>
       </c>
       <c r="P299" s="0" t="s">
-        <v>392</v>
+        <v>737</v>
       </c>
     </row>
     <row r="300">
@@ -16378,7 +17413,7 @@
         <v>1</v>
       </c>
       <c r="P300" s="0" t="s">
-        <v>393</v>
+        <v>738</v>
       </c>
     </row>
     <row r="301">
@@ -16428,7 +17463,7 @@
         <v>1</v>
       </c>
       <c r="P301" s="0" t="s">
-        <v>394</v>
+        <v>739</v>
       </c>
     </row>
     <row r="302">
@@ -16478,7 +17513,7 @@
         <v>1</v>
       </c>
       <c r="P302" s="0" t="s">
-        <v>395</v>
+        <v>740</v>
       </c>
     </row>
     <row r="303">
@@ -16510,7 +17545,7 @@
         <v>1</v>
       </c>
       <c r="J303" s="0">
-        <v>685.47371274742307</v>
+        <v>685.47371274742272</v>
       </c>
       <c r="K303" s="0">
         <v>0.9731869319013895</v>
@@ -16528,7 +17563,7 @@
         <v>1</v>
       </c>
       <c r="P303" s="0" t="s">
-        <v>396</v>
+        <v>741</v>
       </c>
     </row>
     <row r="304">
@@ -16560,7 +17595,7 @@
         <v>1</v>
       </c>
       <c r="J304" s="0">
-        <v>0.12725107804428357</v>
+        <v>0.1272510780442836</v>
       </c>
       <c r="K304" s="0">
         <v>0.2869204259582</v>
@@ -16578,7 +17613,7 @@
         <v>0</v>
       </c>
       <c r="P304" s="0" t="s">
-        <v>397</v>
+        <v>742</v>
       </c>
     </row>
     <row r="305">
@@ -16624,7 +17659,7 @@
         <v>0</v>
       </c>
       <c r="P305" s="0" t="s">
-        <v>398</v>
+        <v>743</v>
       </c>
     </row>
     <row r="306">
@@ -16674,7 +17709,7 @@
         <v>1</v>
       </c>
       <c r="P306" s="0" t="s">
-        <v>399</v>
+        <v>744</v>
       </c>
     </row>
     <row r="307">
@@ -16724,7 +17759,7 @@
         <v>1</v>
       </c>
       <c r="P307" s="0" t="s">
-        <v>400</v>
+        <v>745</v>
       </c>
     </row>
     <row r="308">
@@ -16756,7 +17791,7 @@
         <v>1</v>
       </c>
       <c r="J308" s="0">
-        <v>346.56630219222728</v>
+        <v>346.56630219222734</v>
       </c>
       <c r="K308" s="0">
         <v>0.99843645416990068</v>
@@ -16774,7 +17809,7 @@
         <v>1</v>
       </c>
       <c r="P308" s="0" t="s">
-        <v>401</v>
+        <v>746</v>
       </c>
     </row>
     <row r="309">
@@ -16820,7 +17855,7 @@
         <v>0</v>
       </c>
       <c r="P309" s="0" t="s">
-        <v>402</v>
+        <v>747</v>
       </c>
     </row>
     <row r="310">
@@ -16852,7 +17887,7 @@
         <v>1</v>
       </c>
       <c r="J310" s="0">
-        <v>511.91560184828978</v>
+        <v>511.91560184828961</v>
       </c>
       <c r="K310" s="0">
         <v>0.99694904379922544</v>
@@ -16870,7 +17905,7 @@
         <v>1</v>
       </c>
       <c r="P310" s="0" t="s">
-        <v>403</v>
+        <v>748</v>
       </c>
     </row>
     <row r="311">
@@ -16920,7 +17955,7 @@
         <v>1</v>
       </c>
       <c r="P311" s="0" t="s">
-        <v>404</v>
+        <v>749</v>
       </c>
     </row>
     <row r="312">
@@ -16966,7 +18001,7 @@
         <v>0</v>
       </c>
       <c r="P312" s="0" t="s">
-        <v>405</v>
+        <v>750</v>
       </c>
     </row>
     <row r="313">
@@ -16998,7 +18033,7 @@
         <v>1</v>
       </c>
       <c r="J313" s="0">
-        <v>136.50870813899388</v>
+        <v>136.50870813899394</v>
       </c>
       <c r="K313" s="0">
         <v>0.98806382018266126</v>
@@ -17016,7 +18051,7 @@
         <v>1</v>
       </c>
       <c r="P313" s="0" t="s">
-        <v>406</v>
+        <v>751</v>
       </c>
     </row>
     <row r="314">
@@ -17066,7 +18101,7 @@
         <v>0</v>
       </c>
       <c r="P314" s="0" t="s">
-        <v>407</v>
+        <v>752</v>
       </c>
     </row>
     <row r="315">
@@ -17112,7 +18147,7 @@
         <v>0</v>
       </c>
       <c r="P315" s="0" t="s">
-        <v>408</v>
+        <v>753</v>
       </c>
     </row>
     <row r="316">
@@ -17162,7 +18197,7 @@
         <v>1</v>
       </c>
       <c r="P316" s="0" t="s">
-        <v>409</v>
+        <v>754</v>
       </c>
     </row>
     <row r="317">
@@ -17208,7 +18243,7 @@
         <v>0</v>
       </c>
       <c r="P317" s="0" t="s">
-        <v>410</v>
+        <v>755</v>
       </c>
     </row>
     <row r="318">
@@ -17258,7 +18293,7 @@
         <v>1</v>
       </c>
       <c r="P318" s="0" t="s">
-        <v>411</v>
+        <v>756</v>
       </c>
     </row>
     <row r="319">
@@ -17290,10 +18325,10 @@
         <v>1</v>
       </c>
       <c r="J319" s="0">
-        <v>255.46246187259516</v>
+        <v>255.46246187259499</v>
       </c>
       <c r="K319" s="0">
-        <v>0.99294662619282459</v>
+        <v>0.9929466261928247</v>
       </c>
       <c r="L319" s="0">
         <v>10</v>
@@ -17308,7 +18343,7 @@
         <v>1</v>
       </c>
       <c r="P319" s="0" t="s">
-        <v>412</v>
+        <v>757</v>
       </c>
     </row>
     <row r="320">
@@ -17340,10 +18375,10 @@
         <v>1</v>
       </c>
       <c r="J320" s="0">
-        <v>197.50475430227795</v>
+        <v>197.50475430227797</v>
       </c>
       <c r="K320" s="0">
-        <v>0.98267966160743858</v>
+        <v>0.98267966160743869</v>
       </c>
       <c r="L320" s="0">
         <v>10</v>
@@ -17358,7 +18393,7 @@
         <v>1</v>
       </c>
       <c r="P320" s="0" t="s">
-        <v>413</v>
+        <v>758</v>
       </c>
     </row>
     <row r="321">
@@ -17408,7 +18443,7 @@
         <v>1</v>
       </c>
       <c r="P321" s="0" t="s">
-        <v>414</v>
+        <v>759</v>
       </c>
     </row>
     <row r="322">
@@ -17454,7 +18489,7 @@
         <v>0</v>
       </c>
       <c r="P322" s="0" t="s">
-        <v>415</v>
+        <v>760</v>
       </c>
     </row>
     <row r="323">
@@ -17486,7 +18521,7 @@
         <v>1</v>
       </c>
       <c r="J323" s="0">
-        <v>511.91560184828978</v>
+        <v>511.91560184828961</v>
       </c>
       <c r="K323" s="0">
         <v>0.99694904379922544</v>
@@ -17504,7 +18539,7 @@
         <v>1</v>
       </c>
       <c r="P323" s="0" t="s">
-        <v>416</v>
+        <v>761</v>
       </c>
     </row>
     <row r="324">
@@ -17554,7 +18589,7 @@
         <v>1</v>
       </c>
       <c r="P324" s="0" t="s">
-        <v>417</v>
+        <v>762</v>
       </c>
     </row>
     <row r="325">
@@ -17604,7 +18639,7 @@
         <v>1</v>
       </c>
       <c r="P325" s="0" t="s">
-        <v>418</v>
+        <v>763</v>
       </c>
     </row>
     <row r="326">
@@ -17636,7 +18671,7 @@
         <v>1</v>
       </c>
       <c r="J326" s="0">
-        <v>24.039908371424929</v>
+        <v>24.039908371424922</v>
       </c>
       <c r="K326" s="0">
         <v>0.97593409463413106</v>
@@ -17654,7 +18689,7 @@
         <v>1</v>
       </c>
       <c r="P326" s="0" t="s">
-        <v>419</v>
+        <v>764</v>
       </c>
     </row>
     <row r="327">
@@ -17704,7 +18739,7 @@
         <v>1</v>
       </c>
       <c r="P327" s="0" t="s">
-        <v>420</v>
+        <v>765</v>
       </c>
     </row>
     <row r="328">
@@ -17754,7 +18789,7 @@
         <v>1</v>
       </c>
       <c r="P328" s="0" t="s">
-        <v>421</v>
+        <v>766</v>
       </c>
     </row>
     <row r="329">
@@ -17786,7 +18821,7 @@
         <v>1</v>
       </c>
       <c r="J329" s="0">
-        <v>18.624276947429966</v>
+        <v>18.624276947429959</v>
       </c>
       <c r="K329" s="0">
         <v>0.96489627186554361</v>
@@ -17804,7 +18839,7 @@
         <v>1</v>
       </c>
       <c r="P329" s="0" t="s">
-        <v>422</v>
+        <v>767</v>
       </c>
     </row>
     <row r="330">
@@ -17836,7 +18871,7 @@
         <v>1</v>
       </c>
       <c r="J330" s="0">
-        <v>1437.0215611114031</v>
+        <v>1437.0215611114029</v>
       </c>
       <c r="K330" s="0">
         <v>0.98890169968549757</v>
@@ -17854,7 +18889,7 @@
         <v>1</v>
       </c>
       <c r="P330" s="0" t="s">
-        <v>423</v>
+        <v>768</v>
       </c>
     </row>
     <row r="331">
@@ -17904,7 +18939,7 @@
         <v>1</v>
       </c>
       <c r="P331" s="0" t="s">
-        <v>424</v>
+        <v>769</v>
       </c>
     </row>
     <row r="332">
@@ -17936,7 +18971,7 @@
         <v>1</v>
       </c>
       <c r="J332" s="0">
-        <v>2157.8969355813429</v>
+        <v>2157.8969355813424</v>
       </c>
       <c r="K332" s="0">
         <v>0.98297065951951768</v>
@@ -17954,7 +18989,7 @@
         <v>1</v>
       </c>
       <c r="P332" s="0" t="s">
-        <v>425</v>
+        <v>770</v>
       </c>
     </row>
     <row r="333">
@@ -17986,7 +19021,7 @@
         <v>1</v>
       </c>
       <c r="J333" s="0">
-        <v>1060.6310502079718</v>
+        <v>1060.6310502079721</v>
       </c>
       <c r="K333" s="0">
         <v>0.99413834129628198</v>
@@ -18004,7 +19039,7 @@
         <v>1</v>
       </c>
       <c r="P333" s="0" t="s">
-        <v>426</v>
+        <v>771</v>
       </c>
     </row>
     <row r="334">
@@ -18036,7 +19071,7 @@
         <v>1</v>
       </c>
       <c r="J334" s="0">
-        <v>1721.0132386405028</v>
+        <v>1721.0132386405021</v>
       </c>
       <c r="K334" s="0">
         <v>0.98310352394719425</v>
@@ -18054,7 +19089,7 @@
         <v>1</v>
       </c>
       <c r="P334" s="0" t="s">
-        <v>427</v>
+        <v>772</v>
       </c>
     </row>
     <row r="335">
@@ -18104,7 +19139,7 @@
         <v>1</v>
       </c>
       <c r="P335" s="0" t="s">
-        <v>428</v>
+        <v>773</v>
       </c>
     </row>
     <row r="336">
@@ -18136,7 +19171,7 @@
         <v>1</v>
       </c>
       <c r="J336" s="0">
-        <v>1290.1572222988575</v>
+        <v>1290.157222298858</v>
       </c>
       <c r="K336" s="0">
         <v>0.99665092595450422</v>
@@ -18154,7 +19189,7 @@
         <v>1</v>
       </c>
       <c r="P336" s="0" t="s">
-        <v>429</v>
+        <v>774</v>
       </c>
     </row>
     <row r="337">
@@ -18186,7 +19221,7 @@
         <v>1</v>
       </c>
       <c r="J337" s="0">
-        <v>1390.20480024937</v>
+        <v>1390.2048002493702</v>
       </c>
       <c r="K337" s="0">
         <v>0.97951266077932142</v>
@@ -18204,7 +19239,7 @@
         <v>1</v>
       </c>
       <c r="P337" s="0" t="s">
-        <v>430</v>
+        <v>775</v>
       </c>
     </row>
     <row r="338">
@@ -18254,7 +19289,7 @@
         <v>1</v>
       </c>
       <c r="P338" s="0" t="s">
-        <v>431</v>
+        <v>776</v>
       </c>
     </row>
     <row r="339">
@@ -18304,7 +19339,7 @@
         <v>1</v>
       </c>
       <c r="P339" s="0" t="s">
-        <v>432</v>
+        <v>777</v>
       </c>
     </row>
     <row r="340">
@@ -18354,7 +19389,7 @@
         <v>1</v>
       </c>
       <c r="P340" s="0" t="s">
-        <v>433</v>
+        <v>778</v>
       </c>
     </row>
     <row r="341">
@@ -18404,7 +19439,7 @@
         <v>1</v>
       </c>
       <c r="P341" s="0" t="s">
-        <v>434</v>
+        <v>779</v>
       </c>
     </row>
     <row r="342">
@@ -18436,7 +19471,7 @@
         <v>1</v>
       </c>
       <c r="J342" s="0">
-        <v>1461.285999548682</v>
+        <v>1461.2859995486826</v>
       </c>
       <c r="K342" s="0">
         <v>0.99181305777577145</v>
@@ -18454,7 +19489,7 @@
         <v>1</v>
       </c>
       <c r="P342" s="0" t="s">
-        <v>435</v>
+        <v>780</v>
       </c>
     </row>
     <row r="343">
@@ -18504,7 +19539,7 @@
         <v>1</v>
       </c>
       <c r="P343" s="0" t="s">
-        <v>436</v>
+        <v>781</v>
       </c>
     </row>
     <row r="344">
@@ -18554,7 +19589,7 @@
         <v>1</v>
       </c>
       <c r="P344" s="0" t="s">
-        <v>437</v>
+        <v>782</v>
       </c>
     </row>
     <row r="345">
@@ -18604,7 +19639,7 @@
         <v>1</v>
       </c>
       <c r="P345" s="0" t="s">
-        <v>438</v>
+        <v>783</v>
       </c>
     </row>
     <row r="346">
@@ -18636,10 +19671,10 @@
         <v>1</v>
       </c>
       <c r="J346" s="0">
-        <v>2269.1203856965349</v>
+        <v>2269.1203856965344</v>
       </c>
       <c r="K346" s="0">
-        <v>0.98310623943385045</v>
+        <v>0.98310623943385034</v>
       </c>
       <c r="L346" s="0">
         <v>54</v>
@@ -18654,7 +19689,7 @@
         <v>1</v>
       </c>
       <c r="P346" s="0" t="s">
-        <v>439</v>
+        <v>784</v>
       </c>
     </row>
   </sheetData>
@@ -18666,22 +19701,22 @@
   <dimension ref="A1:P307"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.90625" customWidth="true"/>
-    <col min="2" max="2" width="7.90625" customWidth="true"/>
-    <col min="3" max="3" width="11.81640625" customWidth="true"/>
-    <col min="4" max="4" width="6.54296875" customWidth="true"/>
-    <col min="5" max="5" width="10.36328125" customWidth="true"/>
-    <col min="6" max="6" width="17.36328125" customWidth="true"/>
-    <col min="7" max="7" width="7.36328125" customWidth="true"/>
-    <col min="8" max="8" width="13.7265625" customWidth="true"/>
-    <col min="9" max="9" width="13.81640625" customWidth="true"/>
-    <col min="10" max="10" width="19" customWidth="true"/>
-    <col min="11" max="11" width="12.453125" customWidth="true"/>
-    <col min="12" max="12" width="14.81640625" customWidth="true"/>
-    <col min="13" max="13" width="11.6328125" customWidth="true"/>
-    <col min="14" max="14" width="10.90625" customWidth="true"/>
-    <col min="15" max="15" width="10.54296875" customWidth="true"/>
-    <col min="16" max="16" width="195.7265625" customWidth="true"/>
+    <col min="1" max="1" width="5.140625" customWidth="true"/>
+    <col min="2" max="2" width="8.5703125" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
+    <col min="4" max="4" width="7" customWidth="true"/>
+    <col min="5" max="5" width="11.28515625" customWidth="true"/>
+    <col min="6" max="6" width="18.28515625" customWidth="true"/>
+    <col min="7" max="7" width="7.85546875" customWidth="true"/>
+    <col min="8" max="8" width="15" customWidth="true"/>
+    <col min="9" max="9" width="15" customWidth="true"/>
+    <col min="10" max="10" width="20" customWidth="true"/>
+    <col min="11" max="11" width="12.7109375" customWidth="true"/>
+    <col min="12" max="12" width="16.28515625" customWidth="true"/>
+    <col min="13" max="13" width="12.7109375" customWidth="true"/>
+    <col min="14" max="14" width="11.85546875" customWidth="true"/>
+    <col min="15" max="15" width="11.7109375" customWidth="true"/>
+    <col min="16" max="16" width="175.28515625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18763,10 +19798,10 @@
         <v>1</v>
       </c>
       <c r="J2" s="0">
-        <v>1577.5282337380456</v>
+        <v>1577.5282337380461</v>
       </c>
       <c r="K2" s="0">
-        <v>0.99053861886916805</v>
+        <v>0.99053861886916794</v>
       </c>
       <c r="L2" s="0">
         <v>10</v>
@@ -18781,7 +19816,7 @@
         <v>1</v>
       </c>
       <c r="P2" s="0" t="s">
-        <v>95</v>
+        <v>440</v>
       </c>
     </row>
     <row r="3">
@@ -18813,7 +19848,7 @@
         <v>1</v>
       </c>
       <c r="J3" s="0">
-        <v>812.17656145159049</v>
+        <v>812.17656145159026</v>
       </c>
       <c r="K3" s="0">
         <v>0.9999145356608955</v>
@@ -18831,7 +19866,7 @@
         <v>1</v>
       </c>
       <c r="P3" s="0" t="s">
-        <v>97</v>
+        <v>442</v>
       </c>
     </row>
     <row r="4">
@@ -18866,7 +19901,7 @@
         <v>1263.4461565876516</v>
       </c>
       <c r="K4" s="0">
-        <v>0.98756011177686887</v>
+        <v>0.98756011177686875</v>
       </c>
       <c r="L4" s="0">
         <v>10</v>
@@ -18881,7 +19916,7 @@
         <v>1</v>
       </c>
       <c r="P4" s="0" t="s">
-        <v>98</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5">
@@ -18913,7 +19948,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="0">
-        <v>36.968752859095488</v>
+        <v>36.968752859095495</v>
       </c>
       <c r="K5" s="0">
         <v>0.98178320762864302</v>
@@ -18931,7 +19966,7 @@
         <v>1</v>
       </c>
       <c r="P5" s="0" t="s">
-        <v>99</v>
+        <v>444</v>
       </c>
     </row>
     <row r="6">
@@ -18981,7 +20016,7 @@
         <v>1</v>
       </c>
       <c r="P6" s="0" t="s">
-        <v>100</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7">
@@ -19031,7 +20066,7 @@
         <v>1</v>
       </c>
       <c r="P7" s="0" t="s">
-        <v>102</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8">
@@ -19081,7 +20116,7 @@
         <v>1</v>
       </c>
       <c r="P8" s="0" t="s">
-        <v>103</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -19131,7 +20166,7 @@
         <v>1</v>
       </c>
       <c r="P9" s="0" t="s">
-        <v>105</v>
+        <v>450</v>
       </c>
     </row>
     <row r="10">
@@ -19163,7 +20198,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="0">
-        <v>1152.9138297782222</v>
+        <v>1152.9138297782224</v>
       </c>
       <c r="K10" s="0">
         <v>0.96947372692026201</v>
@@ -19181,7 +20216,7 @@
         <v>1</v>
       </c>
       <c r="P10" s="0" t="s">
-        <v>106</v>
+        <v>451</v>
       </c>
     </row>
     <row r="11">
@@ -19213,7 +20248,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="0">
-        <v>217.11967189177653</v>
+        <v>217.11967189177659</v>
       </c>
       <c r="K11" s="0">
         <v>0.96712552976165778</v>
@@ -19231,7 +20266,7 @@
         <v>1</v>
       </c>
       <c r="P11" s="0" t="s">
-        <v>107</v>
+        <v>452</v>
       </c>
     </row>
     <row r="12">
@@ -19263,7 +20298,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="0">
-        <v>2524.0614300894131</v>
+        <v>2524.0614300894135</v>
       </c>
       <c r="K12" s="0">
         <v>0.99863134409152532</v>
@@ -19281,7 +20316,7 @@
         <v>1</v>
       </c>
       <c r="P12" s="0" t="s">
-        <v>108</v>
+        <v>453</v>
       </c>
     </row>
     <row r="13">
@@ -19331,7 +20366,7 @@
         <v>1</v>
       </c>
       <c r="P13" s="0" t="s">
-        <v>109</v>
+        <v>454</v>
       </c>
     </row>
     <row r="14">
@@ -19381,7 +20416,7 @@
         <v>1</v>
       </c>
       <c r="P14" s="0" t="s">
-        <v>110</v>
+        <v>455</v>
       </c>
     </row>
     <row r="15">
@@ -19431,7 +20466,7 @@
         <v>1</v>
       </c>
       <c r="P15" s="0" t="s">
-        <v>111</v>
+        <v>456</v>
       </c>
     </row>
     <row r="16">
@@ -19481,7 +20516,7 @@
         <v>1</v>
       </c>
       <c r="P16" s="0" t="s">
-        <v>112</v>
+        <v>457</v>
       </c>
     </row>
     <row r="17">
@@ -19531,7 +20566,7 @@
         <v>1</v>
       </c>
       <c r="P17" s="0" t="s">
-        <v>113</v>
+        <v>458</v>
       </c>
     </row>
     <row r="18">
@@ -19563,7 +20598,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="0">
-        <v>1823.4795250269992</v>
+        <v>1823.4795250269983</v>
       </c>
       <c r="K18" s="0">
         <v>0.99911347890930613</v>
@@ -19581,7 +20616,7 @@
         <v>1</v>
       </c>
       <c r="P18" s="0" t="s">
-        <v>114</v>
+        <v>459</v>
       </c>
     </row>
     <row r="19">
@@ -19631,7 +20666,7 @@
         <v>1</v>
       </c>
       <c r="P19" s="0" t="s">
-        <v>115</v>
+        <v>460</v>
       </c>
     </row>
     <row r="20">
@@ -19681,7 +20716,7 @@
         <v>1</v>
       </c>
       <c r="P20" s="0" t="s">
-        <v>116</v>
+        <v>461</v>
       </c>
     </row>
     <row r="21">
@@ -19731,7 +20766,7 @@
         <v>1</v>
       </c>
       <c r="P21" s="0" t="s">
-        <v>117</v>
+        <v>462</v>
       </c>
     </row>
     <row r="22">
@@ -19763,7 +20798,7 @@
         <v>1</v>
       </c>
       <c r="J22" s="0">
-        <v>1734.3440438348966</v>
+        <v>1734.3440438348973</v>
       </c>
       <c r="K22" s="0">
         <v>0.98840687198923027</v>
@@ -19781,7 +20816,7 @@
         <v>1</v>
       </c>
       <c r="P22" s="0" t="s">
-        <v>120</v>
+        <v>465</v>
       </c>
     </row>
     <row r="23">
@@ -19813,7 +20848,7 @@
         <v>1</v>
       </c>
       <c r="J23" s="0">
-        <v>30.482339810018175</v>
+        <v>30.482339810018182</v>
       </c>
       <c r="K23" s="0">
         <v>0.91343665817982434</v>
@@ -19831,7 +20866,7 @@
         <v>1</v>
       </c>
       <c r="P23" s="0" t="s">
-        <v>121</v>
+        <v>466</v>
       </c>
     </row>
     <row r="24">
@@ -19881,7 +20916,7 @@
         <v>1</v>
       </c>
       <c r="P24" s="0" t="s">
-        <v>122</v>
+        <v>467</v>
       </c>
     </row>
     <row r="25">
@@ -19931,7 +20966,7 @@
         <v>1</v>
       </c>
       <c r="P25" s="0" t="s">
-        <v>123</v>
+        <v>468</v>
       </c>
     </row>
     <row r="26">
@@ -19981,7 +21016,7 @@
         <v>1</v>
       </c>
       <c r="P26" s="0" t="s">
-        <v>124</v>
+        <v>469</v>
       </c>
     </row>
     <row r="27">
@@ -20031,7 +21066,7 @@
         <v>1</v>
       </c>
       <c r="P27" s="0" t="s">
-        <v>125</v>
+        <v>470</v>
       </c>
     </row>
     <row r="28">
@@ -20081,7 +21116,7 @@
         <v>1</v>
       </c>
       <c r="P28" s="0" t="s">
-        <v>127</v>
+        <v>472</v>
       </c>
     </row>
     <row r="29">
@@ -20131,7 +21166,7 @@
         <v>1</v>
       </c>
       <c r="P29" s="0" t="s">
-        <v>128</v>
+        <v>473</v>
       </c>
     </row>
     <row r="30">
@@ -20163,10 +21198,10 @@
         <v>1</v>
       </c>
       <c r="J30" s="0">
-        <v>1579.9052222710552</v>
+        <v>1579.905222271055</v>
       </c>
       <c r="K30" s="0">
-        <v>0.98483067773479882</v>
+        <v>0.98483067773479893</v>
       </c>
       <c r="L30" s="0">
         <v>61</v>
@@ -20181,7 +21216,7 @@
         <v>1</v>
       </c>
       <c r="P30" s="0" t="s">
-        <v>129</v>
+        <v>474</v>
       </c>
     </row>
     <row r="31">
@@ -20231,7 +21266,7 @@
         <v>1</v>
       </c>
       <c r="P31" s="0" t="s">
-        <v>130</v>
+        <v>475</v>
       </c>
     </row>
     <row r="32">
@@ -20281,7 +21316,7 @@
         <v>1</v>
       </c>
       <c r="P32" s="0" t="s">
-        <v>131</v>
+        <v>476</v>
       </c>
     </row>
     <row r="33">
@@ -20313,7 +21348,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="0">
-        <v>1626.3766943661206</v>
+        <v>1626.3766943661203</v>
       </c>
       <c r="K33" s="0">
         <v>0.99590425748323641</v>
@@ -20331,7 +21366,7 @@
         <v>1</v>
       </c>
       <c r="P33" s="0" t="s">
-        <v>132</v>
+        <v>477</v>
       </c>
     </row>
     <row r="34">
@@ -20381,7 +21416,7 @@
         <v>1</v>
       </c>
       <c r="P34" s="0" t="s">
-        <v>133</v>
+        <v>478</v>
       </c>
     </row>
     <row r="35">
@@ -20413,7 +21448,7 @@
         <v>1</v>
       </c>
       <c r="J35" s="0">
-        <v>1773.8686804768158</v>
+        <v>1773.8686804768167</v>
       </c>
       <c r="K35" s="0">
         <v>0.99904095147569161</v>
@@ -20431,7 +21466,7 @@
         <v>1</v>
       </c>
       <c r="P35" s="0" t="s">
-        <v>134</v>
+        <v>479</v>
       </c>
     </row>
     <row r="36">
@@ -20481,7 +21516,7 @@
         <v>1</v>
       </c>
       <c r="P36" s="0" t="s">
-        <v>135</v>
+        <v>480</v>
       </c>
     </row>
     <row r="37">
@@ -20531,7 +21566,7 @@
         <v>1</v>
       </c>
       <c r="P37" s="0" t="s">
-        <v>136</v>
+        <v>481</v>
       </c>
     </row>
     <row r="38">
@@ -20581,7 +21616,7 @@
         <v>1</v>
       </c>
       <c r="P38" s="0" t="s">
-        <v>137</v>
+        <v>482</v>
       </c>
     </row>
     <row r="39">
@@ -20631,7 +21666,7 @@
         <v>1</v>
       </c>
       <c r="P39" s="0" t="s">
-        <v>138</v>
+        <v>483</v>
       </c>
     </row>
     <row r="40">
@@ -20663,7 +21698,7 @@
         <v>1</v>
       </c>
       <c r="J40" s="0">
-        <v>2547.0621177642893</v>
+        <v>2547.0621177642888</v>
       </c>
       <c r="K40" s="0">
         <v>0.98728757077028462</v>
@@ -20681,7 +21716,7 @@
         <v>1</v>
       </c>
       <c r="P40" s="0" t="s">
-        <v>139</v>
+        <v>484</v>
       </c>
     </row>
     <row r="41">
@@ -20713,10 +21748,10 @@
         <v>1</v>
       </c>
       <c r="J41" s="0">
-        <v>661.15277973713592</v>
+        <v>661.15277973713546</v>
       </c>
       <c r="K41" s="0">
-        <v>0.97719631778190896</v>
+        <v>0.97719631778190885</v>
       </c>
       <c r="L41" s="0">
         <v>10</v>
@@ -20731,7 +21766,7 @@
         <v>1</v>
       </c>
       <c r="P41" s="0" t="s">
-        <v>140</v>
+        <v>485</v>
       </c>
     </row>
     <row r="42">
@@ -20763,7 +21798,7 @@
         <v>1</v>
       </c>
       <c r="J42" s="0">
-        <v>410.11071230444912</v>
+        <v>410.11071230444918</v>
       </c>
       <c r="K42" s="0">
         <v>0.9970395924818376</v>
@@ -20781,7 +21816,7 @@
         <v>1</v>
       </c>
       <c r="P42" s="0" t="s">
-        <v>141</v>
+        <v>486</v>
       </c>
     </row>
     <row r="43">
@@ -20831,7 +21866,7 @@
         <v>1</v>
       </c>
       <c r="P43" s="0" t="s">
-        <v>144</v>
+        <v>489</v>
       </c>
     </row>
     <row r="44">
@@ -20881,7 +21916,7 @@
         <v>1</v>
       </c>
       <c r="P44" s="0" t="s">
-        <v>145</v>
+        <v>490</v>
       </c>
     </row>
     <row r="45">
@@ -20931,7 +21966,7 @@
         <v>1</v>
       </c>
       <c r="P45" s="0" t="s">
-        <v>147</v>
+        <v>492</v>
       </c>
     </row>
     <row r="46">
@@ -20963,7 +21998,7 @@
         <v>1</v>
       </c>
       <c r="J46" s="0">
-        <v>1221.4178403983819</v>
+        <v>1221.4178403983815</v>
       </c>
       <c r="K46" s="0">
         <v>0.98234377379553039</v>
@@ -20981,7 +22016,7 @@
         <v>1</v>
       </c>
       <c r="P46" s="0" t="s">
-        <v>148</v>
+        <v>493</v>
       </c>
     </row>
     <row r="47">
@@ -21013,7 +22048,7 @@
         <v>1</v>
       </c>
       <c r="J47" s="0">
-        <v>1221.7889918170797</v>
+        <v>1221.788991817079</v>
       </c>
       <c r="K47" s="0">
         <v>0.99687357789713227</v>
@@ -21031,7 +22066,7 @@
         <v>1</v>
       </c>
       <c r="P47" s="0" t="s">
-        <v>149</v>
+        <v>494</v>
       </c>
     </row>
     <row r="48">
@@ -21063,7 +22098,7 @@
         <v>1</v>
       </c>
       <c r="J48" s="0">
-        <v>1513.2397793772052</v>
+        <v>1513.2397793772054</v>
       </c>
       <c r="K48" s="0">
         <v>0.99808716542823806</v>
@@ -21081,7 +22116,7 @@
         <v>1</v>
       </c>
       <c r="P48" s="0" t="s">
-        <v>150</v>
+        <v>495</v>
       </c>
     </row>
     <row r="49">
@@ -21131,7 +22166,7 @@
         <v>1</v>
       </c>
       <c r="P49" s="0" t="s">
-        <v>151</v>
+        <v>496</v>
       </c>
     </row>
     <row r="50">
@@ -21181,7 +22216,7 @@
         <v>1</v>
       </c>
       <c r="P50" s="0" t="s">
-        <v>152</v>
+        <v>497</v>
       </c>
     </row>
     <row r="51">
@@ -21213,7 +22248,7 @@
         <v>1</v>
       </c>
       <c r="J51" s="0">
-        <v>1501.9149999033621</v>
+        <v>1501.9149999033616</v>
       </c>
       <c r="K51" s="0">
         <v>0.9937649828049917</v>
@@ -21231,7 +22266,7 @@
         <v>1</v>
       </c>
       <c r="P51" s="0" t="s">
-        <v>153</v>
+        <v>498</v>
       </c>
     </row>
     <row r="52">
@@ -21263,7 +22298,7 @@
         <v>1</v>
       </c>
       <c r="J52" s="0">
-        <v>1957.5180273677322</v>
+        <v>1957.5180273677331</v>
       </c>
       <c r="K52" s="0">
         <v>0.99272218047441951</v>
@@ -21281,7 +22316,7 @@
         <v>1</v>
       </c>
       <c r="P52" s="0" t="s">
-        <v>155</v>
+        <v>500</v>
       </c>
     </row>
     <row r="53">
@@ -21331,7 +22366,7 @@
         <v>1</v>
       </c>
       <c r="P53" s="0" t="s">
-        <v>156</v>
+        <v>501</v>
       </c>
     </row>
     <row r="54">
@@ -21381,7 +22416,7 @@
         <v>1</v>
       </c>
       <c r="P54" s="0" t="s">
-        <v>157</v>
+        <v>502</v>
       </c>
     </row>
     <row r="55">
@@ -21413,7 +22448,7 @@
         <v>1</v>
       </c>
       <c r="J55" s="0">
-        <v>965.24514797176607</v>
+        <v>965.24514797176596</v>
       </c>
       <c r="K55" s="0">
         <v>0.93672171151202366</v>
@@ -21431,7 +22466,7 @@
         <v>1</v>
       </c>
       <c r="P55" s="0" t="s">
-        <v>158</v>
+        <v>503</v>
       </c>
     </row>
     <row r="56">
@@ -21481,7 +22516,7 @@
         <v>1</v>
       </c>
       <c r="P56" s="0" t="s">
-        <v>159</v>
+        <v>504</v>
       </c>
     </row>
     <row r="57">
@@ -21513,7 +22548,7 @@
         <v>1</v>
       </c>
       <c r="J57" s="0">
-        <v>848.28858262813799</v>
+        <v>848.2885826281381</v>
       </c>
       <c r="K57" s="0">
         <v>0.99868044006558299</v>
@@ -21531,7 +22566,7 @@
         <v>1</v>
       </c>
       <c r="P57" s="0" t="s">
-        <v>160</v>
+        <v>505</v>
       </c>
     </row>
     <row r="58">
@@ -21581,7 +22616,7 @@
         <v>1</v>
       </c>
       <c r="P58" s="0" t="s">
-        <v>161</v>
+        <v>506</v>
       </c>
     </row>
     <row r="59">
@@ -21631,7 +22666,7 @@
         <v>1</v>
       </c>
       <c r="P59" s="0" t="s">
-        <v>162</v>
+        <v>507</v>
       </c>
     </row>
     <row r="60">
@@ -21681,7 +22716,7 @@
         <v>1</v>
       </c>
       <c r="P60" s="0" t="s">
-        <v>163</v>
+        <v>508</v>
       </c>
     </row>
     <row r="61">
@@ -21713,7 +22748,7 @@
         <v>1</v>
       </c>
       <c r="J61" s="0">
-        <v>2205.8138631608372</v>
+        <v>2205.8138631608363</v>
       </c>
       <c r="K61" s="0">
         <v>0.99856334426500071</v>
@@ -21731,7 +22766,7 @@
         <v>1</v>
       </c>
       <c r="P61" s="0" t="s">
-        <v>164</v>
+        <v>509</v>
       </c>
     </row>
     <row r="62">
@@ -21763,7 +22798,7 @@
         <v>1</v>
       </c>
       <c r="J62" s="0">
-        <v>2570.9266181484913</v>
+        <v>2570.92661814849</v>
       </c>
       <c r="K62" s="0">
         <v>0.9955328474633357</v>
@@ -21781,7 +22816,7 @@
         <v>1</v>
       </c>
       <c r="P62" s="0" t="s">
-        <v>165</v>
+        <v>510</v>
       </c>
     </row>
     <row r="63">
@@ -21813,7 +22848,7 @@
         <v>1</v>
       </c>
       <c r="J63" s="0">
-        <v>1532.77289006665</v>
+        <v>1532.7728900666498</v>
       </c>
       <c r="K63" s="0">
         <v>0.99585654454348238</v>
@@ -21831,7 +22866,7 @@
         <v>1</v>
       </c>
       <c r="P63" s="0" t="s">
-        <v>166</v>
+        <v>511</v>
       </c>
     </row>
     <row r="64">
@@ -21881,7 +22916,7 @@
         <v>1</v>
       </c>
       <c r="P64" s="0" t="s">
-        <v>167</v>
+        <v>512</v>
       </c>
     </row>
     <row r="65">
@@ -21913,7 +22948,7 @@
         <v>1</v>
       </c>
       <c r="J65" s="0">
-        <v>2096.176488720449</v>
+        <v>2096.1764887204499</v>
       </c>
       <c r="K65" s="0">
         <v>0.99898513717814475</v>
@@ -21931,7 +22966,7 @@
         <v>1</v>
       </c>
       <c r="P65" s="0" t="s">
-        <v>168</v>
+        <v>513</v>
       </c>
     </row>
     <row r="66">
@@ -21981,7 +23016,7 @@
         <v>1</v>
       </c>
       <c r="P66" s="0" t="s">
-        <v>169</v>
+        <v>514</v>
       </c>
     </row>
     <row r="67">
@@ -22031,7 +23066,7 @@
         <v>1</v>
       </c>
       <c r="P67" s="0" t="s">
-        <v>170</v>
+        <v>515</v>
       </c>
     </row>
     <row r="68">
@@ -22063,7 +23098,7 @@
         <v>1</v>
       </c>
       <c r="J68" s="0">
-        <v>1652.0346967697353</v>
+        <v>1652.0346967697349</v>
       </c>
       <c r="K68" s="0">
         <v>0.99647618341908739</v>
@@ -22081,7 +23116,7 @@
         <v>1</v>
       </c>
       <c r="P68" s="0" t="s">
-        <v>171</v>
+        <v>516</v>
       </c>
     </row>
     <row r="69">
@@ -22131,7 +23166,7 @@
         <v>1</v>
       </c>
       <c r="P69" s="0" t="s">
-        <v>172</v>
+        <v>517</v>
       </c>
     </row>
     <row r="70">
@@ -22181,7 +23216,7 @@
         <v>1</v>
       </c>
       <c r="P70" s="0" t="s">
-        <v>173</v>
+        <v>518</v>
       </c>
     </row>
     <row r="71">
@@ -22231,7 +23266,7 @@
         <v>1</v>
       </c>
       <c r="P71" s="0" t="s">
-        <v>174</v>
+        <v>519</v>
       </c>
     </row>
     <row r="72">
@@ -22281,7 +23316,7 @@
         <v>1</v>
       </c>
       <c r="P72" s="0" t="s">
-        <v>175</v>
+        <v>520</v>
       </c>
     </row>
     <row r="73">
@@ -22313,7 +23348,7 @@
         <v>1</v>
       </c>
       <c r="J73" s="0">
-        <v>1865.4262458669398</v>
+        <v>1865.4262458669396</v>
       </c>
       <c r="K73" s="0">
         <v>0.99891606336650685</v>
@@ -22331,7 +23366,7 @@
         <v>1</v>
       </c>
       <c r="P73" s="0" t="s">
-        <v>176</v>
+        <v>521</v>
       </c>
     </row>
     <row r="74">
@@ -22381,7 +23416,7 @@
         <v>1</v>
       </c>
       <c r="P74" s="0" t="s">
-        <v>177</v>
+        <v>522</v>
       </c>
     </row>
     <row r="75">
@@ -22413,7 +23448,7 @@
         <v>1</v>
       </c>
       <c r="J75" s="0">
-        <v>1886.2575892376642</v>
+        <v>1886.2575892376635</v>
       </c>
       <c r="K75" s="0">
         <v>0.99855474168079894</v>
@@ -22431,7 +23466,7 @@
         <v>1</v>
       </c>
       <c r="P75" s="0" t="s">
-        <v>178</v>
+        <v>523</v>
       </c>
     </row>
     <row r="76">
@@ -22481,7 +23516,7 @@
         <v>1</v>
       </c>
       <c r="P76" s="0" t="s">
-        <v>179</v>
+        <v>524</v>
       </c>
     </row>
     <row r="77">
@@ -22513,7 +23548,7 @@
         <v>1</v>
       </c>
       <c r="J77" s="0">
-        <v>2415.0999901258906</v>
+        <v>2415.0999901258897</v>
       </c>
       <c r="K77" s="0">
         <v>0.99813014732030969</v>
@@ -22531,7 +23566,7 @@
         <v>1</v>
       </c>
       <c r="P77" s="0" t="s">
-        <v>180</v>
+        <v>525</v>
       </c>
     </row>
     <row r="78">
@@ -22563,7 +23598,7 @@
         <v>1</v>
       </c>
       <c r="J78" s="0">
-        <v>2259.2010433261521</v>
+        <v>2259.2010433261526</v>
       </c>
       <c r="K78" s="0">
         <v>0.99728639202050262</v>
@@ -22581,7 +23616,7 @@
         <v>1</v>
       </c>
       <c r="P78" s="0" t="s">
-        <v>181</v>
+        <v>526</v>
       </c>
     </row>
     <row r="79">
@@ -22631,7 +23666,7 @@
         <v>1</v>
       </c>
       <c r="P79" s="0" t="s">
-        <v>182</v>
+        <v>527</v>
       </c>
     </row>
     <row r="80">
@@ -22663,7 +23698,7 @@
         <v>1</v>
       </c>
       <c r="J80" s="0">
-        <v>1913.6401189378073</v>
+        <v>1913.640118937808</v>
       </c>
       <c r="K80" s="0">
         <v>0.99464925416056194</v>
@@ -22681,7 +23716,7 @@
         <v>1</v>
       </c>
       <c r="P80" s="0" t="s">
-        <v>183</v>
+        <v>528</v>
       </c>
     </row>
     <row r="81">
@@ -22731,7 +23766,7 @@
         <v>1</v>
       </c>
       <c r="P81" s="0" t="s">
-        <v>184</v>
+        <v>529</v>
       </c>
     </row>
     <row r="82">
@@ -22763,7 +23798,7 @@
         <v>1</v>
       </c>
       <c r="J82" s="0">
-        <v>2162.0251268629399</v>
+        <v>2162.025126862939</v>
       </c>
       <c r="K82" s="0">
         <v>0.99752640066888976</v>
@@ -22781,7 +23816,7 @@
         <v>1</v>
       </c>
       <c r="P82" s="0" t="s">
-        <v>185</v>
+        <v>530</v>
       </c>
     </row>
     <row r="83">
@@ -22813,7 +23848,7 @@
         <v>1</v>
       </c>
       <c r="J83" s="0">
-        <v>1763.6262685179177</v>
+        <v>1763.6262685179174</v>
       </c>
       <c r="K83" s="0">
         <v>0.9987963878643974</v>
@@ -22831,7 +23866,7 @@
         <v>1</v>
       </c>
       <c r="P83" s="0" t="s">
-        <v>186</v>
+        <v>531</v>
       </c>
     </row>
     <row r="84">
@@ -22881,7 +23916,7 @@
         <v>1</v>
       </c>
       <c r="P84" s="0" t="s">
-        <v>187</v>
+        <v>532</v>
       </c>
     </row>
     <row r="85">
@@ -22931,7 +23966,7 @@
         <v>1</v>
       </c>
       <c r="P85" s="0" t="s">
-        <v>188</v>
+        <v>533</v>
       </c>
     </row>
     <row r="86">
@@ -22981,7 +24016,7 @@
         <v>1</v>
       </c>
       <c r="P86" s="0" t="s">
-        <v>189</v>
+        <v>534</v>
       </c>
     </row>
     <row r="87">
@@ -23031,7 +24066,7 @@
         <v>1</v>
       </c>
       <c r="P87" s="0" t="s">
-        <v>190</v>
+        <v>535</v>
       </c>
     </row>
     <row r="88">
@@ -23063,7 +24098,7 @@
         <v>1</v>
       </c>
       <c r="J88" s="0">
-        <v>1375.0681772061591</v>
+        <v>1375.0681772061589</v>
       </c>
       <c r="K88" s="0">
         <v>0.99863899384873867</v>
@@ -23081,7 +24116,7 @@
         <v>1</v>
       </c>
       <c r="P88" s="0" t="s">
-        <v>191</v>
+        <v>536</v>
       </c>
     </row>
     <row r="89">
@@ -23113,7 +24148,7 @@
         <v>1</v>
       </c>
       <c r="J89" s="0">
-        <v>2833.3640217794336</v>
+        <v>2833.3640217794332</v>
       </c>
       <c r="K89" s="0">
         <v>0.99610968578678283</v>
@@ -23131,7 +24166,7 @@
         <v>1</v>
       </c>
       <c r="P89" s="0" t="s">
-        <v>192</v>
+        <v>537</v>
       </c>
     </row>
     <row r="90">
@@ -23181,7 +24216,7 @@
         <v>1</v>
       </c>
       <c r="P90" s="0" t="s">
-        <v>193</v>
+        <v>538</v>
       </c>
     </row>
     <row r="91">
@@ -23213,7 +24248,7 @@
         <v>1</v>
       </c>
       <c r="J91" s="0">
-        <v>633.64562852100642</v>
+        <v>633.6456285210063</v>
       </c>
       <c r="K91" s="0">
         <v>0.99171960836137507</v>
@@ -23231,7 +24266,7 @@
         <v>1</v>
       </c>
       <c r="P91" s="0" t="s">
-        <v>194</v>
+        <v>539</v>
       </c>
     </row>
     <row r="92">
@@ -23263,7 +24298,7 @@
         <v>1</v>
       </c>
       <c r="J92" s="0">
-        <v>1229.6089370907914</v>
+        <v>1229.6089370907905</v>
       </c>
       <c r="K92" s="0">
         <v>0.99134266664328308</v>
@@ -23281,7 +24316,7 @@
         <v>1</v>
       </c>
       <c r="P92" s="0" t="s">
-        <v>197</v>
+        <v>542</v>
       </c>
     </row>
     <row r="93">
@@ -23313,7 +24348,7 @@
         <v>1</v>
       </c>
       <c r="J93" s="0">
-        <v>1910.12507526124</v>
+        <v>1910.1250752612396</v>
       </c>
       <c r="K93" s="0">
         <v>0.99808579308196443</v>
@@ -23331,7 +24366,7 @@
         <v>1</v>
       </c>
       <c r="P93" s="0" t="s">
-        <v>198</v>
+        <v>543</v>
       </c>
     </row>
     <row r="94">
@@ -23363,7 +24398,7 @@
         <v>1</v>
       </c>
       <c r="J94" s="0">
-        <v>664.83588567874654</v>
+        <v>664.83588567874665</v>
       </c>
       <c r="K94" s="0">
         <v>0.99702641881935639</v>
@@ -23381,7 +24416,7 @@
         <v>1</v>
       </c>
       <c r="P94" s="0" t="s">
-        <v>200</v>
+        <v>545</v>
       </c>
     </row>
     <row r="95">
@@ -23413,7 +24448,7 @@
         <v>1</v>
       </c>
       <c r="J95" s="0">
-        <v>1938.4777163485373</v>
+        <v>1938.4777163485369</v>
       </c>
       <c r="K95" s="0">
         <v>0.99628352391200414</v>
@@ -23431,7 +24466,7 @@
         <v>1</v>
       </c>
       <c r="P95" s="0" t="s">
-        <v>201</v>
+        <v>546</v>
       </c>
     </row>
     <row r="96">
@@ -23481,7 +24516,7 @@
         <v>1</v>
       </c>
       <c r="P96" s="0" t="s">
-        <v>202</v>
+        <v>547</v>
       </c>
     </row>
     <row r="97">
@@ -23531,7 +24566,7 @@
         <v>1</v>
       </c>
       <c r="P97" s="0" t="s">
-        <v>203</v>
+        <v>548</v>
       </c>
     </row>
     <row r="98">
@@ -23563,7 +24598,7 @@
         <v>1</v>
       </c>
       <c r="J98" s="0">
-        <v>793.91322499029854</v>
+        <v>793.91322499029809</v>
       </c>
       <c r="K98" s="0">
         <v>0.98874043350771046</v>
@@ -23581,7 +24616,7 @@
         <v>1</v>
       </c>
       <c r="P98" s="0" t="s">
-        <v>204</v>
+        <v>549</v>
       </c>
     </row>
     <row r="99">
@@ -23631,7 +24666,7 @@
         <v>1</v>
       </c>
       <c r="P99" s="0" t="s">
-        <v>205</v>
+        <v>550</v>
       </c>
     </row>
     <row r="100">
@@ -23681,7 +24716,7 @@
         <v>1</v>
       </c>
       <c r="P100" s="0" t="s">
-        <v>206</v>
+        <v>551</v>
       </c>
     </row>
     <row r="101">
@@ -23731,7 +24766,7 @@
         <v>1</v>
       </c>
       <c r="P101" s="0" t="s">
-        <v>207</v>
+        <v>552</v>
       </c>
     </row>
     <row r="102">
@@ -23763,7 +24798,7 @@
         <v>1</v>
       </c>
       <c r="J102" s="0">
-        <v>1369.3777090845317</v>
+        <v>1369.377709084532</v>
       </c>
       <c r="K102" s="0">
         <v>0.96852539418740868</v>
@@ -23781,7 +24816,7 @@
         <v>1</v>
       </c>
       <c r="P102" s="0" t="s">
-        <v>209</v>
+        <v>554</v>
       </c>
     </row>
     <row r="103">
@@ -23831,7 +24866,7 @@
         <v>1</v>
       </c>
       <c r="P103" s="0" t="s">
-        <v>210</v>
+        <v>555</v>
       </c>
     </row>
     <row r="104">
@@ -23863,7 +24898,7 @@
         <v>1</v>
       </c>
       <c r="J104" s="0">
-        <v>1258.2883952862558</v>
+        <v>1258.288395286256</v>
       </c>
       <c r="K104" s="0">
         <v>0.98999036685482322</v>
@@ -23881,7 +24916,7 @@
         <v>1</v>
       </c>
       <c r="P104" s="0" t="s">
-        <v>211</v>
+        <v>556</v>
       </c>
     </row>
     <row r="105">
@@ -23931,7 +24966,7 @@
         <v>1</v>
       </c>
       <c r="P105" s="0" t="s">
-        <v>212</v>
+        <v>557</v>
       </c>
     </row>
     <row r="106">
@@ -23963,7 +24998,7 @@
         <v>1</v>
       </c>
       <c r="J106" s="0">
-        <v>926.95175513804259</v>
+        <v>926.95175513804236</v>
       </c>
       <c r="K106" s="0">
         <v>0.97991806331277287</v>
@@ -23981,7 +25016,7 @@
         <v>1</v>
       </c>
       <c r="P106" s="0" t="s">
-        <v>213</v>
+        <v>558</v>
       </c>
     </row>
     <row r="107">
@@ -24031,7 +25066,7 @@
         <v>1</v>
       </c>
       <c r="P107" s="0" t="s">
-        <v>214</v>
+        <v>559</v>
       </c>
     </row>
     <row r="108">
@@ -24081,7 +25116,7 @@
         <v>1</v>
       </c>
       <c r="P108" s="0" t="s">
-        <v>215</v>
+        <v>560</v>
       </c>
     </row>
     <row r="109">
@@ -24131,7 +25166,7 @@
         <v>1</v>
       </c>
       <c r="P109" s="0" t="s">
-        <v>216</v>
+        <v>561</v>
       </c>
     </row>
     <row r="110">
@@ -24181,7 +25216,7 @@
         <v>1</v>
       </c>
       <c r="P110" s="0" t="s">
-        <v>217</v>
+        <v>562</v>
       </c>
     </row>
     <row r="111">
@@ -24231,7 +25266,7 @@
         <v>1</v>
       </c>
       <c r="P111" s="0" t="s">
-        <v>218</v>
+        <v>563</v>
       </c>
     </row>
     <row r="112">
@@ -24263,7 +25298,7 @@
         <v>1</v>
       </c>
       <c r="J112" s="0">
-        <v>1786.6511653536056</v>
+        <v>1786.6511653536054</v>
       </c>
       <c r="K112" s="0">
         <v>0.98558158596822099</v>
@@ -24281,7 +25316,7 @@
         <v>1</v>
       </c>
       <c r="P112" s="0" t="s">
-        <v>219</v>
+        <v>564</v>
       </c>
     </row>
     <row r="113">
@@ -24313,7 +25348,7 @@
         <v>1</v>
       </c>
       <c r="J113" s="0">
-        <v>1639.3717147377795</v>
+        <v>1639.3717147377788</v>
       </c>
       <c r="K113" s="0">
         <v>0.99955157487274549</v>
@@ -24331,7 +25366,7 @@
         <v>1</v>
       </c>
       <c r="P113" s="0" t="s">
-        <v>220</v>
+        <v>565</v>
       </c>
     </row>
     <row r="114">
@@ -24381,7 +25416,7 @@
         <v>1</v>
       </c>
       <c r="P114" s="0" t="s">
-        <v>221</v>
+        <v>566</v>
       </c>
     </row>
     <row r="115">
@@ -24413,7 +25448,7 @@
         <v>1</v>
       </c>
       <c r="J115" s="0">
-        <v>2623.734741902274</v>
+        <v>2623.7347419022735</v>
       </c>
       <c r="K115" s="0">
         <v>0.9944157937375373</v>
@@ -24431,7 +25466,7 @@
         <v>1</v>
       </c>
       <c r="P115" s="0" t="s">
-        <v>222</v>
+        <v>567</v>
       </c>
     </row>
     <row r="116">
@@ -24463,7 +25498,7 @@
         <v>1</v>
       </c>
       <c r="J116" s="0">
-        <v>1360.8128554388545</v>
+        <v>1360.8128554388543</v>
       </c>
       <c r="K116" s="0">
         <v>0.99110679854132122</v>
@@ -24481,7 +25516,7 @@
         <v>1</v>
       </c>
       <c r="P116" s="0" t="s">
-        <v>223</v>
+        <v>568</v>
       </c>
     </row>
     <row r="117">
@@ -24531,7 +25566,7 @@
         <v>1</v>
       </c>
       <c r="P117" s="0" t="s">
-        <v>224</v>
+        <v>569</v>
       </c>
     </row>
     <row r="118">
@@ -24581,7 +25616,7 @@
         <v>1</v>
       </c>
       <c r="P118" s="0" t="s">
-        <v>225</v>
+        <v>570</v>
       </c>
     </row>
     <row r="119">
@@ -24631,7 +25666,7 @@
         <v>1</v>
       </c>
       <c r="P119" s="0" t="s">
-        <v>226</v>
+        <v>571</v>
       </c>
     </row>
     <row r="120">
@@ -24666,7 +25701,7 @@
         <v>1597.8522936150403</v>
       </c>
       <c r="K120" s="0">
-        <v>0.991332106869937</v>
+        <v>0.99133210686993689</v>
       </c>
       <c r="L120" s="0">
         <v>59</v>
@@ -24681,7 +25716,7 @@
         <v>1</v>
       </c>
       <c r="P120" s="0" t="s">
-        <v>227</v>
+        <v>572</v>
       </c>
     </row>
     <row r="121">
@@ -24731,7 +25766,7 @@
         <v>1</v>
       </c>
       <c r="P121" s="0" t="s">
-        <v>228</v>
+        <v>573</v>
       </c>
     </row>
     <row r="122">
@@ -24781,7 +25816,7 @@
         <v>1</v>
       </c>
       <c r="P122" s="0" t="s">
-        <v>229</v>
+        <v>574</v>
       </c>
     </row>
     <row r="123">
@@ -24813,7 +25848,7 @@
         <v>1</v>
       </c>
       <c r="J123" s="0">
-        <v>1710.9126759468113</v>
+        <v>1710.9126759468109</v>
       </c>
       <c r="K123" s="0">
         <v>0.99940800704431654</v>
@@ -24831,7 +25866,7 @@
         <v>1</v>
       </c>
       <c r="P123" s="0" t="s">
-        <v>230</v>
+        <v>575</v>
       </c>
     </row>
     <row r="124">
@@ -24881,7 +25916,7 @@
         <v>1</v>
       </c>
       <c r="P124" s="0" t="s">
-        <v>231</v>
+        <v>576</v>
       </c>
     </row>
     <row r="125">
@@ -24931,7 +25966,7 @@
         <v>1</v>
       </c>
       <c r="P125" s="0" t="s">
-        <v>232</v>
+        <v>577</v>
       </c>
     </row>
     <row r="126">
@@ -24963,7 +25998,7 @@
         <v>1</v>
       </c>
       <c r="J126" s="0">
-        <v>1478.7946090480507</v>
+        <v>1478.7946090480509</v>
       </c>
       <c r="K126" s="0">
         <v>0.99616361326427849</v>
@@ -24981,7 +26016,7 @@
         <v>1</v>
       </c>
       <c r="P126" s="0" t="s">
-        <v>233</v>
+        <v>578</v>
       </c>
     </row>
     <row r="127">
@@ -25031,7 +26066,7 @@
         <v>1</v>
       </c>
       <c r="P127" s="0" t="s">
-        <v>234</v>
+        <v>579</v>
       </c>
     </row>
     <row r="128">
@@ -25081,7 +26116,7 @@
         <v>1</v>
       </c>
       <c r="P128" s="0" t="s">
-        <v>235</v>
+        <v>580</v>
       </c>
     </row>
     <row r="129">
@@ -25131,7 +26166,7 @@
         <v>1</v>
       </c>
       <c r="P129" s="0" t="s">
-        <v>236</v>
+        <v>581</v>
       </c>
     </row>
     <row r="130">
@@ -25163,7 +26198,7 @@
         <v>1</v>
       </c>
       <c r="J130" s="0">
-        <v>1274.171945561724</v>
+        <v>1274.1719455617238</v>
       </c>
       <c r="K130" s="0">
         <v>0.9991382800326245</v>
@@ -25181,7 +26216,7 @@
         <v>1</v>
       </c>
       <c r="P130" s="0" t="s">
-        <v>237</v>
+        <v>582</v>
       </c>
     </row>
     <row r="131">
@@ -25213,7 +26248,7 @@
         <v>1</v>
       </c>
       <c r="J131" s="0">
-        <v>1900.0974708825636</v>
+        <v>1900.0974708825634</v>
       </c>
       <c r="K131" s="0">
         <v>0.99728616615662558</v>
@@ -25231,7 +26266,7 @@
         <v>1</v>
       </c>
       <c r="P131" s="0" t="s">
-        <v>238</v>
+        <v>583</v>
       </c>
     </row>
     <row r="132">
@@ -25281,7 +26316,7 @@
         <v>1</v>
       </c>
       <c r="P132" s="0" t="s">
-        <v>239</v>
+        <v>584</v>
       </c>
     </row>
     <row r="133">
@@ -25331,7 +26366,7 @@
         <v>1</v>
       </c>
       <c r="P133" s="0" t="s">
-        <v>240</v>
+        <v>585</v>
       </c>
     </row>
     <row r="134">
@@ -25363,7 +26398,7 @@
         <v>1</v>
       </c>
       <c r="J134" s="0">
-        <v>1121.5213782616102</v>
+        <v>1121.5213782616097</v>
       </c>
       <c r="K134" s="0">
         <v>0.99887580468185711</v>
@@ -25381,7 +26416,7 @@
         <v>1</v>
       </c>
       <c r="P134" s="0" t="s">
-        <v>241</v>
+        <v>586</v>
       </c>
     </row>
     <row r="135">
@@ -25431,7 +26466,7 @@
         <v>1</v>
       </c>
       <c r="P135" s="0" t="s">
-        <v>242</v>
+        <v>587</v>
       </c>
     </row>
     <row r="136">
@@ -25466,7 +26501,7 @@
         <v>1138.8487655225947</v>
       </c>
       <c r="K136" s="0">
-        <v>0.98903905155448857</v>
+        <v>0.98903905155448868</v>
       </c>
       <c r="L136" s="0">
         <v>8</v>
@@ -25481,7 +26516,7 @@
         <v>1</v>
       </c>
       <c r="P136" s="0" t="s">
-        <v>243</v>
+        <v>588</v>
       </c>
     </row>
     <row r="137">
@@ -25513,7 +26548,7 @@
         <v>1</v>
       </c>
       <c r="J137" s="0">
-        <v>1825.9679400029324</v>
+        <v>1825.9679400029329</v>
       </c>
       <c r="K137" s="0">
         <v>0.99594007129911144</v>
@@ -25531,7 +26566,7 @@
         <v>1</v>
       </c>
       <c r="P137" s="0" t="s">
-        <v>244</v>
+        <v>589</v>
       </c>
     </row>
     <row r="138">
@@ -25581,7 +26616,7 @@
         <v>1</v>
       </c>
       <c r="P138" s="0" t="s">
-        <v>245</v>
+        <v>590</v>
       </c>
     </row>
     <row r="139">
@@ -25631,7 +26666,7 @@
         <v>1</v>
       </c>
       <c r="P139" s="0" t="s">
-        <v>246</v>
+        <v>591</v>
       </c>
     </row>
     <row r="140">
@@ -25663,7 +26698,7 @@
         <v>1</v>
       </c>
       <c r="J140" s="0">
-        <v>1258.4838810786696</v>
+        <v>1258.4838810786698</v>
       </c>
       <c r="K140" s="0">
         <v>0.98430666834940672</v>
@@ -25681,7 +26716,7 @@
         <v>1</v>
       </c>
       <c r="P140" s="0" t="s">
-        <v>247</v>
+        <v>592</v>
       </c>
     </row>
     <row r="141">
@@ -25731,7 +26766,7 @@
         <v>1</v>
       </c>
       <c r="P141" s="0" t="s">
-        <v>248</v>
+        <v>593</v>
       </c>
     </row>
     <row r="142">
@@ -25781,7 +26816,7 @@
         <v>1</v>
       </c>
       <c r="P142" s="0" t="s">
-        <v>249</v>
+        <v>594</v>
       </c>
     </row>
     <row r="143">
@@ -25831,7 +26866,7 @@
         <v>1</v>
       </c>
       <c r="P143" s="0" t="s">
-        <v>250</v>
+        <v>595</v>
       </c>
     </row>
     <row r="144">
@@ -25881,7 +26916,7 @@
         <v>1</v>
       </c>
       <c r="P144" s="0" t="s">
-        <v>251</v>
+        <v>596</v>
       </c>
     </row>
     <row r="145">
@@ -25931,7 +26966,7 @@
         <v>1</v>
       </c>
       <c r="P145" s="0" t="s">
-        <v>252</v>
+        <v>597</v>
       </c>
     </row>
     <row r="146">
@@ -25981,7 +27016,7 @@
         <v>1</v>
       </c>
       <c r="P146" s="0" t="s">
-        <v>253</v>
+        <v>598</v>
       </c>
     </row>
     <row r="147">
@@ -26013,7 +27048,7 @@
         <v>1</v>
       </c>
       <c r="J147" s="0">
-        <v>2203.8311405343493</v>
+        <v>2203.8311405343502</v>
       </c>
       <c r="K147" s="0">
         <v>0.9965320898337009</v>
@@ -26031,7 +27066,7 @@
         <v>1</v>
       </c>
       <c r="P147" s="0" t="s">
-        <v>254</v>
+        <v>599</v>
       </c>
     </row>
     <row r="148">
@@ -26081,7 +27116,7 @@
         <v>1</v>
       </c>
       <c r="P148" s="0" t="s">
-        <v>255</v>
+        <v>600</v>
       </c>
     </row>
     <row r="149">
@@ -26131,7 +27166,7 @@
         <v>1</v>
       </c>
       <c r="P149" s="0" t="s">
-        <v>257</v>
+        <v>602</v>
       </c>
     </row>
     <row r="150">
@@ -26163,7 +27198,7 @@
         <v>1</v>
       </c>
       <c r="J150" s="0">
-        <v>1096.4725247574447</v>
+        <v>1096.4725247574445</v>
       </c>
       <c r="K150" s="0">
         <v>0.99012845718378428</v>
@@ -26181,7 +27216,7 @@
         <v>1</v>
       </c>
       <c r="P150" s="0" t="s">
-        <v>258</v>
+        <v>603</v>
       </c>
     </row>
     <row r="151">
@@ -26231,7 +27266,7 @@
         <v>1</v>
       </c>
       <c r="P151" s="0" t="s">
-        <v>259</v>
+        <v>604</v>
       </c>
     </row>
     <row r="152">
@@ -26281,7 +27316,7 @@
         <v>1</v>
       </c>
       <c r="P152" s="0" t="s">
-        <v>260</v>
+        <v>605</v>
       </c>
     </row>
     <row r="153">
@@ -26313,7 +27348,7 @@
         <v>1</v>
       </c>
       <c r="J153" s="0">
-        <v>1258.4838810786696</v>
+        <v>1258.4838810786698</v>
       </c>
       <c r="K153" s="0">
         <v>0.98430666834940672</v>
@@ -26331,7 +27366,7 @@
         <v>1</v>
       </c>
       <c r="P153" s="0" t="s">
-        <v>261</v>
+        <v>606</v>
       </c>
     </row>
     <row r="154">
@@ -26381,7 +27416,7 @@
         <v>1</v>
       </c>
       <c r="P154" s="0" t="s">
-        <v>262</v>
+        <v>607</v>
       </c>
     </row>
     <row r="155">
@@ -26431,7 +27466,7 @@
         <v>1</v>
       </c>
       <c r="P155" s="0" t="s">
-        <v>263</v>
+        <v>608</v>
       </c>
     </row>
     <row r="156">
@@ -26481,7 +27516,7 @@
         <v>1</v>
       </c>
       <c r="P156" s="0" t="s">
-        <v>264</v>
+        <v>609</v>
       </c>
     </row>
     <row r="157">
@@ -26531,7 +27566,7 @@
         <v>1</v>
       </c>
       <c r="P157" s="0" t="s">
-        <v>265</v>
+        <v>610</v>
       </c>
     </row>
     <row r="158">
@@ -26581,7 +27616,7 @@
         <v>1</v>
       </c>
       <c r="P158" s="0" t="s">
-        <v>266</v>
+        <v>611</v>
       </c>
     </row>
     <row r="159">
@@ -26631,7 +27666,7 @@
         <v>1</v>
       </c>
       <c r="P159" s="0" t="s">
-        <v>267</v>
+        <v>612</v>
       </c>
     </row>
     <row r="160">
@@ -26663,7 +27698,7 @@
         <v>1</v>
       </c>
       <c r="J160" s="0">
-        <v>2203.8311405343493</v>
+        <v>2203.8311405343502</v>
       </c>
       <c r="K160" s="0">
         <v>0.9965320898337009</v>
@@ -26681,7 +27716,7 @@
         <v>1</v>
       </c>
       <c r="P160" s="0" t="s">
-        <v>268</v>
+        <v>613</v>
       </c>
     </row>
     <row r="161">
@@ -26731,7 +27766,7 @@
         <v>1</v>
       </c>
       <c r="P161" s="0" t="s">
-        <v>269</v>
+        <v>614</v>
       </c>
     </row>
     <row r="162">
@@ -26781,7 +27816,7 @@
         <v>1</v>
       </c>
       <c r="P162" s="0" t="s">
-        <v>271</v>
+        <v>616</v>
       </c>
     </row>
     <row r="163">
@@ -26831,7 +27866,7 @@
         <v>1</v>
       </c>
       <c r="P163" s="0" t="s">
-        <v>272</v>
+        <v>617</v>
       </c>
     </row>
     <row r="164">
@@ -26881,7 +27916,7 @@
         <v>1</v>
       </c>
       <c r="P164" s="0" t="s">
-        <v>273</v>
+        <v>618</v>
       </c>
     </row>
     <row r="165">
@@ -26913,7 +27948,7 @@
         <v>1</v>
       </c>
       <c r="J165" s="0">
-        <v>1056.3808174752112</v>
+        <v>1056.3808174752107</v>
       </c>
       <c r="K165" s="0">
         <v>0.94283269905406642</v>
@@ -26931,7 +27966,7 @@
         <v>1</v>
       </c>
       <c r="P165" s="0" t="s">
-        <v>274</v>
+        <v>619</v>
       </c>
     </row>
     <row r="166">
@@ -26981,7 +28016,7 @@
         <v>1</v>
       </c>
       <c r="P166" s="0" t="s">
-        <v>275</v>
+        <v>620</v>
       </c>
     </row>
     <row r="167">
@@ -27013,7 +28048,7 @@
         <v>1</v>
       </c>
       <c r="J167" s="0">
-        <v>1845.4900300889026</v>
+        <v>1845.4900300889033</v>
       </c>
       <c r="K167" s="0">
         <v>0.99472905346913398</v>
@@ -27031,7 +28066,7 @@
         <v>1</v>
       </c>
       <c r="P167" s="0" t="s">
-        <v>276</v>
+        <v>621</v>
       </c>
     </row>
     <row r="168">
@@ -27063,7 +28098,7 @@
         <v>1</v>
       </c>
       <c r="J168" s="0">
-        <v>2440.3213240975706</v>
+        <v>2440.3213240975715</v>
       </c>
       <c r="K168" s="0">
         <v>0.99730254767897886</v>
@@ -27081,7 +28116,7 @@
         <v>1</v>
       </c>
       <c r="P168" s="0" t="s">
-        <v>277</v>
+        <v>622</v>
       </c>
     </row>
     <row r="169">
@@ -27131,7 +28166,7 @@
         <v>1</v>
       </c>
       <c r="P169" s="0" t="s">
-        <v>278</v>
+        <v>623</v>
       </c>
     </row>
     <row r="170">
@@ -27181,7 +28216,7 @@
         <v>1</v>
       </c>
       <c r="P170" s="0" t="s">
-        <v>279</v>
+        <v>624</v>
       </c>
     </row>
     <row r="171">
@@ -27213,7 +28248,7 @@
         <v>1</v>
       </c>
       <c r="J171" s="0">
-        <v>1957.1803218846953</v>
+        <v>1957.1803218846944</v>
       </c>
       <c r="K171" s="0">
         <v>0.99710136630858937</v>
@@ -27231,7 +28266,7 @@
         <v>1</v>
       </c>
       <c r="P171" s="0" t="s">
-        <v>280</v>
+        <v>625</v>
       </c>
     </row>
     <row r="172">
@@ -27263,7 +28298,7 @@
         <v>1</v>
       </c>
       <c r="J172" s="0">
-        <v>2100.6071929166155</v>
+        <v>2100.607192916616</v>
       </c>
       <c r="K172" s="0">
         <v>0.99678014918195579</v>
@@ -27281,7 +28316,7 @@
         <v>1</v>
       </c>
       <c r="P172" s="0" t="s">
-        <v>281</v>
+        <v>626</v>
       </c>
     </row>
     <row r="173">
@@ -27331,7 +28366,7 @@
         <v>1</v>
       </c>
       <c r="P173" s="0" t="s">
-        <v>282</v>
+        <v>627</v>
       </c>
     </row>
     <row r="174">
@@ -27381,7 +28416,7 @@
         <v>1</v>
       </c>
       <c r="P174" s="0" t="s">
-        <v>283</v>
+        <v>628</v>
       </c>
     </row>
     <row r="175">
@@ -27431,7 +28466,7 @@
         <v>1</v>
       </c>
       <c r="P175" s="0" t="s">
-        <v>284</v>
+        <v>629</v>
       </c>
     </row>
     <row r="176">
@@ -27466,7 +28501,7 @@
         <v>1616.1367703976414</v>
       </c>
       <c r="K176" s="0">
-        <v>0.97152799656703037</v>
+        <v>0.97152799656703048</v>
       </c>
       <c r="L176" s="0">
         <v>68</v>
@@ -27481,7 +28516,7 @@
         <v>1</v>
       </c>
       <c r="P176" s="0" t="s">
-        <v>285</v>
+        <v>630</v>
       </c>
     </row>
     <row r="177">
@@ -27513,7 +28548,7 @@
         <v>1</v>
       </c>
       <c r="J177" s="0">
-        <v>1056.3808174752112</v>
+        <v>1056.3808174752107</v>
       </c>
       <c r="K177" s="0">
         <v>0.94283269905406642</v>
@@ -27531,7 +28566,7 @@
         <v>1</v>
       </c>
       <c r="P177" s="0" t="s">
-        <v>286</v>
+        <v>631</v>
       </c>
     </row>
     <row r="178">
@@ -27581,7 +28616,7 @@
         <v>1</v>
       </c>
       <c r="P178" s="0" t="s">
-        <v>287</v>
+        <v>632</v>
       </c>
     </row>
     <row r="179">
@@ -27613,7 +28648,7 @@
         <v>1</v>
       </c>
       <c r="J179" s="0">
-        <v>2440.3213240975706</v>
+        <v>2440.3213240975715</v>
       </c>
       <c r="K179" s="0">
         <v>0.99730254767897886</v>
@@ -27631,7 +28666,7 @@
         <v>1</v>
       </c>
       <c r="P179" s="0" t="s">
-        <v>288</v>
+        <v>633</v>
       </c>
     </row>
     <row r="180">
@@ -27681,7 +28716,7 @@
         <v>1</v>
       </c>
       <c r="P180" s="0" t="s">
-        <v>289</v>
+        <v>634</v>
       </c>
     </row>
     <row r="181">
@@ -27731,7 +28766,7 @@
         <v>1</v>
       </c>
       <c r="P181" s="0" t="s">
-        <v>290</v>
+        <v>635</v>
       </c>
     </row>
     <row r="182">
@@ -27763,7 +28798,7 @@
         <v>1</v>
       </c>
       <c r="J182" s="0">
-        <v>1957.1803218846953</v>
+        <v>1957.1803218846944</v>
       </c>
       <c r="K182" s="0">
         <v>0.99710136630858937</v>
@@ -27781,7 +28816,7 @@
         <v>1</v>
       </c>
       <c r="P182" s="0" t="s">
-        <v>291</v>
+        <v>636</v>
       </c>
     </row>
     <row r="183">
@@ -27813,7 +28848,7 @@
         <v>1</v>
       </c>
       <c r="J183" s="0">
-        <v>2335.8882071409444</v>
+        <v>2335.8882071409457</v>
       </c>
       <c r="K183" s="0">
         <v>0.99474605101124125</v>
@@ -27831,7 +28866,7 @@
         <v>1</v>
       </c>
       <c r="P183" s="0" t="s">
-        <v>292</v>
+        <v>637</v>
       </c>
     </row>
     <row r="184">
@@ -27863,7 +28898,7 @@
         <v>1</v>
       </c>
       <c r="J184" s="0">
-        <v>2100.6071929166155</v>
+        <v>2100.607192916616</v>
       </c>
       <c r="K184" s="0">
         <v>0.99678014918195579</v>
@@ -27881,7 +28916,7 @@
         <v>1</v>
       </c>
       <c r="P184" s="0" t="s">
-        <v>293</v>
+        <v>638</v>
       </c>
     </row>
     <row r="185">
@@ -27916,7 +28951,7 @@
         <v>1297.3670999915848</v>
       </c>
       <c r="K185" s="0">
-        <v>0.98822650020533376</v>
+        <v>0.98822650020533387</v>
       </c>
       <c r="L185" s="0">
         <v>50</v>
@@ -27931,7 +28966,7 @@
         <v>1</v>
       </c>
       <c r="P185" s="0" t="s">
-        <v>294</v>
+        <v>639</v>
       </c>
     </row>
     <row r="186">
@@ -27981,7 +29016,7 @@
         <v>1</v>
       </c>
       <c r="P186" s="0" t="s">
-        <v>295</v>
+        <v>640</v>
       </c>
     </row>
     <row r="187">
@@ -28031,7 +29066,7 @@
         <v>1</v>
       </c>
       <c r="P187" s="0" t="s">
-        <v>296</v>
+        <v>641</v>
       </c>
     </row>
     <row r="188">
@@ -28063,7 +29098,7 @@
         <v>1</v>
       </c>
       <c r="J188" s="0">
-        <v>1599.6399572794105</v>
+        <v>1599.6399572794114</v>
       </c>
       <c r="K188" s="0">
         <v>0.99901196054217112</v>
@@ -28081,7 +29116,7 @@
         <v>1</v>
       </c>
       <c r="P188" s="0" t="s">
-        <v>297</v>
+        <v>642</v>
       </c>
     </row>
     <row r="189">
@@ -28131,7 +29166,7 @@
         <v>1</v>
       </c>
       <c r="P189" s="0" t="s">
-        <v>299</v>
+        <v>644</v>
       </c>
     </row>
     <row r="190">
@@ -28163,7 +29198,7 @@
         <v>1</v>
       </c>
       <c r="J190" s="0">
-        <v>2396.349660329468</v>
+        <v>2396.3496603294684</v>
       </c>
       <c r="K190" s="0">
         <v>0.99886183274992047</v>
@@ -28181,7 +29216,7 @@
         <v>1</v>
       </c>
       <c r="P190" s="0" t="s">
-        <v>300</v>
+        <v>645</v>
       </c>
     </row>
     <row r="191">
@@ -28213,7 +29248,7 @@
         <v>1</v>
       </c>
       <c r="J191" s="0">
-        <v>1691.1787902311646</v>
+        <v>1691.1787902311642</v>
       </c>
       <c r="K191" s="0">
         <v>0.99903116195667208</v>
@@ -28231,7 +29266,7 @@
         <v>1</v>
       </c>
       <c r="P191" s="0" t="s">
-        <v>301</v>
+        <v>646</v>
       </c>
     </row>
     <row r="192">
@@ -28263,7 +29298,7 @@
         <v>1</v>
       </c>
       <c r="J192" s="0">
-        <v>1227.7760254013131</v>
+        <v>1227.7760254013128</v>
       </c>
       <c r="K192" s="0">
         <v>0.99646754195860721</v>
@@ -28281,7 +29316,7 @@
         <v>1</v>
       </c>
       <c r="P192" s="0" t="s">
-        <v>302</v>
+        <v>647</v>
       </c>
     </row>
     <row r="193">
@@ -28331,7 +29366,7 @@
         <v>1</v>
       </c>
       <c r="P193" s="0" t="s">
-        <v>303</v>
+        <v>648</v>
       </c>
     </row>
     <row r="194">
@@ -28363,7 +29398,7 @@
         <v>1</v>
       </c>
       <c r="J194" s="0">
-        <v>2555.8481455882634</v>
+        <v>2555.8481455882638</v>
       </c>
       <c r="K194" s="0">
         <v>0.99755119035843598</v>
@@ -28381,7 +29416,7 @@
         <v>1</v>
       </c>
       <c r="P194" s="0" t="s">
-        <v>304</v>
+        <v>649</v>
       </c>
     </row>
     <row r="195">
@@ -28413,7 +29448,7 @@
         <v>1</v>
       </c>
       <c r="J195" s="0">
-        <v>1581.0258855824488</v>
+        <v>1581.0258855824493</v>
       </c>
       <c r="K195" s="0">
         <v>0.98885888391854771</v>
@@ -28431,7 +29466,7 @@
         <v>1</v>
       </c>
       <c r="P195" s="0" t="s">
-        <v>305</v>
+        <v>650</v>
       </c>
     </row>
     <row r="196">
@@ -28463,10 +29498,10 @@
         <v>1</v>
       </c>
       <c r="J196" s="0">
-        <v>671.60786031937676</v>
+        <v>671.60786031937664</v>
       </c>
       <c r="K196" s="0">
-        <v>0.92369673766876226</v>
+        <v>0.92369673766876237</v>
       </c>
       <c r="L196" s="0">
         <v>9</v>
@@ -28481,7 +29516,7 @@
         <v>1</v>
       </c>
       <c r="P196" s="0" t="s">
-        <v>306</v>
+        <v>651</v>
       </c>
     </row>
     <row r="197">
@@ -28513,7 +29548,7 @@
         <v>1</v>
       </c>
       <c r="J197" s="0">
-        <v>1613.7008931305202</v>
+        <v>1613.7008931305206</v>
       </c>
       <c r="K197" s="0">
         <v>0.99901196054217112</v>
@@ -28531,7 +29566,7 @@
         <v>1</v>
       </c>
       <c r="P197" s="0" t="s">
-        <v>307</v>
+        <v>652</v>
       </c>
     </row>
     <row r="198">
@@ -28563,7 +29598,7 @@
         <v>1</v>
       </c>
       <c r="J198" s="0">
-        <v>687.04184450431717</v>
+        <v>687.0418445043174</v>
       </c>
       <c r="K198" s="0">
         <v>0.98797397859549474</v>
@@ -28581,7 +29616,7 @@
         <v>1</v>
       </c>
       <c r="P198" s="0" t="s">
-        <v>309</v>
+        <v>654</v>
       </c>
     </row>
     <row r="199">
@@ -28631,7 +29666,7 @@
         <v>1</v>
       </c>
       <c r="P199" s="0" t="s">
-        <v>310</v>
+        <v>655</v>
       </c>
     </row>
     <row r="200">
@@ -28681,7 +29716,7 @@
         <v>1</v>
       </c>
       <c r="P200" s="0" t="s">
-        <v>312</v>
+        <v>657</v>
       </c>
     </row>
     <row r="201">
@@ -28713,7 +29748,7 @@
         <v>1</v>
       </c>
       <c r="J201" s="0">
-        <v>2396.349660329468</v>
+        <v>2396.3496603294684</v>
       </c>
       <c r="K201" s="0">
         <v>0.99886183274992047</v>
@@ -28731,7 +29766,7 @@
         <v>1</v>
       </c>
       <c r="P201" s="0" t="s">
-        <v>313</v>
+        <v>658</v>
       </c>
     </row>
     <row r="202">
@@ -28763,7 +29798,7 @@
         <v>1</v>
       </c>
       <c r="J202" s="0">
-        <v>1691.1787902311646</v>
+        <v>1691.1787902311642</v>
       </c>
       <c r="K202" s="0">
         <v>0.99903116195667208</v>
@@ -28781,7 +29816,7 @@
         <v>1</v>
       </c>
       <c r="P202" s="0" t="s">
-        <v>314</v>
+        <v>659</v>
       </c>
     </row>
     <row r="203">
@@ -28813,7 +29848,7 @@
         <v>1</v>
       </c>
       <c r="J203" s="0">
-        <v>1227.7760254013131</v>
+        <v>1227.7760254013128</v>
       </c>
       <c r="K203" s="0">
         <v>0.99646754195860721</v>
@@ -28831,7 +29866,7 @@
         <v>1</v>
       </c>
       <c r="P203" s="0" t="s">
-        <v>315</v>
+        <v>660</v>
       </c>
     </row>
     <row r="204">
@@ -28881,7 +29916,7 @@
         <v>1</v>
       </c>
       <c r="P204" s="0" t="s">
-        <v>316</v>
+        <v>661</v>
       </c>
     </row>
     <row r="205">
@@ -28913,7 +29948,7 @@
         <v>1</v>
       </c>
       <c r="J205" s="0">
-        <v>2555.8481455882634</v>
+        <v>2555.8481455882638</v>
       </c>
       <c r="K205" s="0">
         <v>0.99755119035843598</v>
@@ -28931,7 +29966,7 @@
         <v>1</v>
       </c>
       <c r="P205" s="0" t="s">
-        <v>317</v>
+        <v>662</v>
       </c>
     </row>
     <row r="206">
@@ -28963,7 +29998,7 @@
         <v>1</v>
       </c>
       <c r="J206" s="0">
-        <v>1581.0258855824488</v>
+        <v>1581.0258855824493</v>
       </c>
       <c r="K206" s="0">
         <v>0.98885888391854771</v>
@@ -28981,7 +30016,7 @@
         <v>1</v>
       </c>
       <c r="P206" s="0" t="s">
-        <v>318</v>
+        <v>663</v>
       </c>
     </row>
     <row r="207">
@@ -29013,10 +30048,10 @@
         <v>1</v>
       </c>
       <c r="J207" s="0">
-        <v>671.60786031937676</v>
+        <v>671.60786031937664</v>
       </c>
       <c r="K207" s="0">
-        <v>0.92369673766876226</v>
+        <v>0.92369673766876237</v>
       </c>
       <c r="L207" s="0">
         <v>9</v>
@@ -29031,7 +30066,7 @@
         <v>1</v>
       </c>
       <c r="P207" s="0" t="s">
-        <v>319</v>
+        <v>664</v>
       </c>
     </row>
     <row r="208">
@@ -29063,7 +30098,7 @@
         <v>1</v>
       </c>
       <c r="J208" s="0">
-        <v>1613.7008931305202</v>
+        <v>1613.7008931305206</v>
       </c>
       <c r="K208" s="0">
         <v>0.99901196054217112</v>
@@ -29081,7 +30116,7 @@
         <v>1</v>
       </c>
       <c r="P208" s="0" t="s">
-        <v>320</v>
+        <v>665</v>
       </c>
     </row>
     <row r="209">
@@ -29113,7 +30148,7 @@
         <v>1</v>
       </c>
       <c r="J209" s="0">
-        <v>687.04184450431717</v>
+        <v>687.0418445043174</v>
       </c>
       <c r="K209" s="0">
         <v>0.98797397859549474</v>
@@ -29131,7 +30166,7 @@
         <v>1</v>
       </c>
       <c r="P209" s="0" t="s">
-        <v>322</v>
+        <v>667</v>
       </c>
     </row>
     <row r="210">
@@ -29181,7 +30216,7 @@
         <v>1</v>
       </c>
       <c r="P210" s="0" t="s">
-        <v>323</v>
+        <v>668</v>
       </c>
     </row>
     <row r="211">
@@ -29213,7 +30248,7 @@
         <v>1</v>
       </c>
       <c r="J211" s="0">
-        <v>2449.1530928682232</v>
+        <v>2449.1530928682228</v>
       </c>
       <c r="K211" s="0">
         <v>0.99623844745019052</v>
@@ -29231,7 +30266,7 @@
         <v>1</v>
       </c>
       <c r="P211" s="0" t="s">
-        <v>324</v>
+        <v>669</v>
       </c>
     </row>
     <row r="212">
@@ -29281,7 +30316,7 @@
         <v>1</v>
       </c>
       <c r="P212" s="0" t="s">
-        <v>325</v>
+        <v>670</v>
       </c>
     </row>
     <row r="213">
@@ -29331,7 +30366,7 @@
         <v>1</v>
       </c>
       <c r="P213" s="0" t="s">
-        <v>326</v>
+        <v>671</v>
       </c>
     </row>
     <row r="214">
@@ -29381,7 +30416,7 @@
         <v>1</v>
       </c>
       <c r="P214" s="0" t="s">
-        <v>327</v>
+        <v>672</v>
       </c>
     </row>
     <row r="215">
@@ -29413,7 +30448,7 @@
         <v>1</v>
       </c>
       <c r="J215" s="0">
-        <v>1455.5117433463759</v>
+        <v>1455.5117433463756</v>
       </c>
       <c r="K215" s="0">
         <v>0.99751373845169589</v>
@@ -29431,7 +30466,7 @@
         <v>1</v>
       </c>
       <c r="P215" s="0" t="s">
-        <v>328</v>
+        <v>673</v>
       </c>
     </row>
     <row r="216">
@@ -29463,7 +30498,7 @@
         <v>1</v>
       </c>
       <c r="J216" s="0">
-        <v>2874.8707020139023</v>
+        <v>2874.8707020139027</v>
       </c>
       <c r="K216" s="0">
         <v>0.99333099931874025</v>
@@ -29481,7 +30516,7 @@
         <v>1</v>
       </c>
       <c r="P216" s="0" t="s">
-        <v>329</v>
+        <v>674</v>
       </c>
     </row>
     <row r="217">
@@ -29513,7 +30548,7 @@
         <v>1</v>
       </c>
       <c r="J217" s="0">
-        <v>1491.4889605688461</v>
+        <v>1491.4889605688463</v>
       </c>
       <c r="K217" s="0">
         <v>0.99643534655967825</v>
@@ -29531,7 +30566,7 @@
         <v>1</v>
       </c>
       <c r="P217" s="0" t="s">
-        <v>330</v>
+        <v>675</v>
       </c>
     </row>
     <row r="218">
@@ -29563,7 +30598,7 @@
         <v>1</v>
       </c>
       <c r="J218" s="0">
-        <v>1678.4082934635874</v>
+        <v>1678.4082934635876</v>
       </c>
       <c r="K218" s="0">
         <v>0.99709226984163923</v>
@@ -29581,7 +30616,7 @@
         <v>1</v>
       </c>
       <c r="P218" s="0" t="s">
-        <v>331</v>
+        <v>676</v>
       </c>
     </row>
     <row r="219">
@@ -29631,7 +30666,7 @@
         <v>1</v>
       </c>
       <c r="P219" s="0" t="s">
-        <v>332</v>
+        <v>677</v>
       </c>
     </row>
     <row r="220">
@@ -29681,7 +30716,7 @@
         <v>1</v>
       </c>
       <c r="P220" s="0" t="s">
-        <v>333</v>
+        <v>678</v>
       </c>
     </row>
     <row r="221">
@@ -29713,7 +30748,7 @@
         <v>1</v>
       </c>
       <c r="J221" s="0">
-        <v>2525.5924972922203</v>
+        <v>2525.5924972922198</v>
       </c>
       <c r="K221" s="0">
         <v>0.99685333603197013</v>
@@ -29731,7 +30766,7 @@
         <v>1</v>
       </c>
       <c r="P221" s="0" t="s">
-        <v>334</v>
+        <v>679</v>
       </c>
     </row>
     <row r="222">
@@ -29781,7 +30816,7 @@
         <v>1</v>
       </c>
       <c r="P222" s="0" t="s">
-        <v>335</v>
+        <v>680</v>
       </c>
     </row>
     <row r="223">
@@ -29831,7 +30866,7 @@
         <v>1</v>
       </c>
       <c r="P223" s="0" t="s">
-        <v>336</v>
+        <v>681</v>
       </c>
     </row>
     <row r="224">
@@ -29881,7 +30916,7 @@
         <v>1</v>
       </c>
       <c r="P224" s="0" t="s">
-        <v>337</v>
+        <v>682</v>
       </c>
     </row>
     <row r="225">
@@ -29913,7 +30948,7 @@
         <v>1</v>
       </c>
       <c r="J225" s="0">
-        <v>1455.5117433463759</v>
+        <v>1455.5117433463756</v>
       </c>
       <c r="K225" s="0">
         <v>0.99751373845169589</v>
@@ -29931,7 +30966,7 @@
         <v>1</v>
       </c>
       <c r="P225" s="0" t="s">
-        <v>338</v>
+        <v>683</v>
       </c>
     </row>
     <row r="226">
@@ -29963,7 +30998,7 @@
         <v>1</v>
       </c>
       <c r="J226" s="0">
-        <v>2874.8707020139023</v>
+        <v>2874.8707020139027</v>
       </c>
       <c r="K226" s="0">
         <v>0.99333099931874025</v>
@@ -29981,7 +31016,7 @@
         <v>1</v>
       </c>
       <c r="P226" s="0" t="s">
-        <v>339</v>
+        <v>684</v>
       </c>
     </row>
     <row r="227">
@@ -30013,7 +31048,7 @@
         <v>1</v>
       </c>
       <c r="J227" s="0">
-        <v>1491.4889605688461</v>
+        <v>1491.4889605688463</v>
       </c>
       <c r="K227" s="0">
         <v>0.99643534655967825</v>
@@ -30031,7 +31066,7 @@
         <v>1</v>
       </c>
       <c r="P227" s="0" t="s">
-        <v>340</v>
+        <v>685</v>
       </c>
     </row>
     <row r="228">
@@ -30081,7 +31116,7 @@
         <v>1</v>
       </c>
       <c r="P228" s="0" t="s">
-        <v>341</v>
+        <v>686</v>
       </c>
     </row>
     <row r="229">
@@ -30131,7 +31166,7 @@
         <v>1</v>
       </c>
       <c r="P229" s="0" t="s">
-        <v>342</v>
+        <v>687</v>
       </c>
     </row>
     <row r="230">
@@ -30181,7 +31216,7 @@
         <v>1</v>
       </c>
       <c r="P230" s="0" t="s">
-        <v>343</v>
+        <v>688</v>
       </c>
     </row>
     <row r="231">
@@ -30213,7 +31248,7 @@
         <v>1</v>
       </c>
       <c r="J231" s="0">
-        <v>192.42091061333258</v>
+        <v>192.42091061333255</v>
       </c>
       <c r="K231" s="0">
         <v>0.9036431974225605</v>
@@ -30231,7 +31266,7 @@
         <v>1</v>
       </c>
       <c r="P231" s="0" t="s">
-        <v>345</v>
+        <v>690</v>
       </c>
     </row>
     <row r="232">
@@ -30281,7 +31316,7 @@
         <v>1</v>
       </c>
       <c r="P232" s="0" t="s">
-        <v>346</v>
+        <v>691</v>
       </c>
     </row>
     <row r="233">
@@ -30313,7 +31348,7 @@
         <v>1</v>
       </c>
       <c r="J233" s="0">
-        <v>384.45618045661763</v>
+        <v>384.4561804566178</v>
       </c>
       <c r="K233" s="0">
         <v>0.95313019401259691</v>
@@ -30331,7 +31366,7 @@
         <v>1</v>
       </c>
       <c r="P233" s="0" t="s">
-        <v>347</v>
+        <v>692</v>
       </c>
     </row>
     <row r="234">
@@ -30363,7 +31398,7 @@
         <v>1</v>
       </c>
       <c r="J234" s="0">
-        <v>1418.6837585694998</v>
+        <v>1418.6837585695</v>
       </c>
       <c r="K234" s="0">
         <v>0.99586902087078955</v>
@@ -30381,7 +31416,7 @@
         <v>1</v>
       </c>
       <c r="P234" s="0" t="s">
-        <v>348</v>
+        <v>693</v>
       </c>
     </row>
     <row r="235">
@@ -30431,7 +31466,7 @@
         <v>1</v>
       </c>
       <c r="P235" s="0" t="s">
-        <v>350</v>
+        <v>695</v>
       </c>
     </row>
     <row r="236">
@@ -30463,7 +31498,7 @@
         <v>1</v>
       </c>
       <c r="J236" s="0">
-        <v>512.91097720683888</v>
+        <v>512.91097720683877</v>
       </c>
       <c r="K236" s="0">
         <v>0.94181864623289824</v>
@@ -30481,7 +31516,7 @@
         <v>1</v>
       </c>
       <c r="P236" s="0" t="s">
-        <v>352</v>
+        <v>697</v>
       </c>
     </row>
     <row r="237">
@@ -30513,7 +31548,7 @@
         <v>1</v>
       </c>
       <c r="J237" s="0">
-        <v>254.43728349564017</v>
+        <v>254.4372834956402</v>
       </c>
       <c r="K237" s="0">
         <v>0.95447799898686769</v>
@@ -30531,7 +31566,7 @@
         <v>1</v>
       </c>
       <c r="P237" s="0" t="s">
-        <v>354</v>
+        <v>699</v>
       </c>
     </row>
     <row r="238">
@@ -30563,10 +31598,10 @@
         <v>1</v>
       </c>
       <c r="J238" s="0">
-        <v>398.49379114531337</v>
+        <v>398.49379114531348</v>
       </c>
       <c r="K238" s="0">
-        <v>0.979989027928726</v>
+        <v>0.97998902792872589</v>
       </c>
       <c r="L238" s="0">
         <v>9</v>
@@ -30581,7 +31616,7 @@
         <v>1</v>
       </c>
       <c r="P238" s="0" t="s">
-        <v>355</v>
+        <v>700</v>
       </c>
     </row>
     <row r="239">
@@ -30616,7 +31651,7 @@
         <v>45.187736026753143</v>
       </c>
       <c r="K239" s="0">
-        <v>0.95383363988415848</v>
+        <v>0.95383363988415859</v>
       </c>
       <c r="L239" s="0">
         <v>10</v>
@@ -30631,7 +31666,7 @@
         <v>1</v>
       </c>
       <c r="P239" s="0" t="s">
-        <v>357</v>
+        <v>702</v>
       </c>
     </row>
     <row r="240">
@@ -30663,7 +31698,7 @@
         <v>1</v>
       </c>
       <c r="J240" s="0">
-        <v>3.3534192222269947</v>
+        <v>3.3534192222269978</v>
       </c>
       <c r="K240" s="0">
         <v>0.9093946230277079</v>
@@ -30681,7 +31716,7 @@
         <v>1</v>
       </c>
       <c r="P240" s="0" t="s">
-        <v>358</v>
+        <v>703</v>
       </c>
     </row>
     <row r="241">
@@ -30713,10 +31748,10 @@
         <v>1</v>
       </c>
       <c r="J241" s="0">
-        <v>268.1397124491661</v>
+        <v>268.13971244916615</v>
       </c>
       <c r="K241" s="0">
-        <v>0.95938899466819394</v>
+        <v>0.95938899466819383</v>
       </c>
       <c r="L241" s="0">
         <v>10</v>
@@ -30731,7 +31766,7 @@
         <v>1</v>
       </c>
       <c r="P241" s="0" t="s">
-        <v>361</v>
+        <v>706</v>
       </c>
     </row>
     <row r="242">
@@ -30781,7 +31816,7 @@
         <v>1</v>
       </c>
       <c r="P242" s="0" t="s">
-        <v>363</v>
+        <v>708</v>
       </c>
     </row>
     <row r="243">
@@ -30813,7 +31848,7 @@
         <v>1</v>
       </c>
       <c r="J243" s="0">
-        <v>570.94068302014318</v>
+        <v>570.94068302014284</v>
       </c>
       <c r="K243" s="0">
         <v>0.95926162197996057</v>
@@ -30831,7 +31866,7 @@
         <v>1</v>
       </c>
       <c r="P243" s="0" t="s">
-        <v>364</v>
+        <v>709</v>
       </c>
     </row>
     <row r="244">
@@ -30881,7 +31916,7 @@
         <v>1</v>
       </c>
       <c r="P244" s="0" t="s">
-        <v>365</v>
+        <v>710</v>
       </c>
     </row>
     <row r="245">
@@ -30931,7 +31966,7 @@
         <v>1</v>
       </c>
       <c r="P245" s="0" t="s">
-        <v>367</v>
+        <v>712</v>
       </c>
     </row>
     <row r="246">
@@ -30963,7 +31998,7 @@
         <v>1</v>
       </c>
       <c r="J246" s="0">
-        <v>758.06535201219174</v>
+        <v>758.06535201219162</v>
       </c>
       <c r="K246" s="0">
         <v>0.99670764581294224</v>
@@ -30981,7 +32016,7 @@
         <v>1</v>
       </c>
       <c r="P246" s="0" t="s">
-        <v>369</v>
+        <v>714</v>
       </c>
     </row>
     <row r="247">
@@ -31013,7 +32048,7 @@
         <v>1</v>
       </c>
       <c r="J247" s="0">
-        <v>315.48003614417814</v>
+        <v>315.4800361441782</v>
       </c>
       <c r="K247" s="0">
         <v>0.92524688597342442</v>
@@ -31031,7 +32066,7 @@
         <v>1</v>
       </c>
       <c r="P247" s="0" t="s">
-        <v>370</v>
+        <v>715</v>
       </c>
     </row>
     <row r="248">
@@ -31063,7 +32098,7 @@
         <v>1</v>
       </c>
       <c r="J248" s="0">
-        <v>323.04969785446519</v>
+        <v>323.04969785446508</v>
       </c>
       <c r="K248" s="0">
         <v>0.95107206324464433</v>
@@ -31081,7 +32116,7 @@
         <v>1</v>
       </c>
       <c r="P248" s="0" t="s">
-        <v>372</v>
+        <v>717</v>
       </c>
     </row>
     <row r="249">
@@ -31131,7 +32166,7 @@
         <v>1</v>
       </c>
       <c r="P249" s="0" t="s">
-        <v>373</v>
+        <v>718</v>
       </c>
     </row>
     <row r="250">
@@ -31181,7 +32216,7 @@
         <v>1</v>
       </c>
       <c r="P250" s="0" t="s">
-        <v>374</v>
+        <v>719</v>
       </c>
     </row>
     <row r="251">
@@ -31213,7 +32248,7 @@
         <v>1</v>
       </c>
       <c r="J251" s="0">
-        <v>1379.4400953307611</v>
+        <v>1379.4400953307616</v>
       </c>
       <c r="K251" s="0">
         <v>0.99831457480633468</v>
@@ -31231,7 +32266,7 @@
         <v>1</v>
       </c>
       <c r="P251" s="0" t="s">
-        <v>375</v>
+        <v>720</v>
       </c>
     </row>
     <row r="252">
@@ -31263,7 +32298,7 @@
         <v>1</v>
       </c>
       <c r="J252" s="0">
-        <v>1370.2590578219076</v>
+        <v>1370.2590578219078</v>
       </c>
       <c r="K252" s="0">
         <v>0.99669301763227647</v>
@@ -31281,7 +32316,7 @@
         <v>1</v>
       </c>
       <c r="P252" s="0" t="s">
-        <v>376</v>
+        <v>721</v>
       </c>
     </row>
     <row r="253">
@@ -31313,7 +32348,7 @@
         <v>1</v>
       </c>
       <c r="J253" s="0">
-        <v>2539.2521882687824</v>
+        <v>2539.252188268782</v>
       </c>
       <c r="K253" s="0">
         <v>0.9962700456575454</v>
@@ -31331,7 +32366,7 @@
         <v>1</v>
       </c>
       <c r="P253" s="0" t="s">
-        <v>377</v>
+        <v>722</v>
       </c>
     </row>
     <row r="254">
@@ -31381,7 +32416,7 @@
         <v>1</v>
       </c>
       <c r="P254" s="0" t="s">
-        <v>378</v>
+        <v>723</v>
       </c>
     </row>
     <row r="255">
@@ -31416,7 +32451,7 @@
         <v>2621.4672744778886</v>
       </c>
       <c r="K255" s="0">
-        <v>0.99501099374933311</v>
+        <v>0.99501099374933299</v>
       </c>
       <c r="L255" s="0">
         <v>50</v>
@@ -31431,7 +32466,7 @@
         <v>1</v>
       </c>
       <c r="P255" s="0" t="s">
-        <v>379</v>
+        <v>724</v>
       </c>
     </row>
     <row r="256">
@@ -31463,7 +32498,7 @@
         <v>1</v>
       </c>
       <c r="J256" s="0">
-        <v>2592.8762022801302</v>
+        <v>2592.8762022801297</v>
       </c>
       <c r="K256" s="0">
         <v>0.99309025398432471</v>
@@ -31481,7 +32516,7 @@
         <v>1</v>
       </c>
       <c r="P256" s="0" t="s">
-        <v>380</v>
+        <v>725</v>
       </c>
     </row>
     <row r="257">
@@ -31513,7 +32548,7 @@
         <v>1</v>
       </c>
       <c r="J257" s="0">
-        <v>1560.8194865800665</v>
+        <v>1560.8194865800663</v>
       </c>
       <c r="K257" s="0">
         <v>0.99555257962182553</v>
@@ -31531,7 +32566,7 @@
         <v>1</v>
       </c>
       <c r="P257" s="0" t="s">
-        <v>381</v>
+        <v>726</v>
       </c>
     </row>
     <row r="258">
@@ -31563,7 +32598,7 @@
         <v>1</v>
       </c>
       <c r="J258" s="0">
-        <v>2078.9998838732204</v>
+        <v>2078.9998838732208</v>
       </c>
       <c r="K258" s="0">
         <v>0.98474830893698151</v>
@@ -31581,7 +32616,7 @@
         <v>1</v>
       </c>
       <c r="P258" s="0" t="s">
-        <v>382</v>
+        <v>727</v>
       </c>
     </row>
     <row r="259">
@@ -31613,7 +32648,7 @@
         <v>1</v>
       </c>
       <c r="J259" s="0">
-        <v>1190.9117209662809</v>
+        <v>1190.9117209662807</v>
       </c>
       <c r="K259" s="0">
         <v>0.99761066638701845</v>
@@ -31631,7 +32666,7 @@
         <v>1</v>
       </c>
       <c r="P259" s="0" t="s">
-        <v>383</v>
+        <v>728</v>
       </c>
     </row>
     <row r="260">
@@ -31681,7 +32716,7 @@
         <v>1</v>
       </c>
       <c r="P260" s="0" t="s">
-        <v>384</v>
+        <v>729</v>
       </c>
     </row>
     <row r="261">
@@ -31731,7 +32766,7 @@
         <v>1</v>
       </c>
       <c r="P261" s="0" t="s">
-        <v>385</v>
+        <v>730</v>
       </c>
     </row>
     <row r="262">
@@ -31781,7 +32816,7 @@
         <v>1</v>
       </c>
       <c r="P262" s="0" t="s">
-        <v>386</v>
+        <v>731</v>
       </c>
     </row>
     <row r="263">
@@ -31813,7 +32848,7 @@
         <v>1</v>
       </c>
       <c r="J263" s="0">
-        <v>1088.1920475078391</v>
+        <v>1088.1920475078389</v>
       </c>
       <c r="K263" s="0">
         <v>0.96218147899027162</v>
@@ -31831,7 +32866,7 @@
         <v>1</v>
       </c>
       <c r="P263" s="0" t="s">
-        <v>387</v>
+        <v>732</v>
       </c>
     </row>
     <row r="264">
@@ -31881,7 +32916,7 @@
         <v>1</v>
       </c>
       <c r="P264" s="0" t="s">
-        <v>388</v>
+        <v>733</v>
       </c>
     </row>
     <row r="265">
@@ -31913,10 +32948,10 @@
         <v>1</v>
       </c>
       <c r="J265" s="0">
-        <v>1330.2709774134655</v>
+        <v>1330.2709774134648</v>
       </c>
       <c r="K265" s="0">
-        <v>0.99040059469464858</v>
+        <v>0.9904005946946487</v>
       </c>
       <c r="L265" s="0">
         <v>50</v>
@@ -31931,7 +32966,7 @@
         <v>1</v>
       </c>
       <c r="P265" s="0" t="s">
-        <v>389</v>
+        <v>734</v>
       </c>
     </row>
     <row r="266">
@@ -31963,7 +32998,7 @@
         <v>1</v>
       </c>
       <c r="J266" s="0">
-        <v>1566.5286936543673</v>
+        <v>1566.528693654368</v>
       </c>
       <c r="K266" s="0">
         <v>0.99278914480686276</v>
@@ -31981,7 +33016,7 @@
         <v>1</v>
       </c>
       <c r="P266" s="0" t="s">
-        <v>390</v>
+        <v>735</v>
       </c>
     </row>
     <row r="267">
@@ -32013,7 +33048,7 @@
         <v>1</v>
       </c>
       <c r="J267" s="0">
-        <v>1238.7382130834928</v>
+        <v>1238.7382130834931</v>
       </c>
       <c r="K267" s="0">
         <v>0.99789101373191746</v>
@@ -32031,7 +33066,7 @@
         <v>1</v>
       </c>
       <c r="P267" s="0" t="s">
-        <v>391</v>
+        <v>736</v>
       </c>
     </row>
     <row r="268">
@@ -32063,7 +33098,7 @@
         <v>1</v>
       </c>
       <c r="J268" s="0">
-        <v>2040.4546054087846</v>
+        <v>2040.4546054087825</v>
       </c>
       <c r="K268" s="0">
         <v>0.99247701698284152</v>
@@ -32081,7 +33116,7 @@
         <v>1</v>
       </c>
       <c r="P268" s="0" t="s">
-        <v>392</v>
+        <v>737</v>
       </c>
     </row>
     <row r="269">
@@ -32131,7 +33166,7 @@
         <v>1</v>
       </c>
       <c r="P269" s="0" t="s">
-        <v>393</v>
+        <v>738</v>
       </c>
     </row>
     <row r="270">
@@ -32181,7 +33216,7 @@
         <v>1</v>
       </c>
       <c r="P270" s="0" t="s">
-        <v>394</v>
+        <v>739</v>
       </c>
     </row>
     <row r="271">
@@ -32231,7 +33266,7 @@
         <v>1</v>
       </c>
       <c r="P271" s="0" t="s">
-        <v>395</v>
+        <v>740</v>
       </c>
     </row>
     <row r="272">
@@ -32263,7 +33298,7 @@
         <v>1</v>
       </c>
       <c r="J272" s="0">
-        <v>685.47371274742307</v>
+        <v>685.47371274742272</v>
       </c>
       <c r="K272" s="0">
         <v>0.9731869319013895</v>
@@ -32281,7 +33316,7 @@
         <v>1</v>
       </c>
       <c r="P272" s="0" t="s">
-        <v>396</v>
+        <v>741</v>
       </c>
     </row>
     <row r="273">
@@ -32331,7 +33366,7 @@
         <v>1</v>
       </c>
       <c r="P273" s="0" t="s">
-        <v>399</v>
+        <v>744</v>
       </c>
     </row>
     <row r="274">
@@ -32381,7 +33416,7 @@
         <v>1</v>
       </c>
       <c r="P274" s="0" t="s">
-        <v>400</v>
+        <v>745</v>
       </c>
     </row>
     <row r="275">
@@ -32413,7 +33448,7 @@
         <v>1</v>
       </c>
       <c r="J275" s="0">
-        <v>346.56630219222728</v>
+        <v>346.56630219222734</v>
       </c>
       <c r="K275" s="0">
         <v>0.99843645416990068</v>
@@ -32431,7 +33466,7 @@
         <v>1</v>
       </c>
       <c r="P275" s="0" t="s">
-        <v>401</v>
+        <v>746</v>
       </c>
     </row>
     <row r="276">
@@ -32463,7 +33498,7 @@
         <v>1</v>
       </c>
       <c r="J276" s="0">
-        <v>511.91560184828978</v>
+        <v>511.91560184828961</v>
       </c>
       <c r="K276" s="0">
         <v>0.99694904379922544</v>
@@ -32481,7 +33516,7 @@
         <v>1</v>
       </c>
       <c r="P276" s="0" t="s">
-        <v>403</v>
+        <v>748</v>
       </c>
     </row>
     <row r="277">
@@ -32531,7 +33566,7 @@
         <v>1</v>
       </c>
       <c r="P277" s="0" t="s">
-        <v>404</v>
+        <v>749</v>
       </c>
     </row>
     <row r="278">
@@ -32563,7 +33598,7 @@
         <v>1</v>
       </c>
       <c r="J278" s="0">
-        <v>136.50870813899388</v>
+        <v>136.50870813899394</v>
       </c>
       <c r="K278" s="0">
         <v>0.98806382018266126</v>
@@ -32581,7 +33616,7 @@
         <v>1</v>
       </c>
       <c r="P278" s="0" t="s">
-        <v>406</v>
+        <v>751</v>
       </c>
     </row>
     <row r="279">
@@ -32631,7 +33666,7 @@
         <v>1</v>
       </c>
       <c r="P279" s="0" t="s">
-        <v>409</v>
+        <v>754</v>
       </c>
     </row>
     <row r="280">
@@ -32681,7 +33716,7 @@
         <v>1</v>
       </c>
       <c r="P280" s="0" t="s">
-        <v>411</v>
+        <v>756</v>
       </c>
     </row>
     <row r="281">
@@ -32713,10 +33748,10 @@
         <v>1</v>
       </c>
       <c r="J281" s="0">
-        <v>255.46246187259516</v>
+        <v>255.46246187259499</v>
       </c>
       <c r="K281" s="0">
-        <v>0.99294662619282459</v>
+        <v>0.9929466261928247</v>
       </c>
       <c r="L281" s="0">
         <v>10</v>
@@ -32731,7 +33766,7 @@
         <v>1</v>
       </c>
       <c r="P281" s="0" t="s">
-        <v>412</v>
+        <v>757</v>
       </c>
     </row>
     <row r="282">
@@ -32763,10 +33798,10 @@
         <v>1</v>
       </c>
       <c r="J282" s="0">
-        <v>197.50475430227795</v>
+        <v>197.50475430227797</v>
       </c>
       <c r="K282" s="0">
-        <v>0.98267966160743858</v>
+        <v>0.98267966160743869</v>
       </c>
       <c r="L282" s="0">
         <v>10</v>
@@ -32781,7 +33816,7 @@
         <v>1</v>
       </c>
       <c r="P282" s="0" t="s">
-        <v>413</v>
+        <v>758</v>
       </c>
     </row>
     <row r="283">
@@ -32831,7 +33866,7 @@
         <v>1</v>
       </c>
       <c r="P283" s="0" t="s">
-        <v>414</v>
+        <v>759</v>
       </c>
     </row>
     <row r="284">
@@ -32863,7 +33898,7 @@
         <v>1</v>
       </c>
       <c r="J284" s="0">
-        <v>511.91560184828978</v>
+        <v>511.91560184828961</v>
       </c>
       <c r="K284" s="0">
         <v>0.99694904379922544</v>
@@ -32881,7 +33916,7 @@
         <v>1</v>
       </c>
       <c r="P284" s="0" t="s">
-        <v>416</v>
+        <v>761</v>
       </c>
     </row>
     <row r="285">
@@ -32931,7 +33966,7 @@
         <v>1</v>
       </c>
       <c r="P285" s="0" t="s">
-        <v>417</v>
+        <v>762</v>
       </c>
     </row>
     <row r="286">
@@ -32981,7 +34016,7 @@
         <v>1</v>
       </c>
       <c r="P286" s="0" t="s">
-        <v>418</v>
+        <v>763</v>
       </c>
     </row>
     <row r="287">
@@ -33013,7 +34048,7 @@
         <v>1</v>
       </c>
       <c r="J287" s="0">
-        <v>24.039908371424929</v>
+        <v>24.039908371424922</v>
       </c>
       <c r="K287" s="0">
         <v>0.97593409463413106</v>
@@ -33031,7 +34066,7 @@
         <v>1</v>
       </c>
       <c r="P287" s="0" t="s">
-        <v>419</v>
+        <v>764</v>
       </c>
     </row>
     <row r="288">
@@ -33081,7 +34116,7 @@
         <v>1</v>
       </c>
       <c r="P288" s="0" t="s">
-        <v>420</v>
+        <v>765</v>
       </c>
     </row>
     <row r="289">
@@ -33131,7 +34166,7 @@
         <v>1</v>
       </c>
       <c r="P289" s="0" t="s">
-        <v>421</v>
+        <v>766</v>
       </c>
     </row>
     <row r="290">
@@ -33163,7 +34198,7 @@
         <v>1</v>
       </c>
       <c r="J290" s="0">
-        <v>18.624276947429966</v>
+        <v>18.624276947429959</v>
       </c>
       <c r="K290" s="0">
         <v>0.96489627186554361</v>
@@ -33181,7 +34216,7 @@
         <v>1</v>
       </c>
       <c r="P290" s="0" t="s">
-        <v>422</v>
+        <v>767</v>
       </c>
     </row>
     <row r="291">
@@ -33213,7 +34248,7 @@
         <v>1</v>
       </c>
       <c r="J291" s="0">
-        <v>1437.0215611114031</v>
+        <v>1437.0215611114029</v>
       </c>
       <c r="K291" s="0">
         <v>0.98890169968549757</v>
@@ -33231,7 +34266,7 @@
         <v>1</v>
       </c>
       <c r="P291" s="0" t="s">
-        <v>423</v>
+        <v>768</v>
       </c>
     </row>
     <row r="292">
@@ -33281,7 +34316,7 @@
         <v>1</v>
       </c>
       <c r="P292" s="0" t="s">
-        <v>424</v>
+        <v>769</v>
       </c>
     </row>
     <row r="293">
@@ -33313,7 +34348,7 @@
         <v>1</v>
       </c>
       <c r="J293" s="0">
-        <v>2157.8969355813429</v>
+        <v>2157.8969355813424</v>
       </c>
       <c r="K293" s="0">
         <v>0.98297065951951768</v>
@@ -33331,7 +34366,7 @@
         <v>1</v>
       </c>
       <c r="P293" s="0" t="s">
-        <v>425</v>
+        <v>770</v>
       </c>
     </row>
     <row r="294">
@@ -33363,7 +34398,7 @@
         <v>1</v>
       </c>
       <c r="J294" s="0">
-        <v>1060.6310502079718</v>
+        <v>1060.6310502079721</v>
       </c>
       <c r="K294" s="0">
         <v>0.99413834129628198</v>
@@ -33381,7 +34416,7 @@
         <v>1</v>
       </c>
       <c r="P294" s="0" t="s">
-        <v>426</v>
+        <v>771</v>
       </c>
     </row>
     <row r="295">
@@ -33413,7 +34448,7 @@
         <v>1</v>
       </c>
       <c r="J295" s="0">
-        <v>1721.0132386405028</v>
+        <v>1721.0132386405021</v>
       </c>
       <c r="K295" s="0">
         <v>0.98310352394719425</v>
@@ -33431,7 +34466,7 @@
         <v>1</v>
       </c>
       <c r="P295" s="0" t="s">
-        <v>427</v>
+        <v>772</v>
       </c>
     </row>
     <row r="296">
@@ -33481,7 +34516,7 @@
         <v>1</v>
       </c>
       <c r="P296" s="0" t="s">
-        <v>428</v>
+        <v>773</v>
       </c>
     </row>
     <row r="297">
@@ -33513,7 +34548,7 @@
         <v>1</v>
       </c>
       <c r="J297" s="0">
-        <v>1290.1572222988575</v>
+        <v>1290.157222298858</v>
       </c>
       <c r="K297" s="0">
         <v>0.99665092595450422</v>
@@ -33531,7 +34566,7 @@
         <v>1</v>
       </c>
       <c r="P297" s="0" t="s">
-        <v>429</v>
+        <v>774</v>
       </c>
     </row>
     <row r="298">
@@ -33563,7 +34598,7 @@
         <v>1</v>
       </c>
       <c r="J298" s="0">
-        <v>1390.20480024937</v>
+        <v>1390.2048002493702</v>
       </c>
       <c r="K298" s="0">
         <v>0.97951266077932142</v>
@@ -33581,7 +34616,7 @@
         <v>1</v>
       </c>
       <c r="P298" s="0" t="s">
-        <v>430</v>
+        <v>775</v>
       </c>
     </row>
     <row r="299">
@@ -33631,7 +34666,7 @@
         <v>1</v>
       </c>
       <c r="P299" s="0" t="s">
-        <v>431</v>
+        <v>776</v>
       </c>
     </row>
     <row r="300">
@@ -33681,7 +34716,7 @@
         <v>1</v>
       </c>
       <c r="P300" s="0" t="s">
-        <v>432</v>
+        <v>777</v>
       </c>
     </row>
     <row r="301">
@@ -33731,7 +34766,7 @@
         <v>1</v>
       </c>
       <c r="P301" s="0" t="s">
-        <v>433</v>
+        <v>778</v>
       </c>
     </row>
     <row r="302">
@@ -33781,7 +34816,7 @@
         <v>1</v>
       </c>
       <c r="P302" s="0" t="s">
-        <v>434</v>
+        <v>779</v>
       </c>
     </row>
     <row r="303">
@@ -33813,7 +34848,7 @@
         <v>1</v>
       </c>
       <c r="J303" s="0">
-        <v>1461.285999548682</v>
+        <v>1461.2859995486826</v>
       </c>
       <c r="K303" s="0">
         <v>0.99181305777577145</v>
@@ -33831,7 +34866,7 @@
         <v>1</v>
       </c>
       <c r="P303" s="0" t="s">
-        <v>435</v>
+        <v>780</v>
       </c>
     </row>
     <row r="304">
@@ -33881,7 +34916,7 @@
         <v>1</v>
       </c>
       <c r="P304" s="0" t="s">
-        <v>436</v>
+        <v>781</v>
       </c>
     </row>
     <row r="305">
@@ -33931,7 +34966,7 @@
         <v>1</v>
       </c>
       <c r="P305" s="0" t="s">
-        <v>437</v>
+        <v>782</v>
       </c>
     </row>
     <row r="306">
@@ -33981,7 +35016,7 @@
         <v>1</v>
       </c>
       <c r="P306" s="0" t="s">
-        <v>438</v>
+        <v>783</v>
       </c>
     </row>
     <row r="307">
@@ -34013,10 +35048,10 @@
         <v>1</v>
       </c>
       <c r="J307" s="0">
-        <v>2269.1203856965349</v>
+        <v>2269.1203856965344</v>
       </c>
       <c r="K307" s="0">
-        <v>0.98310623943385045</v>
+        <v>0.98310623943385034</v>
       </c>
       <c r="L307" s="0">
         <v>54</v>
@@ -34031,7 +35066,7 @@
         <v>1</v>
       </c>
       <c r="P307" s="0" t="s">
-        <v>439</v>
+        <v>784</v>
       </c>
     </row>
   </sheetData>
